--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -18,15 +18,15 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Instructions'!$A$4:$B$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Instructions'!$A$1:$B$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Button'!$A$8:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Button'!$A$8:$M$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Button'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Button'!$A$1:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Card'!$A$8:$M$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Button'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Card'!$A$8:$M$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Card'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Card'!$A$1:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dialog'!$A$8:$M$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Card'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dialog'!$A$8:$M$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Dialog'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Dialog'!$A$1:$M$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Dialog'!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -367,8 +367,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ButtonEvidence" displayName="ButtonEvidence" ref="A8:M33" headerRowCount="1">
-  <autoFilter ref="A8:M33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ButtonEvidence" displayName="ButtonEvidence" ref="A8:M34" headerRowCount="1">
+  <autoFilter ref="A8:M34"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -389,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CardEvidence" displayName="CardEvidence" ref="A8:M33" headerRowCount="1">
-  <autoFilter ref="A8:M33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CardEvidence" displayName="CardEvidence" ref="A8:M34" headerRowCount="1">
+  <autoFilter ref="A8:M34"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -411,8 +411,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DialogEvidence" displayName="DialogEvidence" ref="A8:M33" headerRowCount="1">
-  <autoFilter ref="A8:M33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DialogEvidence" displayName="DialogEvidence" ref="A8:M34" headerRowCount="1">
+  <autoFilter ref="A8:M34"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTA('Button'!A9:A33)</f>
+        <f>COUNTA('Button'!A9:A34)</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"not started")</f>
+        <f>COUNTIF('Button'!H9:H34,"not started")</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"partial")</f>
+        <f>COUNTIF('Button'!H9:H34,"partial")</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"implemented")</f>
+        <f>COUNTIF('Button'!H9:H34,"implemented")</f>
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"tested")</f>
+        <f>COUNTIF('Button'!H9:H34,"tested")</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"verified")</f>
+        <f>COUNTIF('Button'!H9:H34,"verified")</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"blocked")</f>
+        <f>COUNTIF('Button'!H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I8" s="8">
-        <f>COUNTIF('Button'!H9:H33,"not applicable")</f>
+        <f>COUNTIF('Button'!H9:H34,"not applicable")</f>
         <v/>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(SUM('Button'!M9:M33)/SUM('Button'!L9:L33),0)</f>
+        <f>IFERROR(SUM('Button'!M9:M34)/SUM('Button'!L9:L34),0)</f>
         <v/>
       </c>
       <c r="K8" s="8">
-        <f>IF(COUNTIFS('Button'!E9:E33,"package",'Button'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Button'!E9:E34,"package",'Button'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="L8" s="8">
-        <f>IF(COUNTIFS('Button'!E9:E33,"consumer",'Button'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Button'!E9:E34,"consumer",'Button'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="M8" s="8">
-        <f>IF(COUNTIFS('Button'!E9:E33,"retirement",'Button'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Button'!E9:E34,"retirement",'Button'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="N8" s="8">
@@ -930,51 +930,51 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTA('Card'!A9:A33)</f>
+        <f>COUNTA('Card'!A9:A34)</f>
         <v/>
       </c>
       <c r="C9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"not started")</f>
+        <f>COUNTIF('Card'!H9:H34,"not started")</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"partial")</f>
+        <f>COUNTIF('Card'!H9:H34,"partial")</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"implemented")</f>
+        <f>COUNTIF('Card'!H9:H34,"implemented")</f>
         <v/>
       </c>
       <c r="F9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"tested")</f>
+        <f>COUNTIF('Card'!H9:H34,"tested")</f>
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"verified")</f>
+        <f>COUNTIF('Card'!H9:H34,"verified")</f>
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"blocked")</f>
+        <f>COUNTIF('Card'!H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>COUNTIF('Card'!H9:H33,"not applicable")</f>
+        <f>COUNTIF('Card'!H9:H34,"not applicable")</f>
         <v/>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(SUM('Card'!M9:M33)/SUM('Card'!L9:L33),0)</f>
+        <f>IFERROR(SUM('Card'!M9:M34)/SUM('Card'!L9:L34),0)</f>
         <v/>
       </c>
       <c r="K9" s="8">
-        <f>IF(COUNTIFS('Card'!E9:E33,"package",'Card'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Card'!E9:E34,"package",'Card'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="L9" s="8">
-        <f>IF(COUNTIFS('Card'!E9:E33,"consumer",'Card'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Card'!E9:E34,"consumer",'Card'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="M9" s="8">
-        <f>IF(COUNTIFS('Card'!E9:E33,"retirement",'Card'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Card'!E9:E34,"retirement",'Card'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="N9" s="8">
@@ -989,51 +989,51 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTA('Dialog'!A9:A33)</f>
+        <f>COUNTA('Dialog'!A9:A34)</f>
         <v/>
       </c>
       <c r="C10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"not started")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"not started")</f>
         <v/>
       </c>
       <c r="D10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"partial")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"partial")</f>
         <v/>
       </c>
       <c r="E10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"implemented")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"implemented")</f>
         <v/>
       </c>
       <c r="F10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"tested")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"tested")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"verified")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"verified")</f>
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"blocked")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I10" s="8">
-        <f>COUNTIF('Dialog'!H9:H33,"not applicable")</f>
+        <f>COUNTIF('Dialog'!H9:H34,"not applicable")</f>
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(SUM('Dialog'!M9:M33)/SUM('Dialog'!L9:L33),0)</f>
+        <f>IFERROR(SUM('Dialog'!M9:M34)/SUM('Dialog'!L9:L34),0)</f>
         <v/>
       </c>
       <c r="K10" s="8">
-        <f>IF(COUNTIFS('Dialog'!E9:E33,"package",'Dialog'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Dialog'!E9:E34,"package",'Dialog'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="L10" s="8">
-        <f>IF(COUNTIFS('Dialog'!E9:E33,"consumer",'Dialog'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Dialog'!E9:E34,"consumer",'Dialog'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="M10" s="8">
-        <f>IF(COUNTIFS('Dialog'!E9:E33,"retirement",'Dialog'!M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS('Dialog'!E9:E34,"retirement",'Dialog'!M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="N10" s="8">
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTA(A9:A33)</f>
+        <f>COUNTA(A9:A34)</f>
         <v/>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="D4" s="4">
-        <f>SUM(M9:M33)</f>
+        <f>SUM(M9:M34)</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(D4/SUM(L9:L33),0)</f>
+        <f>IFERROR(D4/SUM(L9:L34),0)</f>
         <v/>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H4" s="4">
-        <f>COUNTIF(H9:H33,"blocked")</f>
+        <f>COUNTIF(H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="J4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"package",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"package",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="L4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"retirement",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"retirement",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Public API</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Public export and declaration surface match the approved brief</t>
+          <t>Atom capability audit covers mobile behavior and every Atom-owned gap is resolved through a released dependency</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
+          <t>Public export and declaration surface match the approved brief</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Visual system</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
+          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>types</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Default recipe and every approved visual option are implemented</t>
+          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Playground</t>
+          <t>Visual system</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Canonical overview and shortest finished state</t>
+          <t>Default recipe and every approved visual option are implemented</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>playground</t>
+          <t>source</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Every public recipe, size, and important state</t>
+          <t>Canonical overview and shortest finished state</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Mobile-first constrained viewport and intentional wide layout</t>
+          <t>Every public recipe, size, and important state</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Light, dark, and relevant preference modes</t>
+          <t>Mobile-first constrained viewport and intentional wide layout</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Long content, localization, zoom, and RTL stress</t>
+          <t>Light, dark, and relevant preference modes</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Token, className, style, slot, and documented part customization</t>
+          <t>Long content, localization, zoom, and RTL stress</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Stable route and deterministic state inputs for browser tests</t>
+          <t>Token, className, style, slot, and documented part customization</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Automated tests</t>
+          <t>Playground</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Vitest and Testing Library component contract tests</t>
+          <t>Stable route and deterministic state inputs for browser tests</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>playground</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Public type and declaration fixtures</t>
+          <t>Vitest and Testing Library component contract tests</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Playwright keyboard, pointer, focus, and state interactions</t>
+          <t>Public type and declaration fixtures</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Axe checks for canonical browser states</t>
+          <t>Playwright keyboard, pointer, focus, and state interactions</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Risk-based Chromium visual baselines reviewed</t>
+          <t>Axe checks for canonical browser states</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
+          <t>Risk-based Chromium visual baselines reviewed</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J26" s="15" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>SSR or server-safe consumer behavior where applicable</t>
+          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Manual evidence</t>
+          <t>Automated tests</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Numbered component manual-test protocol is complete</t>
+          <t>SSR or server-safe consumer behavior where applicable</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Latest required manual run is recorded and passes</t>
+          <t>Numbered component manual-test protocol is complete</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Manual evidence</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Public component documentation follows the standard template</t>
+          <t>Latest required manual run is recorded and passes</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Component changelog and applicable package release notes are updated</t>
+          <t>Public component documentation follows the standard template</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
+          <t>Component changelog and applicable package release notes are updated</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>package</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>docs</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>removal</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
@@ -2771,14 +2771,66 @@
         <v/>
       </c>
     </row>
+    <row r="34" ht="43" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>BUT-26</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>removal</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="16">
+        <f>IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A8:M33"/>
+  <autoFilter ref="A8:M34"/>
   <mergeCells count="3">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H9:H33">
+  <conditionalFormatting sqref="H9:H34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H9="not started"</formula>
     </cfRule>
@@ -2802,10 +2854,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H9:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H9:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$A$1:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I9:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I9:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$B$1:$B$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2823,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2862,7 +2914,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTA(A9:A33)</f>
+        <f>COUNTA(A9:A34)</f>
         <v/>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2871,7 +2923,7 @@
         </is>
       </c>
       <c r="D4" s="4">
-        <f>SUM(M9:M33)</f>
+        <f>SUM(M9:M34)</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2880,7 +2932,7 @@
         </is>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(D4/SUM(L9:L33),0)</f>
+        <f>IFERROR(D4/SUM(L9:L34),0)</f>
         <v/>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2889,7 +2941,7 @@
         </is>
       </c>
       <c r="H4" s="4">
-        <f>COUNTIF(H9:H33,"blocked")</f>
+        <f>COUNTIF(H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -2898,7 +2950,7 @@
         </is>
       </c>
       <c r="J4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"package",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"package",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2907,7 +2959,7 @@
         </is>
       </c>
       <c r="L4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"retirement",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"retirement",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
     </row>
@@ -3045,7 +3097,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Public API</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -3055,7 +3107,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Public export and declaration surface match the approved brief</t>
+          <t>Atom capability audit covers mobile behavior and every Atom-owned gap is resolved through a released dependency</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -3065,7 +3117,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr"/>
@@ -3076,7 +3128,7 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr"/>
@@ -3107,7 +3159,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
+          <t>Public export and declaration surface match the approved brief</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -3149,7 +3201,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Visual system</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -3159,7 +3211,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
+          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -3169,7 +3221,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>types</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr"/>
@@ -3211,7 +3263,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Default recipe and every approved visual option are implemented</t>
+          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -3232,7 +3284,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr"/>
@@ -3253,7 +3305,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Playground</t>
+          <t>Visual system</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -3263,7 +3315,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Canonical overview and shortest finished state</t>
+          <t>Default recipe and every approved visual option are implemented</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -3273,7 +3325,7 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>playground</t>
+          <t>source</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr"/>
@@ -3315,7 +3367,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Every public recipe, size, and important state</t>
+          <t>Canonical overview and shortest finished state</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -3367,7 +3419,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Mobile-first constrained viewport and intentional wide layout</t>
+          <t>Every public recipe, size, and important state</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -3419,7 +3471,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Light, dark, and relevant preference modes</t>
+          <t>Mobile-first constrained viewport and intentional wide layout</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -3471,7 +3523,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Long content, localization, zoom, and RTL stress</t>
+          <t>Light, dark, and relevant preference modes</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -3523,7 +3575,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Token, className, style, slot, and documented part customization</t>
+          <t>Long content, localization, zoom, and RTL stress</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -3575,7 +3627,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Stable route and deterministic state inputs for browser tests</t>
+          <t>Token, className, style, slot, and documented part customization</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -3596,7 +3648,7 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr"/>
@@ -3617,7 +3669,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Automated tests</t>
+          <t>Playground</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -3627,7 +3679,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Vitest and Testing Library component contract tests</t>
+          <t>Stable route and deterministic state inputs for browser tests</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -3637,7 +3689,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>playground</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
@@ -3679,7 +3731,7 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Public type and declaration fixtures</t>
+          <t>Vitest and Testing Library component contract tests</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -3731,7 +3783,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Playwright keyboard, pointer, focus, and state interactions</t>
+          <t>Public type and declaration fixtures</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -3783,7 +3835,7 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Axe checks for canonical browser states</t>
+          <t>Playwright keyboard, pointer, focus, and state interactions</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
@@ -3835,7 +3887,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Risk-based Chromium visual baselines reviewed</t>
+          <t>Axe checks for canonical browser states</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -3856,7 +3908,7 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr"/>
@@ -3887,7 +3939,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
+          <t>Risk-based Chromium visual baselines reviewed</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -3908,7 +3960,7 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J26" s="15" t="inlineStr"/>
@@ -3939,7 +3991,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>SSR or server-safe consumer behavior where applicable</t>
+          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -3981,7 +4033,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Manual evidence</t>
+          <t>Automated tests</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -3991,7 +4043,7 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Numbered component manual-test protocol is complete</t>
+          <t>SSR or server-safe consumer behavior where applicable</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -4001,7 +4053,7 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
@@ -4043,7 +4095,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Latest required manual run is recorded and passes</t>
+          <t>Numbered component manual-test protocol is complete</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -4064,7 +4116,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr"/>
@@ -4085,7 +4137,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Manual evidence</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -4095,7 +4147,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Public component documentation follows the standard template</t>
+          <t>Latest required manual run is recorded and passes</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -4105,7 +4157,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
@@ -4147,7 +4199,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Component changelog and applicable package release notes are updated</t>
+          <t>Public component documentation follows the standard template</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -4168,7 +4220,7 @@
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr"/>
@@ -4189,7 +4241,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -4199,17 +4251,17 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
+          <t>Component changelog and applicable package release notes are updated</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>package</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>docs</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
@@ -4220,7 +4272,7 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr"/>
@@ -4241,7 +4293,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -4251,17 +4303,17 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>removal</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
@@ -4285,14 +4337,66 @@
         <v/>
       </c>
     </row>
+    <row r="34" ht="43" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>CAR-26</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>removal</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="16">
+        <f>IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A8:M33"/>
+  <autoFilter ref="A8:M34"/>
   <mergeCells count="3">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H9:H33">
+  <conditionalFormatting sqref="H9:H34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H9="not started"</formula>
     </cfRule>
@@ -4316,10 +4420,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H9:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H9:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$A$1:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I9:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I9:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$B$1:$B$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4337,7 +4441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4376,7 +4480,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTA(A9:A33)</f>
+        <f>COUNTA(A9:A34)</f>
         <v/>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4385,7 +4489,7 @@
         </is>
       </c>
       <c r="D4" s="4">
-        <f>SUM(M9:M33)</f>
+        <f>SUM(M9:M34)</f>
         <v/>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4394,7 +4498,7 @@
         </is>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(D4/SUM(L9:L33),0)</f>
+        <f>IFERROR(D4/SUM(L9:L34),0)</f>
         <v/>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -4403,7 +4507,7 @@
         </is>
       </c>
       <c r="H4" s="4">
-        <f>COUNTIF(H9:H33,"blocked")</f>
+        <f>COUNTIF(H9:H34,"blocked")</f>
         <v/>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4412,7 +4516,7 @@
         </is>
       </c>
       <c r="J4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"package",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"package",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -4421,7 +4525,7 @@
         </is>
       </c>
       <c r="L4" s="4">
-        <f>IF(COUNTIFS(E9:E33,"retirement",M9:M33,"&lt;1")=0,"complete","open")</f>
+        <f>IF(COUNTIFS(E9:E34,"retirement",M9:M34,"&lt;1")=0,"complete","open")</f>
         <v/>
       </c>
     </row>
@@ -4559,7 +4663,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Public API</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -4569,7 +4673,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Public export and declaration surface match the approved brief</t>
+          <t>Atom capability audit covers mobile behavior and every Atom-owned gap is resolved through a released dependency</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -4579,7 +4683,7 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>types</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr"/>
@@ -4590,7 +4694,7 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr"/>
@@ -4621,7 +4725,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
+          <t>Public export and declaration surface match the approved brief</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -4663,7 +4767,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Visual system</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -4673,7 +4777,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
+          <t>Native props, refs, composition, and public slots follow the adopted API contract</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -4683,7 +4787,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>types</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr"/>
@@ -4725,7 +4829,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Default recipe and every approved visual option are implemented</t>
+          <t>Compiled CSS uses public brick classes, variables, layers, and semantic tokens</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -4746,7 +4850,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr"/>
@@ -4767,7 +4871,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Playground</t>
+          <t>Visual system</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -4777,7 +4881,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Canonical overview and shortest finished state</t>
+          <t>Default recipe and every approved visual option are implemented</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -4787,7 +4891,7 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>playground</t>
+          <t>source</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr"/>
@@ -4829,7 +4933,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Every public recipe, size, and important state</t>
+          <t>Canonical overview and shortest finished state</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -4881,7 +4985,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Mobile-first constrained viewport and intentional wide layout</t>
+          <t>Every public recipe, size, and important state</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -4933,7 +5037,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Light, dark, and relevant preference modes</t>
+          <t>Mobile-first constrained viewport and intentional wide layout</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -4985,7 +5089,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Long content, localization, zoom, and RTL stress</t>
+          <t>Light, dark, and relevant preference modes</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -5037,7 +5141,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Token, className, style, slot, and documented part customization</t>
+          <t>Long content, localization, zoom, and RTL stress</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -5089,7 +5193,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Stable route and deterministic state inputs for browser tests</t>
+          <t>Token, className, style, slot, and documented part customization</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -5110,7 +5214,7 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr"/>
@@ -5131,7 +5235,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Automated tests</t>
+          <t>Playground</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -5141,7 +5245,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Vitest and Testing Library component contract tests</t>
+          <t>Stable route and deterministic state inputs for browser tests</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -5151,7 +5255,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>playground</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
@@ -5193,7 +5297,7 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Public type and declaration fixtures</t>
+          <t>Vitest and Testing Library component contract tests</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -5245,7 +5349,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Playwright keyboard, pointer, focus, and state interactions</t>
+          <t>Public type and declaration fixtures</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -5297,7 +5401,7 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Axe checks for canonical browser states</t>
+          <t>Playwright keyboard, pointer, focus, and state interactions</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
@@ -5349,7 +5453,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Risk-based Chromium visual baselines reviewed</t>
+          <t>Axe checks for canonical browser states</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -5370,7 +5474,7 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr"/>
@@ -5401,7 +5505,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
+          <t>Risk-based Chromium visual baselines reviewed</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -5422,7 +5526,7 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J26" s="15" t="inlineStr"/>
@@ -5453,7 +5557,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>SSR or server-safe consumer behavior where applicable</t>
+          <t>Relevant Chromium, Firefox, WebKit, and mobile-profile checks</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -5495,7 +5599,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Manual evidence</t>
+          <t>Automated tests</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -5505,7 +5609,7 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Numbered component manual-test protocol is complete</t>
+          <t>SSR or server-safe consumer behavior where applicable</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -5515,7 +5619,7 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
@@ -5557,7 +5661,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Latest required manual run is recorded and passes</t>
+          <t>Numbered component manual-test protocol is complete</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -5578,7 +5682,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr"/>
@@ -5599,7 +5703,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Manual evidence</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -5609,7 +5713,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Public component documentation follows the standard template</t>
+          <t>Latest required manual run is recorded and passes</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -5619,7 +5723,7 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
@@ -5661,7 +5765,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Component changelog and applicable package release notes are updated</t>
+          <t>Public component documentation follows the standard template</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -5682,7 +5786,7 @@
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr"/>
@@ -5703,7 +5807,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -5713,17 +5817,17 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
+          <t>Component changelog and applicable package release notes are updated</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>package</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>docs</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
@@ -5734,7 +5838,7 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr"/>
@@ -5755,7 +5859,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -5765,17 +5869,17 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+          <t>Live consumer cutover is verified without adding new legacy Core coupling</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>removal</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
@@ -5799,14 +5903,66 @@
         <v/>
       </c>
     </row>
+    <row r="34" ht="43" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>DIA-26</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Legacy Core slice and authorized stale consumer evidence are removed</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>retirement</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>removal</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="16">
+        <f>IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A8:M33"/>
+  <autoFilter ref="A8:M34"/>
   <mergeCells count="3">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H9:H33">
+  <conditionalFormatting sqref="H9:H34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H9="not started"</formula>
     </cfRule>
@@ -5830,10 +5986,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H9:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H9:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$A$1:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I9:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I9:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Lists!$B$1:$B$2</formula1>
     </dataValidation>
   </dataValidations>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="221">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -476,22 +476,25 @@
     <t xml:space="preserve">consumer</t>
   </si>
   <si>
+    <t xml:space="preserve">../../../../apps/brick-consumer/tests/consumer.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core slice and authorized stale consumer evidence are removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removal</t>
+  </si>
+  <si>
     <t xml:space="preserve">not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUT-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Core slice and authorized stale consumer evidence are removed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">removal</t>
   </si>
   <si>
     <t xml:space="preserve">Card Evidence Matrix</t>
@@ -1570,7 +1573,7 @@
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B10,J8:J10)/SUM(B8:B10),0)</f>
-        <v>0.307692307692308</v>
+        <v>0.320512820512821</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1627,7 +1630,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">COUNTIF(Button!H9:H34,"not started")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">COUNTIF(Button!H9:H34,"partial")</f>
@@ -1643,7 +1646,7 @@
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">COUNTIF(Button!H9:H34,"verified")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="8" t="n">
         <f aca="false">COUNTIF(Button!H9:H34,"blocked")</f>
@@ -1655,7 +1658,7 @@
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">IFERROR(SUM(Button!M9:M34)/SUM(Button!L9:L34),0)</f>
-        <v>0.923076923076923</v>
+        <v>0.961538461538462</v>
       </c>
       <c r="K8" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Button!E9:E34,"package",Button!M9:M34,"&lt;1")=0,"complete","open")</f>
@@ -1663,7 +1666,7 @@
       </c>
       <c r="L8" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Button!E9:E34,"consumer",Button!M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="M8" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Button!E9:E34,"retirement",Button!M9:M34,"&lt;1")=0,"complete","open")</f>
@@ -2072,14 +2075,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M34)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L34),0)</f>
-        <v>0.923076923076923</v>
+        <v>0.961538461538462</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -3140,21 +3143,25 @@
       <c r="F33" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="15"/>
+      <c r="G33" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="H33" s="15" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="15"/>
+      <c r="J33" s="19" t="n">
+        <v>46219</v>
+      </c>
       <c r="K33" s="15"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="18" t="n">
         <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3178,7 +3185,7 @@
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>72</v>
@@ -3296,7 +3303,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3313,7 +3320,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3432,7 +3439,7 @@
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>59</v>
@@ -3441,7 +3448,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>61</v>
@@ -3451,7 +3458,7 @@
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>65</v>
@@ -3468,7 +3475,7 @@
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>67</v>
@@ -3477,7 +3484,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>61</v>
@@ -3487,7 +3494,7 @@
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>72</v>
@@ -3504,7 +3511,7 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>59</v>
@@ -3513,7 +3520,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>61</v>
@@ -3523,7 +3530,7 @@
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>65</v>
@@ -3540,7 +3547,7 @@
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>59</v>
@@ -3549,7 +3556,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>61</v>
@@ -3559,7 +3566,7 @@
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>65</v>
@@ -3576,7 +3583,7 @@
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>81</v>
@@ -3595,7 +3602,7 @@
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>65</v>
@@ -3612,7 +3619,7 @@
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>81</v>
@@ -3621,7 +3628,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>61</v>
@@ -3631,7 +3638,7 @@
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>72</v>
@@ -3648,7 +3655,7 @@
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>88</v>
@@ -3667,7 +3674,7 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>72</v>
@@ -3684,7 +3691,7 @@
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>88</v>
@@ -3693,7 +3700,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>61</v>
@@ -3703,7 +3710,7 @@
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>72</v>
@@ -3720,7 +3727,7 @@
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>88</v>
@@ -3739,7 +3746,7 @@
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>72</v>
@@ -3756,7 +3763,7 @@
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>88</v>
@@ -3765,7 +3772,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
@@ -3775,7 +3782,7 @@
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>72</v>
@@ -3792,7 +3799,7 @@
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>88</v>
@@ -3811,7 +3818,7 @@
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>72</v>
@@ -3828,7 +3835,7 @@
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>88</v>
@@ -3837,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
@@ -3847,7 +3854,7 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>72</v>
@@ -3864,7 +3871,7 @@
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>88</v>
@@ -3883,7 +3890,7 @@
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>65</v>
@@ -3900,7 +3907,7 @@
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>107</v>
@@ -3919,7 +3926,7 @@
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>65</v>
@@ -3936,7 +3943,7 @@
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>107</v>
@@ -3945,7 +3952,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
@@ -3955,7 +3962,7 @@
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>65</v>
@@ -3972,7 +3979,7 @@
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>107</v>
@@ -3991,7 +3998,7 @@
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>65</v>
@@ -4008,7 +4015,7 @@
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>107</v>
@@ -4027,7 +4034,7 @@
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>65</v>
@@ -4044,7 +4051,7 @@
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>107</v>
@@ -4063,7 +4070,7 @@
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>72</v>
@@ -4080,7 +4087,7 @@
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>107</v>
@@ -4099,7 +4106,7 @@
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>65</v>
@@ -4116,7 +4123,7 @@
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>107</v>
@@ -4125,7 +4132,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
@@ -4135,7 +4142,7 @@
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>65</v>
@@ -4152,7 +4159,7 @@
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>128</v>
@@ -4171,7 +4178,7 @@
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>65</v>
@@ -4188,7 +4195,7 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>128</v>
@@ -4207,7 +4214,7 @@
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>72</v>
@@ -4224,7 +4231,7 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>134</v>
@@ -4243,7 +4250,7 @@
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>72</v>
@@ -4260,7 +4267,7 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>134</v>
@@ -4279,7 +4286,7 @@
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>65</v>
@@ -4296,7 +4303,7 @@
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>142</v>
@@ -4315,7 +4322,7 @@
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>72</v>
@@ -4332,7 +4339,7 @@
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>147</v>
@@ -4351,7 +4358,7 @@
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>72</v>
@@ -4445,7 +4452,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4462,7 +4469,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4581,7 +4588,7 @@
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>59</v>
@@ -4590,7 +4597,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>61</v>
@@ -4600,7 +4607,7 @@
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>65</v>
@@ -4617,7 +4624,7 @@
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>67</v>
@@ -4626,7 +4633,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>61</v>
@@ -4636,7 +4643,7 @@
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>72</v>
@@ -4653,7 +4660,7 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>59</v>
@@ -4662,7 +4669,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>61</v>
@@ -4672,7 +4679,7 @@
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>65</v>
@@ -4689,7 +4696,7 @@
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>59</v>
@@ -4698,7 +4705,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>61</v>
@@ -4708,7 +4715,7 @@
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>65</v>
@@ -4725,7 +4732,7 @@
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>81</v>
@@ -4744,7 +4751,7 @@
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>65</v>
@@ -4761,7 +4768,7 @@
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>81</v>
@@ -4770,7 +4777,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>61</v>
@@ -4780,7 +4787,7 @@
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>72</v>
@@ -4797,7 +4804,7 @@
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>88</v>
@@ -4816,7 +4823,7 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>72</v>
@@ -4833,7 +4840,7 @@
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>88</v>
@@ -4842,7 +4849,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>61</v>
@@ -4852,7 +4859,7 @@
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>72</v>
@@ -4869,7 +4876,7 @@
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>88</v>
@@ -4888,7 +4895,7 @@
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>72</v>
@@ -4905,7 +4912,7 @@
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>88</v>
@@ -4914,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
@@ -4924,7 +4931,7 @@
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>72</v>
@@ -4941,7 +4948,7 @@
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>88</v>
@@ -4960,7 +4967,7 @@
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>72</v>
@@ -4977,7 +4984,7 @@
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>88</v>
@@ -4986,7 +4993,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
@@ -4996,7 +5003,7 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>72</v>
@@ -5013,7 +5020,7 @@
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>88</v>
@@ -5032,7 +5039,7 @@
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>65</v>
@@ -5049,7 +5056,7 @@
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>107</v>
@@ -5068,7 +5075,7 @@
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>65</v>
@@ -5085,7 +5092,7 @@
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>107</v>
@@ -5094,7 +5101,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
@@ -5104,7 +5111,7 @@
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>65</v>
@@ -5121,7 +5128,7 @@
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>107</v>
@@ -5140,7 +5147,7 @@
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>65</v>
@@ -5157,7 +5164,7 @@
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>107</v>
@@ -5176,7 +5183,7 @@
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>65</v>
@@ -5193,7 +5200,7 @@
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>107</v>
@@ -5212,7 +5219,7 @@
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>72</v>
@@ -5229,7 +5236,7 @@
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>107</v>
@@ -5248,7 +5255,7 @@
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>65</v>
@@ -5265,7 +5272,7 @@
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>107</v>
@@ -5274,7 +5281,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
@@ -5284,7 +5291,7 @@
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>65</v>
@@ -5301,7 +5308,7 @@
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>128</v>
@@ -5320,7 +5327,7 @@
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>65</v>
@@ -5337,7 +5344,7 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>128</v>
@@ -5356,7 +5363,7 @@
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>72</v>
@@ -5373,7 +5380,7 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>134</v>
@@ -5392,7 +5399,7 @@
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>72</v>
@@ -5409,7 +5416,7 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>134</v>
@@ -5428,7 +5435,7 @@
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>65</v>
@@ -5445,7 +5452,7 @@
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>142</v>
@@ -5464,7 +5471,7 @@
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>72</v>
@@ -5481,7 +5488,7 @@
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>147</v>
@@ -5500,7 +5507,7 @@
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>72</v>
@@ -5579,7 +5586,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>72</v>
@@ -5587,7 +5594,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
@@ -5595,7 +5602,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5610,12 +5617,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -5,21 +5,21 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="2" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Index" sheetId="1" state="hidden" r:id="rId3"/>
-    <sheet name="Instructions" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Index" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Button" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Card" sheetId="4" state="hidden" r:id="rId6"/>
-    <sheet name="Dialog" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="Card" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Dialog" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="_Lists" sheetId="6" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Button!$A$1:$M$34</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Button!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Button!$A$8:$M$34</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Card!$A$1:$M$34</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Card!$A$1:$M$41</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Card!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Card!$A$8:$M$34</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dialog!$A$1:$M$34</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="285">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -500,180 +500,375 @@
     <t xml:space="preserve">Card Evidence Matrix</t>
   </si>
   <si>
+    <t xml:space="preserve">Evidence gates for the adopted static Card compound, its seven public parts, package proof, consumer cutover, and dependency-blocked legacy retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namespace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static Card namespace implementation has no Core, application, or local behavior wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/card/Card.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atom capability audit confirms Card owns no behavior and requires no Atom patch or local workaround</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/card-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and card subpath exports, declarations, defaults, and closed unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/card.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native props, refs, className, style, events, children, and overridable slots forward on every public part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/card.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral div default, restricted semantic elements, variant and size defaults, and no invented role or focus state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title, description, and compact trailing action preserve source order and resilient narrow-screen layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/card.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heading defaults to h3 and supports only h1 through h6 with native heading semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supporting text renders as a native paragraph and forwards its complete public DOM contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compact trailing layout creates no role, focus, click, keyboard, or generated control behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/card.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional body region renders one native element and omitted anatomy creates no empty regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional footer preserves explicit controls, logical order, wrapping, and visible focus at narrow widths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled CSS uses public brick classes, component tokens, layers, logical properties, and semantic roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/card/card.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outline, elevated, and subtle variants plus small, medium, and large density recipes remain distinct in light and dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical article and every partial anatomy are built from public Card parts and Brick Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every variant and size plus media and single-action-link composition are represented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-first constrained layouts and intentional wide layouts preserve natural Card height and containment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light, dark, scoped appearance, forced colors, and reduced motion retain hierarchy and boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long content, unbroken text, localization, 400 percent zoom, and RTL remain contained and readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Card tokens, stable classes, style, data attributes, and overridable part slots are inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable Card route and deterministic scenario selectors support repeatable browser tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest and Testing Library cover the complete component and native DOM contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public type, declaration, invalid-prop, root export, and card-subpath fixtures pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright verifies static semantics, explicit-control focus, accessible link naming, reflow, and zoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axe reports no automatically detectable violations for canonical Card states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six deterministic Chromium visual baselines are reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone release matrix records 73 passes and 42 intentional skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../playwright.config.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSR, package boundary, tarball, and clean React 18 and React 19 consumer verification pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/package/ssr.test.mjs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered ten-step Card manual-test protocol is complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run is recorded and passes after every discovered finding was corrected and retested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Card documentation follows the standard template and documents whole-card accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/card/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card changelog and package release notes record the initial contract and dark-elevation correction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/card/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent consumer uses public Card for project, checklist, and invitation surfaces and passes ten browser checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Card family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Card source, exports, compatibility, and stale evidence are removed only after dependents are resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/core-dependency-ledger.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog, Drawer, and AlertDialog still consume legacy Card parts or types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog Evidence Matrix</t>
+  </si>
+  <si>
     <t xml:space="preserve">Common requirements from Brick's adopted quality contract. Add approved anatomy and component-specific rows after the component brief lands.</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-01</t>
+    <t xml:space="preserve">DIA-01</t>
   </si>
   <si>
     <t xml:space="preserve">Implementation uses public Atom behavior without Core or local headless wrappers</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-02</t>
+    <t xml:space="preserve">DIA-02</t>
   </si>
   <si>
     <t xml:space="preserve">Atom capability audit covers mobile behavior and every Atom-owned gap is resolved through a released dependency</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-03</t>
+    <t xml:space="preserve">DIA-03</t>
   </si>
   <si>
     <t xml:space="preserve">Public export and declaration surface match the approved brief</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-04</t>
+    <t xml:space="preserve">DIA-04</t>
   </si>
   <si>
     <t xml:space="preserve">Native props, refs, composition, and public slots follow the adopted API contract</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-06</t>
+    <t xml:space="preserve">DIA-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-06</t>
   </si>
   <si>
     <t xml:space="preserve">Default recipe and every approved visual option are implemented</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-08</t>
+    <t xml:space="preserve">DIA-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-08</t>
   </si>
   <si>
     <t xml:space="preserve">Every public recipe, size, and important state</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-10</t>
+    <t xml:space="preserve">DIA-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-10</t>
   </si>
   <si>
     <t xml:space="preserve">Light, dark, and relevant preference modes</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-12</t>
+    <t xml:space="preserve">DIA-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-12</t>
   </si>
   <si>
     <t xml:space="preserve">Token, className, style, slot, and documented part customization</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-15</t>
+    <t xml:space="preserve">DIA-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-15</t>
   </si>
   <si>
     <t xml:space="preserve">Public type and declaration fixtures</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-20</t>
+    <t xml:space="preserve">DIA-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-20</t>
   </si>
   <si>
     <t xml:space="preserve">SSR or server-safe consumer behavior where applicable</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIA-21</t>
   </si>
   <si>
@@ -696,9 +891,6 @@
   </si>
   <si>
     <t xml:space="preserve">implemented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blocked</t>
   </si>
   <si>
     <t xml:space="preserve">not applicable</t>
@@ -974,7 +1166,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1017,7 +1209,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF475569"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF991B1B"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1242,8 +1450,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CardEvidence" displayName="CardEvidence" ref="A8:M34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A8:M34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CardEvidence" displayName="CardEvidence" ref="A8:M41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A8:M41"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -1566,14 +1774,14 @@
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">SUM(H8:H10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B10,J8:J10)/SUM(B8:B10),0)</f>
-        <v>0.320512820512821</v>
+        <v>0.670588235294118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1682,56 +1890,56 @@
         <v>20</v>
       </c>
       <c r="B9" s="8" t="n">
-        <f aca="false">COUNTA(Card!A9:A34)</f>
-        <v>26</v>
+        <f aca="false">COUNTA(Card!A9:A41)</f>
+        <v>33</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"not started")</f>
-        <v>26</v>
+        <f aca="false">COUNTIF(Card!H9:H41,"not started")</f>
+        <v>0</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"partial")</f>
+        <f aca="false">COUNTIF(Card!H9:H41,"partial")</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"implemented")</f>
+        <f aca="false">COUNTIF(Card!H9:H41,"implemented")</f>
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"tested")</f>
+        <f aca="false">COUNTIF(Card!H9:H41,"tested")</f>
+        <v>18</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <f aca="false">COUNTIF(Card!H9:H41,"verified")</f>
+        <v>14</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <f aca="false">COUNTIF(Card!H9:H41,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <f aca="false">COUNTIF(Card!H9:H41,"not applicable")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"verified")</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <f aca="false">COUNTIF(Card!H9:H34,"not applicable")</f>
-        <v>0</v>
-      </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">IFERROR(SUM(Card!M9:M34)/SUM(Card!L9:L34),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(SUM(Card!M9:M41)/SUM(Card!L9:L41),0)</f>
+        <v>0.96969696969697</v>
       </c>
       <c r="K9" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Card!E9:E34,"package",Card!M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(Card!E9:E41,"package",Card!M9:M41,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="L9" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Card!E9:E34,"consumer",Card!M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(Card!E9:E41,"consumer",Card!M9:M41,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="M9" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Card!E9:E34,"retirement",Card!M9:M34,"&lt;1")=0,"complete","open")</f>
+        <f aca="false">IF(COUNTIFS(Card!E9:E41,"retirement",Card!M9:M41,"&lt;1")=0,"complete","open")</f>
         <v>open</v>
       </c>
       <c r="N9" s="8" t="str">
         <f aca="false">IF(H9&gt;0,"blocked",IF(AND(J9=1,K9="complete",L9="complete",M9="complete"),"complete",IF(J9=0,"not started","in progress")))</f>
-        <v>not started</v>
+        <v>blocked</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1797,25 +2005,25 @@
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="N8:N10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$N8="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$N8="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$N8="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$N8="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$N8="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$N8="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$N8="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3208,25 +3416,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3258,11 +3466,14 @@
     <hyperlink ref="G23" r:id="rId15" display="../test/types/public-api.test.ts"/>
     <hyperlink ref="G24" r:id="rId16" display="tests/button.spec.ts"/>
     <hyperlink ref="G25" r:id="rId17" display="tests/foundation.spec.ts"/>
-    <hyperlink ref="G27" r:id="rId18" display="../../playwright.config.ts"/>
-    <hyperlink ref="G28" r:id="rId19" display="../scripts/verify-consumers.mjs"/>
-    <hyperlink ref="G29" r:id="rId20" display="manual-tests/button.md"/>
-    <hyperlink ref="G31" r:id="rId21" display="../docs/components/button/README.md"/>
-    <hyperlink ref="G32" r:id="rId22" display="../docs/components/button/CHANGELOG.md"/>
+    <hyperlink ref="G26" r:id="rId18" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G27" r:id="rId19" display="../../playwright.config.ts"/>
+    <hyperlink ref="G28" r:id="rId20" display="../scripts/verify-consumers.mjs"/>
+    <hyperlink ref="G29" r:id="rId21" display="manual-tests/button.md"/>
+    <hyperlink ref="G30" r:id="rId22" display="manual-tests/button.md"/>
+    <hyperlink ref="G31" r:id="rId23" display="../docs/components/button/README.md"/>
+    <hyperlink ref="G32" r:id="rId24" display="../docs/components/button/CHANGELOG.md"/>
+    <hyperlink ref="G33" r:id="rId25" display="../../../../apps/brick-consumer/tests/consumer.spec.ts"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3271,9 +3482,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId23"/>
+  <drawing r:id="rId26"/>
   <tableParts>
-    <tablePart r:id="rId24"/>
+    <tablePart r:id="rId27"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3283,7 +3494,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -3340,42 +3551,42 @@
         <v>7</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">COUNTA(A9:A34)</f>
-        <v>26</v>
+        <f aca="false">COUNTA(A9:A41)</f>
+        <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">SUM(M9:M34)</f>
-        <v>0</v>
+        <f aca="false">SUM(M9:M41)</f>
+        <v>32</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">IFERROR(D4/SUM(L9:L34),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(D4/SUM(L9:L41),0)</f>
+        <v>0.96969696969697</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <f aca="false">COUNTIF(H9:H34,"blocked")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(H9:H41,"blocked")</f>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f aca="false">IF(COUNTIFS(E9:E34,"package",M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(E9:E41,"package",M9:M41,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="5" t="str">
-        <f aca="false">IF(COUNTIFS(E9:E34,"retirement",M9:M34,"&lt;1")=0,"complete","open")</f>
+        <f aca="false">IF(COUNTIFS(E9:E41,"retirement",M9:M41,"&lt;1")=0,"complete","open")</f>
         <v>open</v>
       </c>
     </row>
@@ -3445,10 +3656,10 @@
         <v>59</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>61</v>
@@ -3456,26 +3667,30 @@
       <c r="F9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="15" t="s">
+        <v>157</v>
+      </c>
       <c r="H9" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K9" s="15"/>
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="18" t="n">
         <f aca="false">IF(H9="not applicable",IF(K9&lt;&gt;"",1,0),IF(I9="yes",IF(H9="verified",1,0),IF(OR(H9="tested",H9="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>67</v>
@@ -3484,7 +3699,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>61</v>
@@ -3492,35 +3707,39 @@
       <c r="F10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>160</v>
+      </c>
       <c r="H10" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K10" s="15"/>
       <c r="L10" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="18" t="n">
         <f aca="false">IF(H10="not applicable",IF(K10&lt;&gt;"",1,0),IF(I10="yes",IF(H10="verified",1,0),IF(OR(H10="tested",H10="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>61</v>
@@ -3528,503 +3747,559 @@
       <c r="F11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="H11" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K11" s="15"/>
       <c r="L11" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="18" t="n">
         <f aca="false">IF(H11="not applicable",IF(K11&lt;&gt;"",1,0),IF(I11="yes",IF(H11="verified",1,0),IF(OR(H11="tested",H11="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H12" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K12" s="15"/>
       <c r="L12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M12" s="18" t="n">
         <f aca="false">IF(H12="not applicable",IF(K12&lt;&gt;"",1,0),IF(I12="yes",IF(H12="verified",1,0),IF(OR(H12="tested",H12="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H13" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="15"/>
+      <c r="J13" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K13" s="15"/>
       <c r="L13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="18" t="n">
         <f aca="false">IF(H13="not applicable",IF(K13&lt;&gt;"",1,0),IF(I13="yes",IF(H13="verified",1,0),IF(OR(H13="tested",H13="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H14" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="15"/>
+      <c r="J14" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K14" s="15"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="18" t="n">
         <f aca="false">IF(H14="not applicable",IF(K14&lt;&gt;"",1,0),IF(I14="yes",IF(H14="verified",1,0),IF(OR(H14="tested",H14="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H15" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K15" s="15"/>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M15" s="18" t="n">
         <f aca="false">IF(H15="not applicable",IF(K15&lt;&gt;"",1,0),IF(I15="yes",IF(H15="verified",1,0),IF(OR(H15="tested",H15="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="D16" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K16" s="15"/>
       <c r="L16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="18" t="n">
         <f aca="false">IF(H16="not applicable",IF(K16&lt;&gt;"",1,0),IF(I16="yes",IF(H16="verified",1,0),IF(OR(H16="tested",H16="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>184</v>
+      </c>
       <c r="H17" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K17" s="15"/>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="18" t="n">
         <f aca="false">IF(H17="not applicable",IF(K17&lt;&gt;"",1,0),IF(I17="yes",IF(H17="verified",1,0),IF(OR(H17="tested",H17="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H18" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K18" s="15"/>
       <c r="L18" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="18" t="n">
         <f aca="false">IF(H18="not applicable",IF(K18&lt;&gt;"",1,0),IF(I18="yes",IF(H18="verified",1,0),IF(OR(H18="tested",H18="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H19" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="15"/>
+      <c r="J19" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K19" s="15"/>
       <c r="L19" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M19" s="18" t="n">
         <f aca="false">IF(H19="not applicable",IF(K19&lt;&gt;"",1,0),IF(I19="yes",IF(H19="verified",1,0),IF(OR(H19="tested",H19="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="15"/>
+        <v>62</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>193</v>
+      </c>
       <c r="H20" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K20" s="15"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="18" t="n">
         <f aca="false">IF(H20="not applicable",IF(K20&lt;&gt;"",1,0),IF(I20="yes",IF(H20="verified",1,0),IF(OR(H20="tested",H20="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J21" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K21" s="15"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="18" t="n">
         <f aca="false">IF(H21="not applicable",IF(K21&lt;&gt;"",1,0),IF(I21="yes",IF(H21="verified",1,0),IF(OR(H21="tested",H21="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H22" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J22" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K22" s="15"/>
       <c r="L22" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M22" s="18" t="n">
         <f aca="false">IF(H22="not applicable",IF(K22&lt;&gt;"",1,0),IF(I22="yes",IF(H22="verified",1,0),IF(OR(H22="tested",H22="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>184</v>
+      </c>
       <c r="H23" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J23" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K23" s="15"/>
       <c r="L23" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M23" s="18" t="n">
         <f aca="false">IF(H23="not applicable",IF(K23&lt;&gt;"",1,0),IF(I23="yes",IF(H23="verified",1,0),IF(OR(H23="tested",H23="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H24" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J24" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K24" s="15"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="18" t="n">
         <f aca="false">IF(H24="not applicable",IF(K24&lt;&gt;"",1,0),IF(I24="yes",IF(H24="verified",1,0),IF(OR(H24="tested",H24="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>61</v>
@@ -4032,344 +4307,666 @@
       <c r="F25" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="15"/>
+      <c r="G25" s="15" t="s">
+        <v>98</v>
+      </c>
       <c r="H25" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K25" s="15"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="18" t="n">
         <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H26" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="15"/>
+      <c r="J26" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K26" s="15"/>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="18" t="n">
         <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>174</v>
+      </c>
       <c r="H27" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K27" s="15"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="18" t="n">
         <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>184</v>
+      </c>
       <c r="H28" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J28" s="15"/>
+      <c r="J28" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K28" s="15"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="18" t="n">
         <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="H29" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J29" s="15"/>
+      <c r="J29" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K29" s="15"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="18" t="n">
         <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="H30" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K30" s="15"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M30" s="18" t="n">
         <f aca="false">IF(H30="not applicable",IF(K30&lt;&gt;"",1,0),IF(I30="yes",IF(H30="verified",1,0),IF(OR(H30="tested",H30="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>184</v>
+      </c>
       <c r="H31" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J31" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K31" s="15"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="18" t="n">
         <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G32" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="H32" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J32" s="15"/>
+      <c r="J32" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K32" s="15"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="18" t="n">
         <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="H33" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="15"/>
+      <c r="J33" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K33" s="15"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="18" t="n">
         <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="G34" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>222</v>
+      </c>
       <c r="H34" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>46220</v>
+      </c>
       <c r="K34" s="15"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="18" t="n">
         <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K36" s="15"/>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K37" s="15"/>
+      <c r="L37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <f aca="false">IF(H37="not applicable",IF(K37&lt;&gt;"",1,0),IF(I37="yes",IF(H37="verified",1,0),IF(OR(H37="tested",H37="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K38" s="15"/>
+      <c r="L38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <f aca="false">IF(H38="not applicable",IF(K38&lt;&gt;"",1,0),IF(I38="yes",IF(H38="verified",1,0),IF(OR(H38="tested",H38="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K39" s="15"/>
+      <c r="L39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <f aca="false">IF(H39="not applicable",IF(K39&lt;&gt;"",1,0),IF(I39="yes",IF(H39="verified",1,0),IF(OR(H39="tested",H39="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K40" s="15"/>
+      <c r="L40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <f aca="false">IF(H40="not applicable",IF(K40&lt;&gt;"",1,0),IF(I40="yes",IF(H40="verified",1,0),IF(OR(H40="tested",H40="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <f aca="false">IF(H41="not applicable",IF(K41&lt;&gt;"",1,0),IF(I41="yes",IF(H41="verified",1,0),IF(OR(H41="tested",H41="verified"),1,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -4380,39 +4977,74 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A6:M6"/>
   </mergeCells>
-  <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <conditionalFormatting sqref="H9:H41">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H34" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H41" type="list">
       <formula1>_Lists!$A$1:$A$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I34" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I41" type="list">
       <formula1>_Lists!$B$1:$B$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G9" r:id="rId1" display="../src/components/card/Card.tsx"/>
+    <hyperlink ref="G10" r:id="rId2" display="../../docs/card-component-brief.md"/>
+    <hyperlink ref="G11" r:id="rId3" display="../src/card.ts"/>
+    <hyperlink ref="G12" r:id="rId4" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G13" r:id="rId5" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G14" r:id="rId6" display="manual-tests/card.md"/>
+    <hyperlink ref="G15" r:id="rId7" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G16" r:id="rId8" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G17" r:id="rId9" display="tests/card.spec.ts"/>
+    <hyperlink ref="G18" r:id="rId10" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G19" r:id="rId11" display="manual-tests/card.md"/>
+    <hyperlink ref="G20" r:id="rId12" display="../src/components/card/card.css"/>
+    <hyperlink ref="G21" r:id="rId13" display="manual-tests/card.md"/>
+    <hyperlink ref="G22" r:id="rId14" display="manual-tests/card.md"/>
+    <hyperlink ref="G23" r:id="rId15" display="tests/card.spec.ts"/>
+    <hyperlink ref="G24" r:id="rId16" display="manual-tests/card.md"/>
+    <hyperlink ref="G25" r:id="rId17" display="tests/preferences.spec.ts"/>
+    <hyperlink ref="G26" r:id="rId18" display="manual-tests/card.md"/>
+    <hyperlink ref="G27" r:id="rId19" display="manual-tests/card.md"/>
+    <hyperlink ref="G28" r:id="rId20" display="tests/card.spec.ts"/>
+    <hyperlink ref="G29" r:id="rId21" display="../test/components/card.test.tsx"/>
+    <hyperlink ref="G30" r:id="rId22" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G31" r:id="rId23" display="tests/card.spec.ts"/>
+    <hyperlink ref="G32" r:id="rId24" display="tests/foundation.spec.ts"/>
+    <hyperlink ref="G33" r:id="rId25" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G34" r:id="rId26" display="../playwright.config.ts"/>
+    <hyperlink ref="G35" r:id="rId27" display="../test/package/ssr.test.mjs"/>
+    <hyperlink ref="G36" r:id="rId28" display="manual-tests/card.md"/>
+    <hyperlink ref="G37" r:id="rId29" display="manual-tests/card.md"/>
+    <hyperlink ref="G38" r:id="rId30" display="../docs/components/card/README.md"/>
+    <hyperlink ref="G39" r:id="rId31" display="../docs/components/card/CHANGELOG.md"/>
+    <hyperlink ref="G40" r:id="rId32" display="../../../../apps/brick-consumer/tests/consumer.spec.ts"/>
+    <hyperlink ref="G41" r:id="rId33" display="../../docs/core-dependency-ledger.md"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4420,9 +5052,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId34"/>
   <tableParts>
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId35"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4452,7 +5084,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4469,7 +5101,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4588,7 +5220,7 @@
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>59</v>
@@ -4597,7 +5229,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>61</v>
@@ -4624,7 +5256,7 @@
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>67</v>
@@ -4633,7 +5265,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>61</v>
@@ -4660,7 +5292,7 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>59</v>
@@ -4669,7 +5301,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>61</v>
@@ -4696,7 +5328,7 @@
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>59</v>
@@ -4705,7 +5337,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>61</v>
@@ -4732,7 +5364,7 @@
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>81</v>
@@ -4768,7 +5400,7 @@
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>81</v>
@@ -4777,7 +5409,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>61</v>
@@ -4804,7 +5436,7 @@
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>88</v>
@@ -4840,7 +5472,7 @@
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>88</v>
@@ -4849,7 +5481,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>61</v>
@@ -4876,7 +5508,7 @@
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>88</v>
@@ -4912,7 +5544,7 @@
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>88</v>
@@ -4921,7 +5553,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>170</v>
+        <v>262</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
@@ -4948,7 +5580,7 @@
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>88</v>
@@ -4984,7 +5616,7 @@
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>88</v>
@@ -4993,7 +5625,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
@@ -5020,7 +5652,7 @@
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>88</v>
@@ -5056,7 +5688,7 @@
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>107</v>
@@ -5092,7 +5724,7 @@
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>107</v>
@@ -5101,7 +5733,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
@@ -5128,7 +5760,7 @@
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>107</v>
@@ -5164,7 +5796,7 @@
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>107</v>
@@ -5200,7 +5832,7 @@
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>208</v>
+        <v>272</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>107</v>
@@ -5236,7 +5868,7 @@
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>107</v>
@@ -5272,7 +5904,7 @@
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>107</v>
@@ -5281,7 +5913,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
@@ -5308,7 +5940,7 @@
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>128</v>
@@ -5344,7 +5976,7 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>128</v>
@@ -5380,7 +6012,7 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>134</v>
@@ -5416,7 +6048,7 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>214</v>
+        <v>279</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>134</v>
@@ -5452,7 +6084,7 @@
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>142</v>
@@ -5488,7 +6120,7 @@
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>216</v>
+        <v>281</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>147</v>
@@ -5530,25 +6162,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5594,7 +6226,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
@@ -5602,7 +6234,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>218</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5617,12 +6249,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -22,9 +22,9 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Card!$A$1:$M$41</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Card!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Card!$A$8:$M$34</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dialog!$A$1:$M$34</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dialog!$A$1:$M$45</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Dialog!$1:$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Dialog!$A$8:$M$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Dialog!$A$8:$M$45</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Index!$A$1:$N$10</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$B$18</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Instructions!$A$4:$B$18</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="338">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -776,115 +776,274 @@
     <t xml:space="preserve">Dialog Evidence Matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">Common requirements from Brick's adopted quality contract. Add approved anatomy and component-specific rows after the component brief lands.</t>
+    <t xml:space="preserve">Evidence gates for the adopted modal Dialog compound, its twelve public parts, package proof, consumer cutover, and dependency-blocked legacy retirement.</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Implementation uses public Atom behavior without Core or local headless wrappers</t>
+    <t xml:space="preserve">Implementation directly composes public Atom 0.3.2 behavior without Core or local headless wrappers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/dialog/Dialog.tsx</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Atom capability audit covers mobile behavior and every Atom-owned gap is resolved through a released dependency</t>
+    <t xml:space="preserve">Adopted capability audit covers focus, nested layers, portals, isolation, scrolling, touch focus, presence, and dismissal; released Atom gaps are resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/dialog-component-brief.md</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Public export and declaration surface match the approved brief</t>
+    <t xml:space="preserve">Root and dialog-subpath namespaces, direct part exports, declarations, and closed prop unions match the adopted brief</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Native props, refs, composition, and public slots follow the adopted API contract</t>
+    <t xml:space="preserve">Controlled and uncontrolled state, modal policy, dismissal controls, and close-reason detail remain public Atom behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/dialog.test.tsx</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-05</t>
   </si>
   <si>
+    <t xml:space="preserve">Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger preserves native props, ref, stable Brick hooks, and Atom asChild and render composition</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Default recipe and every approved visual option are implemented</t>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal preserves default body, inline disabled, and custom-container composition without copying behavior into Brick</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlay remains a sibling of Content, exposes the semantic scrim, and preserves exact-target and disabled dismissal behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/dialog.spec.ts</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Every public recipe, size, and important state</t>
+    <t xml:space="preserve">Modal semantics, ARIA ownership, focus scope, native props, ref, stable hooks, and sm, md, and lg sizes follow the adopted contract</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Header renders one native visual region for title, description, and optional explicit controls without generated behavior</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Light, dark, and relevant preference modes</t>
+    <t xml:space="preserve">Visible accessible naming and h1 through h6 heading control preserve Atom ARIA relationships</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Optional paragraph content supplies the accessible description without inventing copy or empty relationships</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Token, className, style, slot, and documented part customization</t>
+    <t xml:space="preserve">Body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bounded body scrolling keeps long content readable without moving Header, Footer, or the background page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/dialog.md</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Consumer-selected actions preserve source order, wrap logically, and remain reachable at narrow and keyboard-constrained heights</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close preserves native props, ref, stable Brick hooks, Atom composition, and the closeClick reason</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Public type and declaration fixtures</t>
+    <t xml:space="preserve">Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch remains the public registration boundary for owned third-party portals and adds only stable Brick styling hooks</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-16</t>
   </si>
   <si>
+    <t xml:space="preserve">Compiled CSS uses public Brick classes, component tokens, layers, logical properties, semantic roles, and direction-neutral centering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/dialog/dialog.css</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-17</t>
   </si>
   <si>
+    <t xml:space="preserve">The semantic overlay recipe, border, elevation, spacing, three sizes, and reduced-motion states remain distinct and coherent</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-18</t>
   </si>
   <si>
+    <t xml:space="preserve">The nine-section deterministic workbench uses public Dialog anatomy and Brick Button composition</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Overview, sizes, anatomy, dismissal, nesting, scoped appearance, customization, long content, and RTL scenarios are represented</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-20</t>
   </si>
   <si>
-    <t xml:space="preserve">SSR or server-safe consumer behavior where applicable</t>
+    <t xml:space="preserve">Mobile-first constrained and intentional wide layouts preserve viewport gaps, bounded height, body scrolling, and reachable actions</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Light, dark, scoped appearance, forced colors, and reduced motion retain hierarchy, boundaries, and focus visibility</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Long content, unbroken text, localization, 200 and 400 percent zoom, narrow widths, and RTL remain contained and readable</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-23</t>
   </si>
   <si>
+    <t xml:space="preserve">Public Dialog tokens, stable classes, style, data attributes, and overridable part slots remain local and inspectable</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Stable Dialog route and deterministic selectors support repeatable browser and visual checks</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Vitest and Testing Library cover default DOM, native contracts, composition, sizes, ARIA, state, and namespace identity</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public types, declarations, invalid size and flat-call exclusions, root exports, and dialog-subpath fixtures pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright verifies modal anatomy, focus containment and restoration, dismissal, nested cleanup, RTL, and mobile geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axe reports no automatically detectable violations for the canonical open Dialog state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four deterministic Chromium visual baselines covering light, dark, mobile RTL, and forced colors are reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Dialog release matrix records 30 passing checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered nine-step Dialog manual-test protocol is complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run passes after nested isolation, portalled RTL direction, and direction-neutral centering findings were corrected and retested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Dialog documentation follows the standard template and covers anatomy, behavior, portals, scope, Branch, tokens, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/dialog/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog component changelog and package release notes record the initial contract and post-review corrections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/dialog/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Brick Consumer uses Dialog through public package exports and passes production, interaction, layout, and axe gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Dialog family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core Dialog source, exports, defaults, compatibility, and stale evidence are removed only after dependents are resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlertDialog still imports shared Dialog defaults and legacy structures.</t>
   </si>
   <si>
     <t xml:space="preserve">partial</t>
@@ -1201,23 +1360,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE2E8F0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFEE2E2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF475569"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1327,6 +1470,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE2E8F0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFEDE9FE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1336,6 +1487,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF166534"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF475569"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1493,8 +1652,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DialogEvidence" displayName="DialogEvidence" ref="A8:M34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A8:M34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DialogEvidence" displayName="DialogEvidence" ref="A8:M45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A8:M45"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -1774,14 +1933,14 @@
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">SUM(H8:H10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B10,J8:J10)/SUM(B8:B10),0)</f>
-        <v>0.670588235294118</v>
+        <v>0.96875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,56 +2106,56 @@
         <v>21</v>
       </c>
       <c r="B10" s="8" t="n">
-        <f aca="false">COUNTA(Dialog!A9:A34)</f>
-        <v>26</v>
+        <f aca="false">COUNTA(Dialog!A9:A45)</f>
+        <v>37</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"not started")</f>
-        <v>26</v>
+        <f aca="false">COUNTIF(Dialog!H9:H45,"not started")</f>
+        <v>0</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"partial")</f>
+        <f aca="false">COUNTIF(Dialog!H9:H45,"partial")</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"implemented")</f>
+        <f aca="false">COUNTIF(Dialog!H9:H45,"implemented")</f>
         <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"tested")</f>
+        <f aca="false">COUNTIF(Dialog!H9:H45,"tested")</f>
+        <v>22</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <f aca="false">COUNTIF(Dialog!H9:H45,"verified")</f>
+        <v>14</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <f aca="false">COUNTIF(Dialog!H9:H45,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <f aca="false">COUNTIF(Dialog!H9:H45,"not applicable")</f>
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"verified")</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <f aca="false">COUNTIF(Dialog!H9:H34,"not applicable")</f>
-        <v>0</v>
-      </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">IFERROR(SUM(Dialog!M9:M34)/SUM(Dialog!L9:L34),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(SUM(Dialog!M9:M45)/SUM(Dialog!L9:L45),0)</f>
+        <v>0.972972972972973</v>
       </c>
       <c r="K10" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Dialog!E9:E34,"package",Dialog!M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(Dialog!E9:E45,"package",Dialog!M9:M45,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="L10" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Dialog!E9:E34,"consumer",Dialog!M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(Dialog!E9:E45,"consumer",Dialog!M9:M45,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="M10" s="8" t="str">
-        <f aca="false">IF(COUNTIFS(Dialog!E9:E34,"retirement",Dialog!M9:M34,"&lt;1")=0,"complete","open")</f>
+        <f aca="false">IF(COUNTIFS(Dialog!E9:E45,"retirement",Dialog!M9:M45,"&lt;1")=0,"complete","open")</f>
         <v>open</v>
       </c>
       <c r="N10" s="8" t="str">
         <f aca="false">IF(H10&gt;0,"blocked",IF(AND(J10=1,K10="complete",L10="complete",M10="complete"),"complete",IF(J10=0,"not started","in progress")))</f>
-        <v>not started</v>
+        <v>blocked</v>
       </c>
     </row>
   </sheetData>
@@ -2005,25 +2164,25 @@
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="N8:N10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$N8="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$N8="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$N8="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$N8="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$N8="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$N8="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$N8="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3416,25 +3575,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4688,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
         <v>223</v>
       </c>
@@ -4728,7 +4887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
         <v>226</v>
       </c>
@@ -4768,7 +4927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
         <v>228</v>
       </c>
@@ -4808,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
         <v>230</v>
       </c>
@@ -4848,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
         <v>233</v>
       </c>
@@ -4888,7 +5047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
         <v>236</v>
       </c>
@@ -4928,7 +5087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="26.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
         <v>238</v>
       </c>
@@ -4978,25 +5137,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H41">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5064,7 +5223,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -5121,42 +5280,42 @@
         <v>7</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">COUNTA(A9:A34)</f>
-        <v>26</v>
+        <f aca="false">COUNTA(A9:A45)</f>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">SUM(M9:M34)</f>
-        <v>0</v>
+        <f aca="false">SUM(M9:M45)</f>
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">IFERROR(D4/SUM(L9:L34),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(D4/SUM(L9:L45),0)</f>
+        <v>0.972972972972973</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <f aca="false">COUNTIF(H9:H34,"blocked")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(H9:H45,"blocked")</f>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f aca="false">IF(COUNTIFS(E9:E34,"package",M9:M34,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <f aca="false">IF(COUNTIFS(E9:E45,"package",M9:M45,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="5" t="str">
-        <f aca="false">IF(COUNTIFS(E9:E34,"retirement",M9:M34,"&lt;1")=0,"complete","open")</f>
+        <f aca="false">IF(COUNTIFS(E9:E45,"retirement",M9:M45,"&lt;1")=0,"complete","open")</f>
         <v>open</v>
       </c>
     </row>
@@ -5218,7 +5377,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>246</v>
       </c>
@@ -5237,26 +5396,30 @@
       <c r="F9" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="15" t="s">
+        <v>248</v>
+      </c>
       <c r="H9" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K9" s="15"/>
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="18" t="n">
         <f aca="false">IF(H9="not applicable",IF(K9&lt;&gt;"",1,0),IF(I9="yes",IF(H9="verified",1,0),IF(OR(H9="tested",H9="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>67</v>
@@ -5265,7 +5428,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>61</v>
@@ -5273,35 +5436,39 @@
       <c r="F10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>251</v>
+      </c>
       <c r="H10" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K10" s="15"/>
       <c r="L10" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="18" t="n">
         <f aca="false">IF(H10="not applicable",IF(K10&lt;&gt;"",1,0),IF(I10="yes",IF(H10="verified",1,0),IF(OR(H10="tested",H10="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>61</v>
@@ -5309,395 +5476,439 @@
       <c r="F11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="H11" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K11" s="15"/>
       <c r="L11" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="18" t="n">
         <f aca="false">IF(H11="not applicable",IF(K11&lt;&gt;"",1,0),IF(I11="yes",IF(H11="verified",1,0),IF(OR(H11="tested",H11="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H12" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K12" s="15"/>
       <c r="L12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M12" s="18" t="n">
         <f aca="false">IF(H12="not applicable",IF(K12&lt;&gt;"",1,0),IF(I12="yes",IF(H12="verified",1,0),IF(OR(H12="tested",H12="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>6</v>
+        <v>258</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H13" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="15"/>
+      <c r="J13" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K13" s="15"/>
       <c r="L13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="18" t="n">
         <f aca="false">IF(H13="not applicable",IF(K13&lt;&gt;"",1,0),IF(I13="yes",IF(H13="verified",1,0),IF(OR(H13="tested",H13="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>6</v>
+        <v>261</v>
       </c>
       <c r="D14" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K14" s="15"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="18" t="n">
         <f aca="false">IF(H14="not applicable",IF(K14&lt;&gt;"",1,0),IF(I14="yes",IF(H14="verified",1,0),IF(OR(H14="tested",H14="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>89</v>
+        <v>265</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>266</v>
+      </c>
       <c r="H15" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K15" s="15"/>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M15" s="18" t="n">
         <f aca="false">IF(H15="not applicable",IF(K15&lt;&gt;"",1,0),IF(I15="yes",IF(H15="verified",1,0),IF(OR(H15="tested",H15="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H16" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K16" s="15"/>
       <c r="L16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="18" t="n">
         <f aca="false">IF(H16="not applicable",IF(K16&lt;&gt;"",1,0),IF(I16="yes",IF(H16="verified",1,0),IF(OR(H16="tested",H16="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H17" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K17" s="15"/>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="18" t="n">
         <f aca="false">IF(H17="not applicable",IF(K17&lt;&gt;"",1,0),IF(I17="yes",IF(H17="verified",1,0),IF(OR(H17="tested",H17="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H18" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K18" s="15"/>
       <c r="L18" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="18" t="n">
         <f aca="false">IF(H18="not applicable",IF(K18&lt;&gt;"",1,0),IF(I18="yes",IF(H18="verified",1,0),IF(OR(H18="tested",H18="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H19" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K19" s="15"/>
       <c r="L19" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M19" s="18" t="n">
         <f aca="false">IF(H19="not applicable",IF(K19&lt;&gt;"",1,0),IF(I19="yes",IF(H19="verified",1,0),IF(OR(H19="tested",H19="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>6</v>
+        <v>276</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H20" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="15"/>
+      <c r="J20" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K20" s="15"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="18" t="n">
         <f aca="false">IF(H20="not applicable",IF(K20&lt;&gt;"",1,0),IF(I20="yes",IF(H20="verified",1,0),IF(OR(H20="tested",H20="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H21" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J21" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K21" s="15"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="18" t="n">
         <f aca="false">IF(H21="not applicable",IF(K21&lt;&gt;"",1,0),IF(I21="yes",IF(H21="verified",1,0),IF(OR(H21="tested",H21="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>6</v>
+        <v>282</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>61</v>
@@ -5705,35 +5916,39 @@
       <c r="F22" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H22" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J22" s="15"/>
+      <c r="J22" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K22" s="15"/>
       <c r="L22" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M22" s="18" t="n">
         <f aca="false">IF(H22="not applicable",IF(K22&lt;&gt;"",1,0),IF(I22="yes",IF(H22="verified",1,0),IF(OR(H22="tested",H22="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>6</v>
+        <v>285</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
@@ -5741,251 +5956,279 @@
       <c r="F23" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H23" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J23" s="15"/>
+      <c r="J23" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K23" s="15"/>
       <c r="L23" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M23" s="18" t="n">
         <f aca="false">IF(H23="not applicable",IF(K23&lt;&gt;"",1,0),IF(I23="yes",IF(H23="verified",1,0),IF(OR(H23="tested",H23="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" s="15"/>
+        <v>62</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="H24" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J24" s="15"/>
+      <c r="J24" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K24" s="15"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="18" t="n">
         <f aca="false">IF(H24="not applicable",IF(K24&lt;&gt;"",1,0),IF(I24="yes",IF(H24="verified",1,0),IF(OR(H24="tested",H24="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>116</v>
+        <v>291</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H25" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K25" s="15"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="18" t="n">
         <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>119</v>
+        <v>293</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H26" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="15"/>
+      <c r="J26" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K26" s="15"/>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="18" t="n">
         <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>122</v>
+        <v>295</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>266</v>
+      </c>
       <c r="H27" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K27" s="15"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="18" t="n">
         <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H28" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J28" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K28" s="15"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="18" t="n">
         <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="H29" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J29" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K29" s="15"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="18" t="n">
         <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>132</v>
+        <v>301</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>61</v>
@@ -5993,203 +6236,665 @@
       <c r="F30" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="H30" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J30" s="15"/>
+      <c r="J30" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K30" s="15"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M30" s="18" t="n">
         <f aca="false">IF(H30="not applicable",IF(K30&lt;&gt;"",1,0),IF(I30="yes",IF(H30="verified",1,0),IF(OR(H30="tested",H30="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="15"/>
+      <c r="J31" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K31" s="15"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="18" t="n">
         <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>139</v>
+        <v>305</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G32" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>266</v>
+      </c>
       <c r="H32" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J32" s="15"/>
+      <c r="J32" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K32" s="15"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="18" t="n">
         <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>256</v>
+      </c>
       <c r="H33" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K33" s="15"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="18" t="n">
         <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>148</v>
+        <v>309</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="G34" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="H34" s="15" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="15"/>
+        <v>65</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>46220</v>
+      </c>
       <c r="K34" s="15"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="18" t="n">
         <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K36" s="15"/>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K37" s="15"/>
+      <c r="L37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <f aca="false">IF(H37="not applicable",IF(K37&lt;&gt;"",1,0),IF(I37="yes",IF(H37="verified",1,0),IF(OR(H37="tested",H37="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K38" s="15"/>
+      <c r="L38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <f aca="false">IF(H38="not applicable",IF(K38&lt;&gt;"",1,0),IF(I38="yes",IF(H38="verified",1,0),IF(OR(H38="tested",H38="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K39" s="15"/>
+      <c r="L39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <f aca="false">IF(H39="not applicable",IF(K39&lt;&gt;"",1,0),IF(I39="yes",IF(H39="verified",1,0),IF(OR(H39="tested",H39="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K40" s="15"/>
+      <c r="L40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <f aca="false">IF(H40="not applicable",IF(K40&lt;&gt;"",1,0),IF(I40="yes",IF(H40="verified",1,0),IF(OR(H40="tested",H40="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K41" s="15"/>
+      <c r="L41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <f aca="false">IF(H41="not applicable",IF(K41&lt;&gt;"",1,0),IF(I41="yes",IF(H41="verified",1,0),IF(OR(H41="tested",H41="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K42" s="15"/>
+      <c r="L42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K43" s="15"/>
+      <c r="L43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="18" t="n">
+        <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K44" s="15"/>
+      <c r="L44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18" t="n">
+        <f aca="false">IF(H44="not applicable",IF(K44&lt;&gt;"",1,0),IF(I44="yes",IF(H44="verified",1,0),IF(OR(H44="tested",H44="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="L45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <f aca="false">IF(H45="not applicable",IF(K45&lt;&gt;"",1,0),IF(I45="yes",IF(H45="verified",1,0),IF(OR(H45="tested",H45="verified"),1,0)))</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:M34"/>
+  <autoFilter ref="A8:M45"/>
   <mergeCells count="3">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A6:M6"/>
   </mergeCells>
-  <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+  <conditionalFormatting sqref="H9:H45">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H34" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H45" type="list">
       <formula1>_Lists!$A$1:$A$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I34" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I45" type="list">
       <formula1>_Lists!$B$1:$B$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6226,7 +6931,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
@@ -6234,7 +6939,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6254,7 +6959,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="339">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">Human-review rows resolve only at verified. Other rows resolve at tested or verified. A documented not-applicable row also resolves.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implementation, playground, automated tests, manual evidence, and documentation are complete.</t>
+    <t xml:space="preserve">Implementation, playground, automated tests, manual evidence, and documentation are complete; every tested or verified claim has been sampled against its exact assertion.</t>
   </si>
   <si>
     <t xml:space="preserve">A live consumer uses the finished Brick component and the cutover is verified.</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Editing</t>
   </si>
   <si>
-    <t xml:space="preserve">Use list values, keep evidence links short, record blocker and not-applicable reasons, recalculate, and visually inspect every changed sheet.</t>
+    <t xml:space="preserve">Use list values; classify Atom, Brick adapter, browser, and manual ownership; keep claims assertion-specific; record blocker and not-applicable reasons; recalculate; and visually inspect every changed sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Button Evidence Matrix</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">DIA-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Controlled and uncontrolled state, modal policy, dismissal controls, and close-reason detail remain public Atom behavior</t>
+    <t xml:space="preserve">Atom owns exhaustive controlled and uncontrolled state and modal policy; Brick verifies disabled Root forwarding and representative close-reason preservation</t>
   </si>
   <si>
     <t xml:space="preserve">../test/components/dialog.test.tsx</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">Trigger</t>
   </si>
   <si>
-    <t xml:space="preserve">Trigger preserves native props, ref, stable Brick hooks, and Atom asChild and render composition</t>
+    <t xml:space="preserve">Trigger preserves disabled state, native props, ref, stable Brick hooks, and representative Atom asChild and render composition</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-06</t>
@@ -830,6 +830,9 @@
     <t xml:space="preserve">Portal preserves default body, inline disabled, and custom-container composition without copying behavior into Brick</t>
   </si>
   <si>
+    <t xml:space="preserve">../test/components/dialog.test.tsx + tests/dialog.spec.ts</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIA-07</t>
   </si>
   <si>
@@ -857,7 +860,7 @@
     <t xml:space="preserve">DIA-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Visible accessible naming and h1 through h6 heading control preserve Atom ARIA relationships</t>
+    <t xml:space="preserve">Visible accessible naming, the default h2, and a representative h1 override preserve Atom ARIA relationships and heading forwarding</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-11</t>
@@ -890,7 +893,7 @@
     <t xml:space="preserve">Close</t>
   </si>
   <si>
-    <t xml:space="preserve">Close preserves native props, ref, stable Brick hooks, Atom composition, and the closeClick reason</t>
+    <t xml:space="preserve">Close preserves native props, ref, stable Brick hooks, representative asChild and render composition, and the closeClick reason</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-15</t>
@@ -899,7 +902,7 @@
     <t xml:space="preserve">Branch</t>
   </si>
   <si>
-    <t xml:space="preserve">Branch remains the public registration boundary for owned third-party portals and adds only stable Brick styling hooks</t>
+    <t xml:space="preserve">Branch preserves Atom registration ownership while Brick verifies render composition, native forwarding, ref wiring, and stable styling hooks</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-16</t>
@@ -962,7 +965,7 @@
     <t xml:space="preserve">DIA-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Vitest and Testing Library cover default DOM, native contracts, composition, sizes, ARIA, state, and namespace identity</t>
+    <t xml:space="preserve">Vitest and Testing Library cover default DOM, native contracts, disabled Root, asChild and render composition, portal container, heading override, sizes, ARIA, close reason, and namespace identity</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-26</t>
@@ -974,7 +977,7 @@
     <t xml:space="preserve">DIA-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Playwright verifies modal anatomy, focus containment and restoration, dismissal, nested cleanup, RTL, and mobile geometry</t>
+    <t xml:space="preserve">Playwright verifies modal anatomy, focus containment and restoration, dismissal, disabled Trigger and Overlay paths, nested cleanup, RTL, and mobile geometry</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-28</t>
@@ -992,7 +995,7 @@
     <t xml:space="preserve">DIA-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Dialog release matrix records 30 passing checks</t>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Dialog release matrix records 40 passing Dialog checks</t>
   </si>
   <si>
     <t xml:space="preserve">DIA-31</t>
@@ -1013,7 +1016,7 @@
     <t xml:space="preserve">DIA-34</t>
   </si>
   <si>
-    <t xml:space="preserve">Public Dialog documentation follows the standard template and covers anatomy, behavior, portals, scope, Branch, tokens, and customization</t>
+    <t xml:space="preserve">Public Dialog documentation follows the standard template and covers use boundaries, anatomy, API, states, accessibility, responsive behavior, portals, Branch, tokens, composition, and customization</t>
   </si>
   <si>
     <t xml:space="preserve">../docs/components/dialog/README.md</t>
@@ -1022,7 +1025,7 @@
     <t xml:space="preserve">DIA-35</t>
   </si>
   <si>
-    <t xml:space="preserve">Dialog component changelog and package release notes record the initial contract and post-review corrections</t>
+    <t xml:space="preserve">Dialog component changelog records the initial contract and post-review evidence corrections</t>
   </si>
   <si>
     <t xml:space="preserve">../docs/components/dialog/CHANGELOG.md</t>
@@ -1605,6 +1608,7 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1626,6 +1630,7 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1648,6 +1653,7 @@
     <tableColumn id="13" name="Retirement gate"/>
     <tableColumn id="14" name="Status"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1669,6 +1675,7 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1679,6 +1686,7 @@
     <tableColumn id="1" name="Topic"/>
     <tableColumn id="2" name="Rule"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -5526,7 +5534,7 @@
         <v>65</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="18" t="n">
@@ -5566,7 +5574,7 @@
         <v>65</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="18" t="n">
@@ -5597,7 +5605,7 @@
         <v>109</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>64</v>
@@ -5606,7 +5614,7 @@
         <v>65</v>
       </c>
       <c r="J14" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="18" t="n">
@@ -5619,16 +5627,16 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>61</v>
@@ -5637,7 +5645,7 @@
         <v>109</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>64</v>
@@ -5646,7 +5654,7 @@
         <v>65</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="18" t="n">
@@ -5659,7 +5667,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>39</v>
@@ -5668,7 +5676,7 @@
         <v>186</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>61</v>
@@ -5699,7 +5707,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>39</v>
@@ -5708,7 +5716,7 @@
         <v>172</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>61</v>
@@ -5739,7 +5747,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>39</v>
@@ -5748,7 +5756,7 @@
         <v>176</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>61</v>
@@ -5766,7 +5774,7 @@
         <v>65</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K18" s="15"/>
       <c r="L18" s="18" t="n">
@@ -5779,7 +5787,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>39</v>
@@ -5788,7 +5796,7 @@
         <v>179</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>61</v>
@@ -5819,16 +5827,16 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>61</v>
@@ -5837,7 +5845,7 @@
         <v>130</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>71</v>
@@ -5859,7 +5867,7 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>39</v>
@@ -5868,7 +5876,7 @@
         <v>189</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>61</v>
@@ -5877,7 +5885,7 @@
         <v>130</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>71</v>
@@ -5899,16 +5907,16 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>61</v>
@@ -5926,7 +5934,7 @@
         <v>65</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="18" t="n">
@@ -5939,16 +5947,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>61</v>
@@ -5966,7 +5974,7 @@
         <v>65</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="18" t="n">
@@ -5979,7 +5987,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>81</v>
@@ -5988,7 +5996,7 @@
         <v>165</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>61</v>
@@ -5997,7 +6005,7 @@
         <v>62</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>64</v>
@@ -6019,7 +6027,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>81</v>
@@ -6028,7 +6036,7 @@
         <v>186</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>61</v>
@@ -6037,7 +6045,7 @@
         <v>130</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>71</v>
@@ -6059,7 +6067,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>88</v>
@@ -6068,7 +6076,7 @@
         <v>165</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>61</v>
@@ -6077,7 +6085,7 @@
         <v>90</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>71</v>
@@ -6099,7 +6107,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>88</v>
@@ -6108,7 +6116,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>61</v>
@@ -6117,7 +6125,7 @@
         <v>90</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>71</v>
@@ -6139,7 +6147,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>88</v>
@@ -6148,7 +6156,7 @@
         <v>186</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>61</v>
@@ -6157,7 +6165,7 @@
         <v>130</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>71</v>
@@ -6179,7 +6187,7 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>88</v>
@@ -6188,7 +6196,7 @@
         <v>165</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>61</v>
@@ -6219,7 +6227,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>88</v>
@@ -6228,7 +6236,7 @@
         <v>165</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>61</v>
@@ -6237,7 +6245,7 @@
         <v>130</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>71</v>
@@ -6259,7 +6267,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>88</v>
@@ -6268,7 +6276,7 @@
         <v>165</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>61</v>
@@ -6277,7 +6285,7 @@
         <v>130</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>71</v>
@@ -6299,7 +6307,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>88</v>
@@ -6308,7 +6316,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>61</v>
@@ -6317,7 +6325,7 @@
         <v>90</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>64</v>
@@ -6339,7 +6347,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>107</v>
@@ -6348,7 +6356,7 @@
         <v>165</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>61</v>
@@ -6366,7 +6374,7 @@
         <v>65</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K33" s="15"/>
       <c r="L33" s="18" t="n">
@@ -6379,7 +6387,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>107</v>
@@ -6388,7 +6396,7 @@
         <v>155</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>61</v>
@@ -6419,7 +6427,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>107</v>
@@ -6428,7 +6436,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>61</v>
@@ -6437,7 +6445,7 @@
         <v>109</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>64</v>
@@ -6446,7 +6454,7 @@
         <v>65</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="18" t="n">
@@ -6459,7 +6467,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>107</v>
@@ -6468,7 +6476,7 @@
         <v>186</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>61</v>
@@ -6477,7 +6485,7 @@
         <v>109</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>64</v>
@@ -6499,7 +6507,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>107</v>
@@ -6508,7 +6516,7 @@
         <v>165</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>61</v>
@@ -6539,7 +6547,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>107</v>
@@ -6548,7 +6556,7 @@
         <v>165</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>61</v>
@@ -6566,7 +6574,7 @@
         <v>65</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="18" t="n">
@@ -6579,7 +6587,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>107</v>
@@ -6619,7 +6627,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>128</v>
@@ -6628,7 +6636,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>61</v>
@@ -6637,7 +6645,7 @@
         <v>130</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>64</v>
@@ -6659,7 +6667,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>128</v>
@@ -6668,7 +6676,7 @@
         <v>165</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>61</v>
@@ -6677,7 +6685,7 @@
         <v>130</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>71</v>
@@ -6699,7 +6707,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>134</v>
@@ -6708,7 +6716,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>61</v>
@@ -6717,7 +6725,7 @@
         <v>136</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>71</v>
@@ -6726,7 +6734,7 @@
         <v>72</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
@@ -6739,7 +6747,7 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>134</v>
@@ -6748,7 +6756,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>61</v>
@@ -6757,7 +6765,7 @@
         <v>136</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>64</v>
@@ -6766,7 +6774,7 @@
         <v>65</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="18" t="n">
@@ -6779,7 +6787,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>142</v>
@@ -6788,7 +6796,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>144</v>
@@ -6819,16 +6827,16 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>149</v>
@@ -6849,7 +6857,7 @@
         <v>46220</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1</v>
@@ -6931,7 +6939,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
@@ -6939,7 +6947,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6959,7 +6967,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -14,8 +14,11 @@
     <sheet name="Card" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Dialog" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="_Lists" sheetId="6" state="hidden" r:id="rId8"/>
+    <sheet name="AlertDialog" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">AlertDialog!$A$1:$M$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">AlertDialog!$A$8:$M$47</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Button!$A$1:$M$34</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Button!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Button!$A$8:$M$34</definedName>
@@ -25,7 +28,7 @@
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dialog!$A$1:$M$45</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Dialog!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Dialog!$A$8:$M$45</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Index!$A$1:$N$10</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Index!$A$1:$N$11</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$B$18</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Instructions!$A$4:$B$18</definedName>
   </definedNames>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="429">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -107,6 +110,9 @@
     <t xml:space="preserve">Dialog</t>
   </si>
   <si>
+    <t xml:space="preserve">AlertDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brick Component Coverage</t>
   </si>
   <si>
@@ -1056,6 +1062,273 @@
   </si>
   <si>
     <t xml:space="preserve">not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlertDialog Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted urgent-decision compound, its twelve public parts, package proof, consumer cutover, and dependency-led legacy retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation directly composes public Atom 0.3.2 AlertDialog behavior without Core or local headless wrappers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/alert-dialog/AlertDialog.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adopted capability audit covers alert semantics, required message, safe Cancel focus, modal layers, portals, isolation, scrolling, presence, and dismissal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/alert-dialog-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and alert-dialog-subpath namespaces, direct part exports, declarations, and closed prop unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atom owns controlled and uncontrolled state, Escape policy, disabled state, close reasons, and modal ownership; Brick forwards the public contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/alert-dialog.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlay remains a sibling of Content, exposes the semantic scrim, never dismisses, and exposes no redundant disabled prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/alert-dialog.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alertdialog semantics, ARIA ownership, focus scope, native props, ref, stable hooks, and sm/md sizes follow the adopted contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header renders one native visual region for Title and required alert message without generated behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description supplies the required alert message and generated accessible description without inventing copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional supplemental detail uses a bounded scroll region while the alert message and responses remain reachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/alert-dialog.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner manual review pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer-selected responses preserve source order, wrap logically, and remain reachable at narrow and keyboard-constrained heights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel preserves native props, ref, stable hooks, composition, cancel close reason, safe initial focus, and restoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/alert-dialog.test.tsx + tests/alert-dialog.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action preserves native props, ref, stable hooks, composition, action close reason, and preventDefault closure control without owning application work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled CSS uses public Brick classes, component tokens, layers, logical properties, semantic colors, and direction-neutral centering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/alert-dialog/alert-dialog.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlay, surface, border, elevation, spacing, two sizes, focus, and reduced-motion treatment are visually coherent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The nine-section deterministic workbench uses public AlertDialog anatomy and explicit Brick Button composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../playground/src/main.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview, sizes, anatomy, outcomes, disabled and pending state, nesting, scoped appearance, customization, long content, and RTL are represented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-first constrained and intentional wide layouts preserve viewport gaps, bounded height, Body scrolling, and reachable responses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public tokens, stable classes, style, data attributes, and overridable part slots remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable AlertDialog route and deterministic selectors support repeatable browser and visual checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest covers default DOM, ARIA, native contracts, disabled native and composed Triggers, sizes, close reasons, autofocus, composition, refs, portal container, heading override, prevention, and namespace identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public types, declarations, invalid size, callable API, backdrop prop, and Overlay-disabled exclusions plus root/subpath fixtures pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright verifies alert anatomy, Cancel focus, focus restoration, explicit outcomes, Escape policy, and blocked backdrop dismissal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger and Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright verifies disabled pointer/keyboard opening and prevented Action closure with application-owned pending feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nested AlertDialog cleanup returns focus and control to its parent Dialog and leaves the application operable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axe reports no automatically detectable violations for the canonical open AlertDialog state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone AlertDialog release matrix passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package boundary, tarball, and clean React 18 and React 19 consumer verification include AlertDialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered nine-step AlertDialog manual-test protocol exists with assertion-specific owner checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run passes visual, keyboard, touch, nesting, real-phone, preference, reflow, RTL, screen-reader, and customization review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public AlertDialog guide covers use boundaries, anatomy, API, required message, focus, dismissal, async prevention, nesting, responsiveness, tokens, composition, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/alert-dialog/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlertDialog component and package changelogs record the initial contract and evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/alert-dialog/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Brick Consumer uses the public AlertDialog subpath and passes production, boundary, interaction, layout, desktop/mobile, and axe gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALD-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy AlertDialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core AlertDialog source and feedback export are removed after the package and consumer gates pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package owner-review gate remains open; legacy source is retained until it passes.</t>
   </si>
 </sst>
 </file>
@@ -1139,6 +1412,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF172033"/>
@@ -1159,13 +1439,6 @@
       <color rgb="FF526072"/>
       <name val="Aptos"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1279,32 +1552,32 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1328,7 +1601,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="23">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1510,6 +1783,22 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92400E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1590,6 +1879,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ButtonEvidence" displayName="ButtonEvidence" ref="A8:M34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A8:M34"/>
@@ -1608,7 +1901,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1630,7 +1922,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1653,7 +1944,6 @@
     <tableColumn id="13" name="Retirement gate"/>
     <tableColumn id="14" name="Status"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1675,7 +1965,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1686,7 +1975,6 @@
     <tableColumn id="1" name="Topic"/>
     <tableColumn id="2" name="Rule"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1870,7 +2158,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -1926,29 +2214,29 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">COUNTA(A8:A10)</f>
-        <v>3</v>
+        <f aca="false">COUNTA(A8:A11)</f>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">COUNTIF(M8:M10,"complete")</f>
+        <f aca="false">COUNTIF(N8:N11,"complete")</f>
         <v>0</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="5" t="n">
-        <f aca="false">SUM(H8:H10)</f>
-        <v>2</v>
+        <f aca="false">SUM(H8:H11)</f>
+        <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(B8:B10,J8:J10)/SUM(B8:B10),0)</f>
-        <v>0.96875</v>
+        <f aca="false">IFERROR(SUMPRODUCT(B8:B11,J8:J11)/SUM(B8:B11),0)</f>
+        <v>0.918518518518519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2163,6 +2451,63 @@
       </c>
       <c r="N10" s="8" t="str">
         <f aca="false">IF(H10&gt;0,"blocked",IF(AND(J10=1,K10="complete",L10="complete",M10="complete"),"complete",IF(J10=0,"not started","in progress")))</f>
+        <v>blocked</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <f aca="false">COUNTA(AlertDialog!A9:A47)</f>
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"not started")</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"partial")</f>
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"implemented")</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"tested")</f>
+        <v>29</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"verified")</f>
+        <v>2</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <f aca="false">COUNTIF(AlertDialog!H9:H47,"not applicable")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <f aca="false">IFERROR(SUM(AlertDialog!M9:M47)/SUM(AlertDialog!L9:L47),0)</f>
+        <v>0.794871794871795</v>
+      </c>
+      <c r="K11" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(AlertDialog!E9:E47,"package",AlertDialog!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="L11" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(AlertDialog!E9:E47,"consumer",AlertDialog!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
+      </c>
+      <c r="M11" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(AlertDialog!E9:E47,"retirement",AlertDialog!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <f aca="false">IF(H11&gt;0,"blocked",IF(AND(J11=1,K11="complete",L11="complete",M11="complete"),"complete",IF(J11=0,"not started","in progress")))</f>
         <v>blocked</v>
       </c>
     </row>
@@ -2198,6 +2543,7 @@
     <hyperlink ref="A8" r:id="rId1" location="'Button'!A1" display="Button"/>
     <hyperlink ref="A9" r:id="rId2" location="'Card'!A1" display="Card"/>
     <hyperlink ref="A10" r:id="rId3" location="'Dialog'!A1" display="Dialog"/>
+    <hyperlink ref="A11" r:id="rId4" location="'AlertDialog'!A1" display="AlertDialog"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2207,7 +2553,7 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2226,7 +2572,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2234,7 +2580,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2242,122 +2588,122 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="B5" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>28</v>
+      <c r="B6" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>29</v>
+      <c r="B7" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>30</v>
+      <c r="B8" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>31</v>
+      <c r="B9" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>32</v>
+      <c r="B10" s="14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
+      <c r="B11" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>34</v>
+      <c r="B12" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>35</v>
+      <c r="B13" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>36</v>
+      <c r="B14" s="14" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>37</v>
+      <c r="B15" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>38</v>
+      <c r="B16" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="11" t="s">
         <v>40</v>
       </c>
+      <c r="B17" s="12" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="13" t="s">
+      <c r="A18" s="13" t="s">
         <v>42</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2751,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2422,7 +2768,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2446,7 +2792,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M34)</f>
@@ -2482,95 +2828,95 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="E9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="G9" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K9" s="15"/>
+      <c r="K9" s="16"/>
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
@@ -2580,37 +2926,37 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="B10" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="E10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="G10" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="16"/>
       <c r="L10" s="18" t="n">
         <v>1</v>
       </c>
@@ -2620,37 +2966,37 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="E11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="15" t="s">
+      <c r="G11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K11" s="15"/>
+      <c r="K11" s="16"/>
       <c r="L11" s="18" t="n">
         <v>1</v>
       </c>
@@ -2660,37 +3006,37 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="E12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J12" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="16"/>
       <c r="L12" s="18" t="n">
         <v>1</v>
       </c>
@@ -2700,37 +3046,37 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="E13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="16"/>
       <c r="L13" s="18" t="n">
         <v>1</v>
       </c>
@@ -2740,37 +3086,37 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="A14" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="16"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
@@ -2780,37 +3126,37 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="E15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="G15" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K15" s="15"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
@@ -2820,37 +3166,37 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="H16" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J16" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="18" t="n">
         <v>1</v>
       </c>
@@ -2860,37 +3206,37 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="16" t="s">
+      <c r="D17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="G17" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
@@ -2900,37 +3246,37 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="A18" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="16" t="s">
+      <c r="D18" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="E18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K18" s="15"/>
+      <c r="K18" s="16"/>
       <c r="L18" s="18" t="n">
         <v>1</v>
       </c>
@@ -2940,37 +3286,37 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="16" t="s">
+      <c r="D19" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="G19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K19" s="15"/>
+      <c r="K19" s="16"/>
       <c r="L19" s="18" t="n">
         <v>1</v>
       </c>
@@ -2980,37 +3326,37 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="A20" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="16" t="s">
+      <c r="D20" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="G20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="16"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
@@ -3020,37 +3366,37 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="A21" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="16" t="s">
+      <c r="D21" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="E21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K21" s="15"/>
+      <c r="K21" s="16"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
@@ -3060,37 +3406,37 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="15" t="s">
+      <c r="D22" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="15" t="s">
+      <c r="E22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="18" t="n">
         <v>1</v>
       </c>
@@ -3100,37 +3446,37 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="15" t="s">
+      <c r="G23" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K23" s="15"/>
+      <c r="K23" s="16"/>
       <c r="L23" s="18" t="n">
         <v>1</v>
       </c>
@@ -3140,37 +3486,37 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="15" t="s">
+      <c r="A24" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="15" t="s">
+      <c r="D24" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J24" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
@@ -3180,37 +3526,37 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="15" t="s">
+      <c r="A25" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="H25" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="15" t="s">
+      <c r="E25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
@@ -3220,37 +3566,37 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="A26" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="15" t="s">
+      <c r="D26" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H26" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="15" t="s">
+      <c r="E26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>46219</v>
       </c>
-      <c r="K26" s="15"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
@@ -3260,37 +3606,37 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="A27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="16" t="s">
+      <c r="D27" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="H27" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="15" t="s">
+      <c r="E27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K27" s="15"/>
+      <c r="K27" s="16"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
@@ -3300,37 +3646,37 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="A28" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" s="16" t="s">
+      <c r="D28" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="H28" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="15" t="s">
+      <c r="E28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J28" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K28" s="15"/>
+      <c r="K28" s="16"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
@@ -3340,37 +3686,37 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="15" t="s">
+      <c r="D29" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G29" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="15" t="s">
+      <c r="E29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J29" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K29" s="15"/>
+      <c r="K29" s="16"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
@@ -3380,37 +3726,37 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="15" t="s">
+      <c r="G30" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>46219</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="16"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
@@ -3420,37 +3766,37 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="15" t="s">
+      <c r="D31" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="E31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I31" s="15" t="s">
+      <c r="G31" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J31" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K31" s="15"/>
+      <c r="K31" s="16"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
@@ -3460,37 +3806,37 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="15" t="s">
+      <c r="A32" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G32" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="H32" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="15" t="s">
+      <c r="E32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>46219</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
@@ -3500,37 +3846,37 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="D33" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" s="15" t="s">
+      <c r="E33" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="H33" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I33" s="15" t="s">
+      <c r="F33" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H33" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>46219</v>
       </c>
-      <c r="K33" s="15"/>
+      <c r="K33" s="16"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
@@ -3540,33 +3886,33 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="B34" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I34" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
@@ -3681,7 +4027,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3698,7 +4044,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3722,7 +4068,7 @@
         <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M41)</f>
@@ -3758,95 +4104,95 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="E9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K9" s="15"/>
+      <c r="K9" s="16"/>
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
@@ -3856,37 +4202,37 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="E10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="16"/>
       <c r="L10" s="18" t="n">
         <v>1</v>
       </c>
@@ -3896,37 +4242,37 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="15" t="s">
+      <c r="B11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="15" t="s">
+      <c r="E11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K11" s="15"/>
+      <c r="K11" s="16"/>
       <c r="L11" s="18" t="n">
         <v>1</v>
       </c>
@@ -3936,37 +4282,37 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="B12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="E12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J12" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="16"/>
       <c r="L12" s="18" t="n">
         <v>1</v>
       </c>
@@ -3976,37 +4322,37 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="16"/>
       <c r="L13" s="18" t="n">
         <v>1</v>
       </c>
@@ -4016,37 +4362,37 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="B14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="16"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
@@ -4056,37 +4402,37 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="B15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="D15" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K15" s="15"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
@@ -4096,37 +4442,37 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="B16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="D16" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J16" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="18" t="n">
         <v>1</v>
       </c>
@@ -4136,37 +4482,37 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="B17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="E17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
@@ -4176,37 +4522,37 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="B18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="D18" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K18" s="15"/>
+      <c r="K18" s="16"/>
       <c r="L18" s="18" t="n">
         <v>1</v>
       </c>
@@ -4216,37 +4562,37 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="B19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="D19" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K19" s="15"/>
+      <c r="K19" s="16"/>
       <c r="L19" s="18" t="n">
         <v>1</v>
       </c>
@@ -4256,37 +4602,37 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="B20" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H20" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="E20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="16"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
@@ -4296,37 +4642,37 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="B21" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K21" s="15"/>
+      <c r="K21" s="16"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
@@ -4336,37 +4682,37 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="15" t="s">
+      <c r="B22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="18" t="n">
         <v>1</v>
       </c>
@@ -4376,37 +4722,37 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="15" t="s">
+      <c r="B23" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K23" s="15"/>
+      <c r="K23" s="16"/>
       <c r="L23" s="18" t="n">
         <v>1</v>
       </c>
@@ -4416,37 +4762,37 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="15" t="s">
+      <c r="B24" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J24" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
@@ -4456,37 +4802,37 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="15" t="s">
+      <c r="B25" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
@@ -4496,37 +4842,37 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="15" t="s">
+      <c r="B26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J26" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K26" s="15"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
@@ -4536,37 +4882,37 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" s="15" t="s">
+      <c r="B27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K27" s="15"/>
+      <c r="K27" s="16"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
@@ -4576,37 +4922,37 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="A28" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="15" t="s">
+      <c r="D28" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J28" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K28" s="15"/>
+      <c r="K28" s="16"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
@@ -4616,37 +4962,37 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="15" t="s">
+      <c r="B29" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J29" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K29" s="15"/>
+      <c r="K29" s="16"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
@@ -4656,37 +5002,37 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="15" t="s">
+      <c r="B30" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J30" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="16"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
@@ -4696,37 +5042,37 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="15" t="s">
+      <c r="B31" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J31" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K31" s="15"/>
+      <c r="K31" s="16"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
@@ -4736,37 +5082,37 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="15" t="s">
+      <c r="B32" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H32" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
@@ -4776,37 +5122,37 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I33" s="15" t="s">
+      <c r="B33" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J33" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K33" s="15"/>
+      <c r="K33" s="16"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
@@ -4816,37 +5162,37 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G34" s="15" t="s">
+      <c r="B34" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="H34" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="15" t="s">
+      <c r="E34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="H34" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J34" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K34" s="15"/>
+      <c r="K34" s="16"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
@@ -4856,37 +5202,37 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="A35" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="15" t="s">
+      <c r="D35" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H35" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="15" t="s">
+      <c r="E35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="H35" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J35" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K35" s="15"/>
+      <c r="K35" s="16"/>
       <c r="L35" s="18" t="n">
         <v>1</v>
       </c>
@@ -4896,37 +5242,37 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="A36" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="15" t="s">
+      <c r="D36" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J36" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K36" s="15"/>
+      <c r="K36" s="16"/>
       <c r="L36" s="18" t="n">
         <v>1</v>
       </c>
@@ -4936,37 +5282,37 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="B37" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J37" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K37" s="15"/>
+      <c r="K37" s="16"/>
       <c r="L37" s="18" t="n">
         <v>1</v>
       </c>
@@ -4976,37 +5322,37 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="A38" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G38" s="15" t="s">
+      <c r="D38" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="H38" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="15" t="s">
+      <c r="E38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="H38" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J38" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K38" s="15"/>
+      <c r="K38" s="16"/>
       <c r="L38" s="18" t="n">
         <v>1</v>
       </c>
@@ -5016,37 +5362,37 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="A39" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G39" s="15" t="s">
+      <c r="D39" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="H39" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="15" t="s">
+      <c r="E39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J39" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K39" s="15"/>
+      <c r="K39" s="16"/>
       <c r="L39" s="18" t="n">
         <v>1</v>
       </c>
@@ -5056,37 +5402,37 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="A40" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G40" s="15" t="s">
+      <c r="D40" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="H40" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I40" s="15" t="s">
+      <c r="F40" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J40" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K40" s="15"/>
+      <c r="K40" s="16"/>
       <c r="L40" s="18" t="n">
         <v>1</v>
       </c>
@@ -5096,38 +5442,38 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="B41" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" s="15" t="s">
+      <c r="D41" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="H41" s="15" t="s">
+      <c r="F41" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G41" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="I41" s="15" t="s">
-        <v>72</v>
+      <c r="H41" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J41" s="17" t="n">
         <v>46220</v>
       </c>
-      <c r="K41" s="15" t="s">
-        <v>243</v>
+      <c r="K41" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>1</v>
@@ -5251,7 +5597,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5268,7 +5614,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5292,7 +5638,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M45)</f>
@@ -5328,95 +5674,95 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="E9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K9" s="15"/>
+      <c r="K9" s="16"/>
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
@@ -5426,37 +5772,37 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="E10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="16"/>
       <c r="L10" s="18" t="n">
         <v>1</v>
       </c>
@@ -5466,37 +5812,37 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="15" t="s">
+      <c r="B11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K11" s="15"/>
+      <c r="K11" s="16"/>
       <c r="L11" s="18" t="n">
         <v>1</v>
       </c>
@@ -5506,37 +5852,37 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="B12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="E12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J12" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="16"/>
       <c r="L12" s="18" t="n">
         <v>1</v>
       </c>
@@ -5546,37 +5892,37 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="16"/>
       <c r="L13" s="18" t="n">
         <v>1</v>
       </c>
@@ -5586,37 +5932,37 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="B14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J14" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="16"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
@@ -5626,37 +5972,37 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="B15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="H15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="E15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K15" s="15"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
@@ -5666,37 +6012,37 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="B16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H16" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J16" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="18" t="n">
         <v>1</v>
       </c>
@@ -5706,37 +6052,37 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="B17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J17" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
@@ -5746,37 +6092,37 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="B18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J18" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K18" s="15"/>
+      <c r="K18" s="16"/>
       <c r="L18" s="18" t="n">
         <v>1</v>
       </c>
@@ -5786,37 +6132,37 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="B19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H19" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K19" s="15"/>
+      <c r="K19" s="16"/>
       <c r="L19" s="18" t="n">
         <v>1</v>
       </c>
@@ -5826,37 +6172,37 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="B20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="D20" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="H20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="E20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J20" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="16"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
@@ -5866,37 +6212,37 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="H21" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J21" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K21" s="15"/>
+      <c r="K21" s="16"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
@@ -5906,37 +6252,37 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="B22" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="15" t="s">
+      <c r="D22" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J22" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="18" t="n">
         <v>1</v>
       </c>
@@ -5946,37 +6292,37 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="B23" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="15" t="s">
+      <c r="D23" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J23" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K23" s="15"/>
+      <c r="K23" s="16"/>
       <c r="L23" s="18" t="n">
         <v>1</v>
       </c>
@@ -5986,37 +6332,37 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="15" t="s">
+      <c r="B24" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="15" t="s">
+      <c r="E24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J24" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
@@ -6026,37 +6372,37 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="15" t="s">
+      <c r="B25" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J25" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
@@ -6066,37 +6412,37 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="15" t="s">
+      <c r="B26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K26" s="15"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
@@ -6106,37 +6452,37 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="A27" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" s="15" t="s">
+      <c r="D27" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J27" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K27" s="15"/>
+      <c r="K27" s="16"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
@@ -6146,37 +6492,37 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" s="15" t="s">
+      <c r="B28" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H28" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J28" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K28" s="15"/>
+      <c r="K28" s="16"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
@@ -6186,37 +6532,37 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="15" t="s">
+      <c r="B29" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J29" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K29" s="15"/>
+      <c r="K29" s="16"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
@@ -6226,37 +6572,37 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="15" t="s">
+      <c r="B30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H30" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="16"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
@@ -6266,37 +6612,37 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I31" s="15" t="s">
+      <c r="B31" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J31" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K31" s="15"/>
+      <c r="K31" s="16"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
@@ -6306,37 +6652,37 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="15" t="s">
+      <c r="A32" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="15" t="s">
+      <c r="D32" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H32" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J32" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
@@ -6346,37 +6692,37 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="15" t="s">
+      <c r="B33" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H33" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K33" s="15"/>
+      <c r="K33" s="16"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
@@ -6386,37 +6732,37 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="15" t="s">
+      <c r="B34" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K34" s="15"/>
+      <c r="K34" s="16"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
@@ -6426,37 +6772,37 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="A35" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="15" t="s">
+      <c r="D35" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H35" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J35" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K35" s="15"/>
+      <c r="K35" s="16"/>
       <c r="L35" s="18" t="n">
         <v>1</v>
       </c>
@@ -6466,37 +6812,37 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="E36" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="15" t="s">
+      <c r="B36" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H36" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K36" s="15"/>
+      <c r="K36" s="16"/>
       <c r="L36" s="18" t="n">
         <v>1</v>
       </c>
@@ -6506,37 +6852,37 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="B37" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K37" s="15"/>
+      <c r="K37" s="16"/>
       <c r="L37" s="18" t="n">
         <v>1</v>
       </c>
@@ -6546,37 +6892,37 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="E38" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I38" s="15" t="s">
+      <c r="B38" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="H38" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K38" s="15"/>
+      <c r="K38" s="16"/>
       <c r="L38" s="18" t="n">
         <v>1</v>
       </c>
@@ -6586,37 +6932,37 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="A39" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="15" t="s">
+      <c r="D39" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="H39" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J39" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K39" s="15"/>
+      <c r="K39" s="16"/>
       <c r="L39" s="18" t="n">
         <v>1</v>
       </c>
@@ -6626,37 +6972,37 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="A40" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="15" t="s">
+      <c r="D40" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H40" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J40" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K40" s="15"/>
+      <c r="K40" s="16"/>
       <c r="L40" s="18" t="n">
         <v>1</v>
       </c>
@@ -6666,37 +7012,37 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="15" t="s">
+      <c r="B41" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="H41" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J41" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K41" s="15"/>
+      <c r="K41" s="16"/>
       <c r="L41" s="18" t="n">
         <v>1</v>
       </c>
@@ -6706,37 +7052,37 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="15" t="s">
+      <c r="A42" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="15" t="s">
+      <c r="D42" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="H42" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="15" t="s">
+      <c r="E42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H42" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J42" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K42" s="15"/>
+      <c r="K42" s="16"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
@@ -6746,37 +7092,37 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="A43" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G43" s="15" t="s">
+      <c r="D43" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="H43" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I43" s="15" t="s">
+      <c r="E43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="H43" s="16" t="s">
         <v>65</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="J43" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K43" s="15"/>
+      <c r="K43" s="16"/>
       <c r="L43" s="18" t="n">
         <v>1</v>
       </c>
@@ -6786,37 +7132,37 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="15" t="s">
+      <c r="A44" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G44" s="15" t="s">
+      <c r="D44" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="H44" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="15" t="s">
+      <c r="F44" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H44" s="16" t="s">
         <v>72</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J44" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K44" s="15"/>
+      <c r="K44" s="16"/>
       <c r="L44" s="18" t="n">
         <v>1</v>
       </c>
@@ -6826,38 +7172,38 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" s="15" t="s">
+      <c r="A45" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="B45" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="E45" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="F45" s="15" t="s">
+      <c r="D45" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E45" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G45" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="H45" s="15" t="s">
+      <c r="F45" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="I45" s="15" t="s">
-        <v>72</v>
+      <c r="H45" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="J45" s="19" t="n">
         <v>46220</v>
       </c>
-      <c r="K45" s="15" t="s">
-        <v>335</v>
+      <c r="K45" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1</v>
@@ -6931,43 +7277,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -6979,4 +7325,1815 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <f aca="false">COUNTA(A9:A47)</f>
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <f aca="false">SUM(M9:M47)</f>
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
+        <v>0.794871794871795</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <f aca="false">COUNTIF(H9:H47,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="5" t="str">
+        <f aca="false">IF(COUNTIFS(E9:E47,"retirement",M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="18" t="n">
+        <f aca="false">IF(H9="not applicable",IF(K9&lt;&gt;"",1,0),IF(I9="yes",IF(H9="verified",1,0),IF(OR(H9="tested",H9="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K10" s="16"/>
+      <c r="L10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <f aca="false">IF(H10="not applicable",IF(K10&lt;&gt;"",1,0),IF(I10="yes",IF(H10="verified",1,0),IF(OR(H10="tested",H10="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <f aca="false">IF(H11="not applicable",IF(K11&lt;&gt;"",1,0),IF(I11="yes",IF(H11="verified",1,0),IF(OR(H11="tested",H11="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <f aca="false">IF(H12="not applicable",IF(K12&lt;&gt;"",1,0),IF(I12="yes",IF(H12="verified",1,0),IF(OR(H12="tested",H12="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <f aca="false">IF(H13="not applicable",IF(K13&lt;&gt;"",1,0),IF(I13="yes",IF(H13="verified",1,0),IF(OR(H13="tested",H13="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <f aca="false">IF(H14="not applicable",IF(K14&lt;&gt;"",1,0),IF(I14="yes",IF(H14="verified",1,0),IF(OR(H14="tested",H14="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <f aca="false">IF(H15="not applicable",IF(K15&lt;&gt;"",1,0),IF(I15="yes",IF(H15="verified",1,0),IF(OR(H15="tested",H15="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">IF(H16="not applicable",IF(K16&lt;&gt;"",1,0),IF(I16="yes",IF(H16="verified",1,0),IF(OR(H16="tested",H16="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="18" t="n">
+        <f aca="false">IF(H17="not applicable",IF(K17&lt;&gt;"",1,0),IF(I17="yes",IF(H17="verified",1,0),IF(OR(H17="tested",H17="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="18" t="n">
+        <f aca="false">IF(H18="not applicable",IF(K18&lt;&gt;"",1,0),IF(I18="yes",IF(H18="verified",1,0),IF(OR(H18="tested",H18="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <f aca="false">IF(H19="not applicable",IF(K19&lt;&gt;"",1,0),IF(I19="yes",IF(H19="verified",1,0),IF(OR(H19="tested",H19="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <f aca="false">IF(H20="not applicable",IF(K20&lt;&gt;"",1,0),IF(I20="yes",IF(H20="verified",1,0),IF(OR(H20="tested",H20="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <f aca="false">IF(H21="not applicable",IF(K21&lt;&gt;"",1,0),IF(I21="yes",IF(H21="verified",1,0),IF(OR(H21="tested",H21="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <f aca="false">IF(H22="not applicable",IF(K22&lt;&gt;"",1,0),IF(I22="yes",IF(H22="verified",1,0),IF(OR(H22="tested",H22="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <f aca="false">IF(H23="not applicable",IF(K23&lt;&gt;"",1,0),IF(I23="yes",IF(H23="verified",1,0),IF(OR(H23="tested",H23="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <f aca="false">IF(H24="not applicable",IF(K24&lt;&gt;"",1,0),IF(I24="yes",IF(H24="verified",1,0),IF(OR(H24="tested",H24="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J29" s="19"/>
+      <c r="K29" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="19"/>
+      <c r="K30" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18" t="n">
+        <f aca="false">IF(H30="not applicable",IF(K30&lt;&gt;"",1,0),IF(I30="yes",IF(H30="verified",1,0),IF(OR(H30="tested",H30="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="19"/>
+      <c r="K31" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18" t="n">
+        <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="18" t="n">
+        <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18" t="n">
+        <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K36" s="16"/>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K37" s="16"/>
+      <c r="L37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <f aca="false">IF(H37="not applicable",IF(K37&lt;&gt;"",1,0),IF(I37="yes",IF(H37="verified",1,0),IF(OR(H37="tested",H37="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K38" s="16"/>
+      <c r="L38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <f aca="false">IF(H38="not applicable",IF(K38&lt;&gt;"",1,0),IF(I38="yes",IF(H38="verified",1,0),IF(OR(H38="tested",H38="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <f aca="false">IF(H39="not applicable",IF(K39&lt;&gt;"",1,0),IF(I39="yes",IF(H39="verified",1,0),IF(OR(H39="tested",H39="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K40" s="16"/>
+      <c r="L40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <f aca="false">IF(H40="not applicable",IF(K40&lt;&gt;"",1,0),IF(I40="yes",IF(H40="verified",1,0),IF(OR(H40="tested",H40="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K41" s="16"/>
+      <c r="L41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <f aca="false">IF(H41="not applicable",IF(K41&lt;&gt;"",1,0),IF(I41="yes",IF(H41="verified",1,0),IF(OR(H41="tested",H41="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K42" s="16"/>
+      <c r="L42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="18" t="n">
+        <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18" t="n">
+        <f aca="false">IF(H44="not applicable",IF(K44&lt;&gt;"",1,0),IF(I44="yes",IF(H44="verified",1,0),IF(OR(H44="tested",H44="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <f aca="false">IF(H45="not applicable",IF(K45&lt;&gt;"",1,0),IF(I45="yes",IF(H45="verified",1,0),IF(OR(H45="tested",H45="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K46" s="16"/>
+      <c r="L46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="18" t="n">
+        <f aca="false">IF(H46="not applicable",IF(K46&lt;&gt;"",1,0),IF(I46="yes",IF(H46="verified",1,0),IF(OR(H46="tested",H46="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J47" s="19"/>
+      <c r="K47" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="L47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="18" t="n">
+        <f aca="false">IF(H47="not applicable",IF(K47&lt;&gt;"",1,0),IF(I47="yes",IF(H47="verified",1,0),IF(OR(H47="tested",H47="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:M47"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A6:M6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H9:H47">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$H9="not started"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$H9="partial"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$H9="implemented"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$H9="tested"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$H9="verified"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>$H9="blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>$H9="not applicable"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H47" type="list">
+      <formula1>_Lists!$A$1:$A$7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I47" type="list">
+      <formula1>_Lists!$B$1:$B$2</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G9" r:id="rId1" display="../src/components/alert-dialog/AlertDialog.tsx"/>
+    <hyperlink ref="G10" r:id="rId2" display="../../docs/alert-dialog-component-brief.md"/>
+    <hyperlink ref="G11" r:id="rId3" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G12" r:id="rId4" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G13" r:id="rId5" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G14" r:id="rId6" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G15" r:id="rId7" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G16" r:id="rId8" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G17" r:id="rId9" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G18" r:id="rId10" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G19" r:id="rId11" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G20" r:id="rId12" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G21" r:id="rId13" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G22" r:id="rId14" display="../test/components/alert-dialog.test.tsx + tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G23" r:id="rId15" display="../test/components/alert-dialog.test.tsx + tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G24" r:id="rId16" display="../src/components/alert-dialog/alert-dialog.css"/>
+    <hyperlink ref="G25" r:id="rId17" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G26" r:id="rId18" display="../playground/src/main.tsx"/>
+    <hyperlink ref="G27" r:id="rId19" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G28" r:id="rId20" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G29" r:id="rId21" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G30" r:id="rId22" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G31" r:id="rId23" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G32" r:id="rId24" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G33" r:id="rId25" display="../test/components/alert-dialog.test.tsx"/>
+    <hyperlink ref="G34" r:id="rId26" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G35" r:id="rId27" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G36" r:id="rId28" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G37" r:id="rId29" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G38" r:id="rId30" display="tests/alert-dialog.spec.ts"/>
+    <hyperlink ref="G39" r:id="rId31" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G40" r:id="rId32" display="../playwright.config.ts"/>
+    <hyperlink ref="G41" r:id="rId33" display="../scripts/verify-consumers.mjs"/>
+    <hyperlink ref="G42" r:id="rId34" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G43" r:id="rId35" display="manual-tests/alert-dialog.md"/>
+    <hyperlink ref="G44" r:id="rId36" display="../docs/components/alert-dialog/README.md"/>
+    <hyperlink ref="G45" r:id="rId37" display="../docs/components/alert-dialog/CHANGELOG.md"/>
+    <hyperlink ref="G46" r:id="rId38" display="../../../../apps/brick-consumer/tests/consumer.spec.ts"/>
+    <hyperlink ref="G47" r:id="rId39" display="../../docs/core-dependency-ledger.md"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId40"/>
+</worksheet>
 </file>
--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Dialog" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="_Lists" sheetId="6" state="hidden" r:id="rId8"/>
     <sheet name="AlertDialog" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Drawer" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">AlertDialog!$A$1:$M$47</definedName>
@@ -28,7 +29,10 @@
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dialog!$A$1:$M$45</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Dialog!$1:$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Dialog!$A$8:$M$45</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Index!$A$1:$N$11</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Drawer!$A$1:$M$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Drawer!$A$8:$M$47</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Index!$A$1:$N$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Index!$A$7:$N$12</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$B$18</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Instructions!$A$4:$B$18</definedName>
   </definedNames>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="523">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -113,6 +117,9 @@
     <t xml:space="preserve">AlertDialog</t>
   </si>
   <si>
+    <t xml:space="preserve">Drawer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brick Component Coverage</t>
   </si>
   <si>
@@ -1329,6 +1336,285 @@
   </si>
   <si>
     <t xml:space="preserve">Package owner-review gate remains open; legacy source is retained until it passes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawer Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted logical-edge modal compound, its twelve public parts, package proof, Consumer cutover, deferred owner review, and Sidebar-led legacy retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation directly composes public Atom 0.3.2 Drawer behavior and Modal.Branch without Core or local headless wrappers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/drawer/Drawer.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved capability audit covers modal state, keyboard, pointer, touch activation, focus, dismissal, portals, isolation, scrolling, presence, direction, and constrained viewports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/drawer-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swipe, drag, snap, handle, and gesture behavior are excluded from this release and the named Gesture Drawer / Bottom Sheet audit is tracked before a gesture surface is selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../TODO.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and drawer-subpath namespaces, direct part exports, declarations, logical placement, and closed size unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atom owns controlled/uncontrolled state, Escape/backdrop policy, disabled state, close reasons, modal layers, and cleanup; Brick forwards the public contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/drawer.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger preserves disabled state, native props, ref, stable hooks, and representative Atom asChild and render composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal preserves body, inline, and custom-container composition without copying behavior into Brick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visible Overlay preserves class/slot/ref/native props and enabled/disabled exact-target dismissal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/drawer.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content preserves dialog semantics, accessible-name fallback, refs and native props while adding only placement, size, class, slot, and visual data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header is one optional native visual region with stable class/slot and no generated semantic structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title preserves Atom registration, generated accessible naming, heading-level forwarding, ref, and visual hooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description preserves Atom registration and the optional generated accessible description while forwarding native props and ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body is the flexible independently scrollable native region and keeps long mobile content contained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer is a native wrapping action region in logical source order and stays reachable with long content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close preserves close reason, native props, ref, stable hooks, and representative asChild/render composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch preserves Atom registration, render composition, ref, and stable Drawer hooks for a body-portalled composite surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logical start, end, top, and bottom placement attach to the correct edge and remain viewport-bound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small, medium, large, and full size recipes are closed, directional, and exposed through public CSS variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile side sizes remain strictly ordered; non-full sizes preserve Overlay context and only full occupies the viewport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled CSS uses public classes, component tokens, logical properties, elevated surface hierarchy, and safe-area-aware edge treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light and dark Drawer surfaces retain readable hierarchy, controls, scrim, and edge separation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTL start resolves to the physical right with direction-correct title, body, footer, radius, shadow, and entrance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced-motion baselines remove travel and forced colors retain a system boundary and operable controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public tokens, class, style, slot, scoped appearance, and inline Portal customization remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /drawer workbench exposes overview, anatomy, placements, sizes, state, appearance, responsive, customization, stress, and evidence scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nested modal, portalled Branch, long content, RTL, mobile, dismissal, disabled Trigger, and full-viewport cases are deterministic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest and Testing Library adapter tests cover defaults, anatomy, props, refs, composition, disabled behavior, Portal, heading, placements, sizes, and exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types accept supported native and Atom props and reject physical placement, invalid sizes, and callable Drawer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node boundary/export/CSS tests, strict typecheck, build, and 100% component-source coverage pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/package/package.test.mjs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Drawer interaction matrix passes for all eleven focused scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical open Drawer and Consumer workflow have no automated axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five Chromium visual baselines are recorded and reviewed for light, dark, mobile RTL, full mobile, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry-run pack, CSS size report, and clean React 18/19 tarball consumers verify published files and imports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered Drawer manual-test protocol covers human visual, keyboard, touch, phone, zoom, VoiceOver, direction, preferences, Branch, and customization judgment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/drawer.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner manual run records every numbered result and corrects any finding before package completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner manual review intentionally deferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Drawer guide covers role, imports, anatomy, API, placement, mobile sizes, tokens, responsive behavior, accessibility, composition, and gesture exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/drawer/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawer and package changelogs record the public component, mobile sizing, evidence, and named gesture follow-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/drawer/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer composes a public-subpath project-filter workflow and passes boundary, production, desktop/mobile interaction, layout, focus, and axe gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Drawer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core Drawer remains until Sidebar stops importing DrawerContentBase and a later authorized cutover removes source, types, defaults, exports, CSS, and dead declarations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidebar imports DrawerContentBase</t>
   </si>
 </sst>
 </file>
@@ -1620,6 +1906,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF172033"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1723,14 +2017,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8FAFC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1883,6 +2169,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ButtonEvidence" displayName="ButtonEvidence" ref="A8:M34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A8:M34"/>
@@ -1926,8 +2220,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CoverageIndex" displayName="CoverageIndex" ref="A7:N10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A7:N10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CoverageIndex" displayName="CoverageIndex" ref="A7:N12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A7:N12"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Component"/>
     <tableColumn id="2" name="Requirements"/>
@@ -2158,7 +2452,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -2214,29 +2508,29 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">COUNTA(A8:A11)</f>
-        <v>4</v>
+        <f aca="false">COUNTA(A8:A12)</f>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">COUNTIF(N8:N11,"complete")</f>
+        <f aca="false">COUNTIF(N8:N12,"complete")</f>
         <v>0</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="5" t="n">
-        <f aca="false">SUM(H8:H11)</f>
-        <v>3</v>
+        <f aca="false">SUM(H8:H12)</f>
+        <v>4</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(B8:B11,J8:J11)/SUM(B8:B11),0)</f>
-        <v>0.918518518518519</v>
+        <f aca="false">IFERROR(SUMPRODUCT(B8:B12,J8:J12)/SUM(B8:B12),0)</f>
+        <v>0.925287356321839</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2511,39 +2805,98 @@
         <v>blocked</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <f aca="false">COUNTA(Drawer!A9:A47)</f>
+        <v>39</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"not started")</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"partial")</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"implemented")</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"tested")</f>
+        <v>31</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"verified")</f>
+        <v>6</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <f aca="false">COUNTIF(Drawer!H9:H47,"not applicable")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <f aca="false">IFERROR(SUM(Drawer!M9:M47)/SUM(Drawer!L9:L47),0)</f>
+        <v>0.948717948717949</v>
+      </c>
+      <c r="K12" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(Drawer!E9:E47,"package",Drawer!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="L12" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(Drawer!E9:E47,"consumer",Drawer!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>complete</v>
+      </c>
+      <c r="M12" s="8" t="str">
+        <f aca="false">IF(COUNTIFS(Drawer!E9:E47,"retirement",Drawer!M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="N12" s="1" t="str">
+        <f aca="false">IF(H12&gt;0,"blocked",IF(AND(J12=1,K12="complete",L12="complete",M12="complete"),"complete",IF(J12=0,"not started","in progress")))</f>
+        <v>blocked</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A7:N12"/>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N8:N10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <conditionalFormatting sqref="N8:N12">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$N8="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$N8="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$N8="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$N8="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$N8="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$N8="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$N8="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="A8" r:id="rId1" location="'Button'!A1" display="Button"/>
-    <hyperlink ref="A9" r:id="rId2" location="'Card'!A1" display="Card"/>
-    <hyperlink ref="A10" r:id="rId3" location="'Dialog'!A1" display="Dialog"/>
-    <hyperlink ref="A11" r:id="rId4" location="'AlertDialog'!A1" display="AlertDialog"/>
+    <hyperlink ref="A8" location="'Button'!A1" display="Button"/>
+    <hyperlink ref="A9" location="'Card'!A1" display="Card"/>
+    <hyperlink ref="A10" location="'Dialog'!A1" display="Dialog"/>
+    <hyperlink ref="A11" location="'AlertDialog'!A1" display="AlertDialog"/>
+    <hyperlink ref="A12" location="'Drawer'!A1" display="Drawer"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2552,8 +2905,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <tableParts>
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2572,7 +2926,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2580,7 +2934,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2588,18 +2942,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2607,7 +2961,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2615,7 +2969,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2623,7 +2977,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2631,7 +2985,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2639,7 +2993,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2647,7 +3001,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2655,7 +3009,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2663,7 +3017,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2671,7 +3025,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2687,23 +3041,23 @@
         <v>17</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2751,7 +3105,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2768,7 +3122,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2792,7 +3146,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M34)</f>
@@ -2829,7 +3183,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -2846,72 +3200,72 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>46219</v>
@@ -2927,31 +3281,31 @@
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>46219</v>
@@ -2967,31 +3321,31 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>46219</v>
@@ -3007,31 +3361,31 @@
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="17" t="n">
         <v>46219</v>
@@ -3047,31 +3401,31 @@
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>46219</v>
@@ -3087,31 +3441,31 @@
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>46219</v>
@@ -3127,31 +3481,31 @@
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>46219</v>
@@ -3167,31 +3521,31 @@
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J16" s="17" t="n">
         <v>46219</v>
@@ -3207,31 +3561,31 @@
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>46219</v>
@@ -3247,31 +3601,31 @@
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>46219</v>
@@ -3287,31 +3641,31 @@
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>46219</v>
@@ -3327,31 +3681,31 @@
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>46219</v>
@@ -3367,31 +3721,31 @@
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>46219</v>
@@ -3407,31 +3761,31 @@
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>46219</v>
@@ -3447,31 +3801,31 @@
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>46219</v>
@@ -3487,31 +3841,31 @@
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J24" s="17" t="n">
         <v>46219</v>
@@ -3527,31 +3881,31 @@
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>46219</v>
@@ -3567,31 +3921,31 @@
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>46219</v>
@@ -3607,31 +3961,31 @@
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>46219</v>
@@ -3647,31 +4001,31 @@
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J28" s="17" t="n">
         <v>46219</v>
@@ -3687,31 +4041,31 @@
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J29" s="17" t="n">
         <v>46219</v>
@@ -3727,31 +4081,31 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>46219</v>
@@ -3767,31 +4121,31 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J31" s="17" t="n">
         <v>46219</v>
@@ -3807,31 +4161,31 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>46219</v>
@@ -3847,31 +4201,31 @@
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>46219</v>
@@ -3887,29 +4241,29 @@
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G34" s="16"/>
       <c r="H34" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J34" s="16"/>
       <c r="K34" s="16"/>
@@ -3929,25 +4283,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H34">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4027,7 +4381,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4044,7 +4398,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4068,7 +4422,7 @@
         <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M41)</f>
@@ -4105,7 +4459,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -4122,72 +4476,72 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>46220</v>
@@ -4203,31 +4557,31 @@
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>46220</v>
@@ -4243,31 +4597,31 @@
     </row>
     <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>46220</v>
@@ -4283,31 +4637,31 @@
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="17" t="n">
         <v>46220</v>
@@ -4323,31 +4677,31 @@
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>168</v>
-      </c>
       <c r="H13" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>46220</v>
@@ -4363,31 +4717,31 @@
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>46220</v>
@@ -4403,31 +4757,31 @@
     </row>
     <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>46220</v>
@@ -4443,31 +4797,31 @@
     </row>
     <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J16" s="17" t="n">
         <v>46220</v>
@@ -4483,31 +4837,31 @@
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>46220</v>
@@ -4523,31 +4877,31 @@
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>46220</v>
@@ -4563,31 +4917,31 @@
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>46220</v>
@@ -4603,31 +4957,31 @@
     </row>
     <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>46220</v>
@@ -4643,31 +4997,31 @@
     </row>
     <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>46220</v>
@@ -4683,31 +5037,31 @@
     </row>
     <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>46220</v>
@@ -4723,31 +5077,31 @@
     </row>
     <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>46220</v>
@@ -4763,31 +5117,31 @@
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J24" s="17" t="n">
         <v>46220</v>
@@ -4803,31 +5157,31 @@
     </row>
     <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>46220</v>
@@ -4843,31 +5197,31 @@
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J26" s="17" t="n">
         <v>46220</v>
@@ -4883,31 +5237,31 @@
     </row>
     <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>46220</v>
@@ -4923,31 +5277,31 @@
     </row>
     <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J28" s="17" t="n">
         <v>46220</v>
@@ -4963,31 +5317,31 @@
     </row>
     <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J29" s="17" t="n">
         <v>46220</v>
@@ -5003,31 +5357,31 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J30" s="17" t="n">
         <v>46220</v>
@@ -5043,31 +5397,31 @@
     </row>
     <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J31" s="17" t="n">
         <v>46220</v>
@@ -5083,31 +5437,31 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J32" s="17" t="n">
         <v>46220</v>
@@ -5123,31 +5477,31 @@
     </row>
     <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J33" s="17" t="n">
         <v>46220</v>
@@ -5163,31 +5517,31 @@
     </row>
     <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J34" s="17" t="n">
         <v>46220</v>
@@ -5203,31 +5557,31 @@
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J35" s="17" t="n">
         <v>46220</v>
@@ -5243,31 +5597,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J36" s="17" t="n">
         <v>46220</v>
@@ -5283,31 +5637,31 @@
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J37" s="17" t="n">
         <v>46220</v>
@@ -5323,31 +5677,31 @@
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J38" s="17" t="n">
         <v>46220</v>
@@ -5363,31 +5717,31 @@
     </row>
     <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J39" s="17" t="n">
         <v>46220</v>
@@ -5403,31 +5757,31 @@
     </row>
     <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J40" s="17" t="n">
         <v>46220</v>
@@ -5443,37 +5797,37 @@
     </row>
     <row r="41" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J41" s="17" t="n">
         <v>46220</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>1</v>
@@ -5491,25 +5845,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H41">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5597,7 +5951,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5614,7 +5968,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5638,7 +5992,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M45)</f>
@@ -5675,7 +6029,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -5692,72 +6046,72 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46220</v>
@@ -5773,31 +6127,31 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>46220</v>
@@ -5813,31 +6167,31 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>46220</v>
@@ -5853,31 +6207,31 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="19" t="n">
         <v>46221</v>
@@ -5893,31 +6247,31 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>257</v>
-      </c>
       <c r="H13" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>46221</v>
@@ -5933,31 +6287,31 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14" s="19" t="n">
         <v>46221</v>
@@ -5973,31 +6327,31 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>46221</v>
@@ -6013,31 +6367,31 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J16" s="19" t="n">
         <v>46220</v>
@@ -6053,31 +6407,31 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J17" s="19" t="n">
         <v>46220</v>
@@ -6093,31 +6447,31 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="19" t="n">
         <v>46221</v>
@@ -6133,31 +6487,31 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>46220</v>
@@ -6173,31 +6527,31 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J20" s="19" t="n">
         <v>46220</v>
@@ -6213,31 +6567,31 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>280</v>
-      </c>
       <c r="H21" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J21" s="19" t="n">
         <v>46220</v>
@@ -6253,31 +6607,31 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J22" s="19" t="n">
         <v>46221</v>
@@ -6293,31 +6647,31 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J23" s="19" t="n">
         <v>46221</v>
@@ -6333,31 +6687,31 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J24" s="19" t="n">
         <v>46220</v>
@@ -6373,31 +6727,31 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J25" s="19" t="n">
         <v>46220</v>
@@ -6413,31 +6767,31 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>46220</v>
@@ -6453,31 +6807,31 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J27" s="19" t="n">
         <v>46220</v>
@@ -6493,31 +6847,31 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J28" s="19" t="n">
         <v>46220</v>
@@ -6533,31 +6887,31 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J29" s="19" t="n">
         <v>46220</v>
@@ -6573,31 +6927,31 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>46220</v>
@@ -6613,31 +6967,31 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J31" s="19" t="n">
         <v>46220</v>
@@ -6653,31 +7007,31 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J32" s="19" t="n">
         <v>46220</v>
@@ -6693,31 +7047,31 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>46221</v>
@@ -6733,31 +7087,31 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>46220</v>
@@ -6773,31 +7127,31 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J35" s="19" t="n">
         <v>46221</v>
@@ -6813,31 +7167,31 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>46220</v>
@@ -6853,31 +7207,31 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>46220</v>
@@ -6893,31 +7247,31 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>46221</v>
@@ -6933,31 +7287,31 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J39" s="19" t="n">
         <v>46220</v>
@@ -6973,31 +7327,31 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J40" s="19" t="n">
         <v>46220</v>
@@ -7013,31 +7367,31 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J41" s="19" t="n">
         <v>46220</v>
@@ -7053,31 +7407,31 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J42" s="19" t="n">
         <v>46221</v>
@@ -7093,31 +7447,31 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J43" s="19" t="n">
         <v>46221</v>
@@ -7133,31 +7487,31 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J44" s="19" t="n">
         <v>46220</v>
@@ -7173,37 +7527,37 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J45" s="19" t="n">
         <v>46220</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1</v>
@@ -7221,25 +7575,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H45">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7253,6 +7607,45 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G9" r:id="rId1" display="../src/components/dialog/Dialog.tsx"/>
+    <hyperlink ref="G10" r:id="rId2" display="../../docs/dialog-component-brief.md"/>
+    <hyperlink ref="G11" r:id="rId3" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G12" r:id="rId4" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G13" r:id="rId5" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G14" r:id="rId6" display="../test/components/dialog.test.tsx + tests/dialog.spec.ts"/>
+    <hyperlink ref="G15" r:id="rId7" display="tests/dialog.spec.ts"/>
+    <hyperlink ref="G16" r:id="rId8" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G17" r:id="rId9" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G18" r:id="rId10" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G19" r:id="rId11" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G20" r:id="rId12" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G21" r:id="rId13" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G22" r:id="rId14" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G23" r:id="rId15" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G24" r:id="rId16" display="../src/components/dialog/dialog.css"/>
+    <hyperlink ref="G25" r:id="rId17" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G26" r:id="rId18" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G27" r:id="rId19" display="tests/dialog.spec.ts"/>
+    <hyperlink ref="G28" r:id="rId20" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G29" r:id="rId21" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G30" r:id="rId22" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G31" r:id="rId23" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G32" r:id="rId24" display="tests/dialog.spec.ts"/>
+    <hyperlink ref="G33" r:id="rId25" display="../test/components/dialog.test.tsx"/>
+    <hyperlink ref="G34" r:id="rId26" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G35" r:id="rId27" display="tests/dialog.spec.ts"/>
+    <hyperlink ref="G36" r:id="rId28" display="tests/dialog.spec.ts"/>
+    <hyperlink ref="G37" r:id="rId29" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G38" r:id="rId30" display="../playwright.config.ts"/>
+    <hyperlink ref="G39" r:id="rId31" display="../scripts/verify-consumers.mjs"/>
+    <hyperlink ref="G40" r:id="rId32" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G41" r:id="rId33" display="manual-tests/dialog.md"/>
+    <hyperlink ref="G42" r:id="rId34" display="../docs/components/dialog/README.md"/>
+    <hyperlink ref="G43" r:id="rId35" display="../docs/components/dialog/CHANGELOG.md"/>
+    <hyperlink ref="G44" r:id="rId36" display="../../../../apps/brick-consumer/tests/consumer.spec.ts"/>
+    <hyperlink ref="G45" r:id="rId37" display="../../docs/core-dependency-ledger.md"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7260,9 +7653,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId38"/>
   <tableParts>
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7277,43 +7670,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -7352,7 +7745,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7369,7 +7762,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7393,7 +7786,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
@@ -7430,7 +7823,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -7447,72 +7840,72 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46221</v>
@@ -7528,31 +7921,31 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>46221</v>
@@ -7568,31 +7961,31 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>46221</v>
@@ -7608,31 +8001,31 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="19" t="n">
         <v>46221</v>
@@ -7648,31 +8041,31 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>352</v>
-      </c>
       <c r="H13" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>46221</v>
@@ -7688,31 +8081,31 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14" s="19" t="n">
         <v>46221</v>
@@ -7728,31 +8121,31 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>46221</v>
@@ -7768,31 +8161,31 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J16" s="19" t="n">
         <v>46221</v>
@@ -7808,31 +8201,31 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J17" s="19" t="n">
         <v>46221</v>
@@ -7848,31 +8241,31 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="19" t="n">
         <v>46221</v>
@@ -7888,31 +8281,31 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>46221</v>
@@ -7928,35 +8321,35 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L20" s="18" t="n">
         <v>1</v>
@@ -7968,35 +8361,35 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J21" s="19"/>
       <c r="K21" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1</v>
@@ -8008,31 +8401,31 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J22" s="19" t="n">
         <v>46221</v>
@@ -8048,31 +8441,31 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>374</v>
-      </c>
       <c r="H23" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J23" s="19" t="n">
         <v>46221</v>
@@ -8088,31 +8481,31 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J24" s="19" t="n">
         <v>46221</v>
@@ -8128,35 +8521,35 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>1</v>
@@ -8168,31 +8561,31 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>46221</v>
@@ -8208,31 +8601,31 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J27" s="19" t="n">
         <v>46221</v>
@@ -8248,31 +8641,31 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J28" s="19" t="n">
         <v>46221</v>
@@ -8288,35 +8681,35 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J29" s="19"/>
       <c r="K29" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1</v>
@@ -8328,35 +8721,35 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J30" s="19"/>
       <c r="K30" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L30" s="18" t="n">
         <v>1</v>
@@ -8368,35 +8761,35 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J31" s="19"/>
       <c r="K31" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1</v>
@@ -8408,31 +8801,31 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J32" s="19" t="n">
         <v>46221</v>
@@ -8448,31 +8841,31 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>46221</v>
@@ -8488,31 +8881,31 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>46221</v>
@@ -8528,31 +8921,31 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J35" s="19" t="n">
         <v>46221</v>
@@ -8568,31 +8961,31 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>46221</v>
@@ -8608,31 +9001,31 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J37" s="19" t="n">
         <v>46221</v>
@@ -8648,31 +9041,31 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>46221</v>
@@ -8688,31 +9081,31 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J39" s="19" t="n">
         <v>46221</v>
@@ -8728,31 +9121,31 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J40" s="19" t="n">
         <v>46221</v>
@@ -8768,31 +9161,31 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J41" s="19" t="n">
         <v>46221</v>
@@ -8808,31 +9201,31 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J42" s="19" t="n">
         <v>46221</v>
@@ -8848,35 +9241,35 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1</v>
@@ -8888,31 +9281,31 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J44" s="19" t="n">
         <v>46221</v>
@@ -8928,31 +9321,31 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J45" s="19" t="n">
         <v>46221</v>
@@ -8968,31 +9361,31 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J46" s="19" t="n">
         <v>46221</v>
@@ -9008,35 +9401,35 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J47" s="19"/>
       <c r="K47" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>
@@ -9054,25 +9447,25 @@
     <mergeCell ref="A6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H47">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H9="not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H9="partial"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H9="implemented"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$H9="tested"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$H9="verified"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$H9="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$H9="not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9136,4 +9529,1817 @@
   </headerFooter>
   <drawing r:id="rId40"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <f aca="false">COUNTA(A9:A47)</f>
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <f aca="false">SUM(M9:M47)</f>
+        <v>37</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
+        <v>0.948717948717949</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <f aca="false">COUNTIF(H9:H47,"blocked")</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="5" t="str">
+        <f aca="false">IF(COUNTIFS(E9:E47,"retirement",M9:M47,"&lt;1")=0,"complete","open")</f>
+        <v>open</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="18" t="n">
+        <f aca="false">IF(H9="not applicable",IF(K9&lt;&gt;"",1,0),IF(I9="yes",IF(H9="verified",1,0),IF(OR(H9="tested",H9="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K10" s="16"/>
+      <c r="L10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <f aca="false">IF(H10="not applicable",IF(K10&lt;&gt;"",1,0),IF(I10="yes",IF(H10="verified",1,0),IF(OR(H10="tested",H10="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <f aca="false">IF(H11="not applicable",IF(K11&lt;&gt;"",1,0),IF(I11="yes",IF(H11="verified",1,0),IF(OR(H11="tested",H11="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <f aca="false">IF(H12="not applicable",IF(K12&lt;&gt;"",1,0),IF(I12="yes",IF(H12="verified",1,0),IF(OR(H12="tested",H12="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <f aca="false">IF(H13="not applicable",IF(K13&lt;&gt;"",1,0),IF(I13="yes",IF(H13="verified",1,0),IF(OR(H13="tested",H13="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <f aca="false">IF(H14="not applicable",IF(K14&lt;&gt;"",1,0),IF(I14="yes",IF(H14="verified",1,0),IF(OR(H14="tested",H14="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <f aca="false">IF(H15="not applicable",IF(K15&lt;&gt;"",1,0),IF(I15="yes",IF(H15="verified",1,0),IF(OR(H15="tested",H15="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">IF(H16="not applicable",IF(K16&lt;&gt;"",1,0),IF(I16="yes",IF(H16="verified",1,0),IF(OR(H16="tested",H16="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="18" t="n">
+        <f aca="false">IF(H17="not applicable",IF(K17&lt;&gt;"",1,0),IF(I17="yes",IF(H17="verified",1,0),IF(OR(H17="tested",H17="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="18" t="n">
+        <f aca="false">IF(H18="not applicable",IF(K18&lt;&gt;"",1,0),IF(I18="yes",IF(H18="verified",1,0),IF(OR(H18="tested",H18="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <f aca="false">IF(H19="not applicable",IF(K19&lt;&gt;"",1,0),IF(I19="yes",IF(H19="verified",1,0),IF(OR(H19="tested",H19="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <f aca="false">IF(H20="not applicable",IF(K20&lt;&gt;"",1,0),IF(I20="yes",IF(H20="verified",1,0),IF(OR(H20="tested",H20="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <f aca="false">IF(H21="not applicable",IF(K21&lt;&gt;"",1,0),IF(I21="yes",IF(H21="verified",1,0),IF(OR(H21="tested",H21="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <f aca="false">IF(H22="not applicable",IF(K22&lt;&gt;"",1,0),IF(I22="yes",IF(H22="verified",1,0),IF(OR(H22="tested",H22="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <f aca="false">IF(H23="not applicable",IF(K23&lt;&gt;"",1,0),IF(I23="yes",IF(H23="verified",1,0),IF(OR(H23="tested",H23="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <f aca="false">IF(H24="not applicable",IF(K24&lt;&gt;"",1,0),IF(I24="yes",IF(H24="verified",1,0),IF(OR(H24="tested",H24="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18" t="n">
+        <f aca="false">IF(H30="not applicable",IF(K30&lt;&gt;"",1,0),IF(I30="yes",IF(H30="verified",1,0),IF(OR(H30="tested",H30="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18" t="n">
+        <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="18" t="n">
+        <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18" t="n">
+        <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K36" s="16"/>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K37" s="16"/>
+      <c r="L37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <f aca="false">IF(H37="not applicable",IF(K37&lt;&gt;"",1,0),IF(I37="yes",IF(H37="verified",1,0),IF(OR(H37="tested",H37="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K38" s="16"/>
+      <c r="L38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <f aca="false">IF(H38="not applicable",IF(K38&lt;&gt;"",1,0),IF(I38="yes",IF(H38="verified",1,0),IF(OR(H38="tested",H38="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <f aca="false">IF(H39="not applicable",IF(K39&lt;&gt;"",1,0),IF(I39="yes",IF(H39="verified",1,0),IF(OR(H39="tested",H39="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K40" s="16"/>
+      <c r="L40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <f aca="false">IF(H40="not applicable",IF(K40&lt;&gt;"",1,0),IF(I40="yes",IF(H40="verified",1,0),IF(OR(H40="tested",H40="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K41" s="16"/>
+      <c r="L41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <f aca="false">IF(H41="not applicable",IF(K41&lt;&gt;"",1,0),IF(I41="yes",IF(H41="verified",1,0),IF(OR(H41="tested",H41="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K42" s="16"/>
+      <c r="L42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="18" t="n">
+        <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18" t="n">
+        <f aca="false">IF(H44="not applicable",IF(K44&lt;&gt;"",1,0),IF(I44="yes",IF(H44="verified",1,0),IF(OR(H44="tested",H44="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <f aca="false">IF(H45="not applicable",IF(K45&lt;&gt;"",1,0),IF(I45="yes",IF(H45="verified",1,0),IF(OR(H45="tested",H45="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K46" s="16"/>
+      <c r="L46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="18" t="n">
+        <f aca="false">IF(H46="not applicable",IF(K46&lt;&gt;"",1,0),IF(I46="yes",IF(H46="verified",1,0),IF(OR(H46="tested",H46="verified"),1,0)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="L47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="18" t="n">
+        <f aca="false">IF(H47="not applicable",IF(K47&lt;&gt;"",1,0),IF(I47="yes",IF(H47="verified",1,0),IF(OR(H47="tested",H47="verified"),1,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:M47"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A6:M6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H9:H47">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$H9="not started"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$H9="partial"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$H9="implemented"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$H9="tested"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>$H9="verified"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>$H9="blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>$H9="not applicable"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H9:H47" type="list">
+      <formula1>_Lists!$A$1:$A$7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9:I47" type="list">
+      <formula1>_Lists!$B$1:$B$2</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G9" r:id="rId1" display="../src/components/drawer/Drawer.tsx"/>
+    <hyperlink ref="G10" r:id="rId2" display="../../docs/drawer-component-brief.md"/>
+    <hyperlink ref="G11" r:id="rId3" display="../../TODO.md"/>
+    <hyperlink ref="G12" r:id="rId4" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G13" r:id="rId5" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G14" r:id="rId6" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G15" r:id="rId7" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G16" r:id="rId8" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G17" r:id="rId9" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G18" r:id="rId10" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G19" r:id="rId11" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G20" r:id="rId12" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G21" r:id="rId13" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G22" r:id="rId14" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G23" r:id="rId15" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G24" r:id="rId16" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G25" r:id="rId17" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G26" r:id="rId18" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G27" r:id="rId19" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G28" r:id="rId20" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G29" r:id="rId21" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G30" r:id="rId22" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G31" r:id="rId23" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G32" r:id="rId24" display="../playground/src/main.tsx"/>
+    <hyperlink ref="G33" r:id="rId25" display="../playground/src/main.tsx"/>
+    <hyperlink ref="G34" r:id="rId26" display="../playground/src/main.tsx"/>
+    <hyperlink ref="G35" r:id="rId27" display="../test/components/drawer.test.tsx"/>
+    <hyperlink ref="G36" r:id="rId28" display="../test/types/public-api.test.ts"/>
+    <hyperlink ref="G37" r:id="rId29" display="../test/package/package.test.mjs"/>
+    <hyperlink ref="G38" r:id="rId30" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G39" r:id="rId31" display="tests/drawer.spec.ts"/>
+    <hyperlink ref="G40" r:id="rId32" display="tests/visual.spec.ts"/>
+    <hyperlink ref="G41" r:id="rId33" display="../scripts/verify-consumers.mjs"/>
+    <hyperlink ref="G42" r:id="rId34" display="manual-tests/drawer.md"/>
+    <hyperlink ref="G43" r:id="rId35" display="manual-tests/drawer.md"/>
+    <hyperlink ref="G44" r:id="rId36" display="../docs/components/drawer/README.md"/>
+    <hyperlink ref="G45" r:id="rId37" display="../docs/components/drawer/CHANGELOG.md"/>
+    <hyperlink ref="G46" r:id="rId38" display="../../../../apps/brick-consumer/tests/consumer.spec.ts"/>
+    <hyperlink ref="G47" r:id="rId39" display="../../docs/core-dependency-ledger.md"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId40"/>
+</worksheet>
 </file>
--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4789" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="1314">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -1192,9 +1192,6 @@
     <t xml:space="preserve">manual-tests/alert-dialog.md</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner manual review pending.</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALD-13</t>
   </si>
   <si>
@@ -1372,7 +1369,7 @@
     <t xml:space="preserve">Legacy Core AlertDialog source and feedback export are removed after the package and consumer gates pass</t>
   </si>
   <si>
-    <t xml:space="preserve">Package owner-review gate remains open; legacy source is retained until it passes.</t>
+    <t xml:space="preserve">Owner review and package gate pass; legacy removal awaits explicit dependency-led retirement authorization.</t>
   </si>
   <si>
     <t xml:space="preserve">Drawer Evidence Matrix</t>
@@ -1579,7 +1576,7 @@
     <t xml:space="preserve">DRA-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Drawer interaction matrix passes for all eleven focused scenarios</t>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Drawer interaction matrix passes, including focused RTL travel and extreme-height reflow coverage</t>
   </si>
   <si>
     <t xml:space="preserve">DRA-31</t>
@@ -1615,574 +1612,577 @@
     <t xml:space="preserve">Latest owner manual run records every numbered result and corrects any finding before package completion</t>
   </si>
   <si>
+    <t xml:space="preserve">Owner run completed: eight steps pass; iOS Safari 26.5.2 Hide Toolbar reproduces a shared Atom modal scroll-lock/visual-viewport blocker in Drawer and Dialog.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Drawer guide covers role, imports, anatomy, API, placement, mobile sizes, tokens, responsive behavior, accessibility, composition, and gesture exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/drawer/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawer and package changelogs record the public component, mobile sizing, evidence, and named gesture follow-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/drawer/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer composes a public-subpath project-filter workflow and passes boundary, production, desktop/mobile interaction, layout, focus, and axe gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRA-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Drawer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core Drawer remains until Sidebar stops importing DrawerContentBase and a later authorized cutover removes source, types, defaults, exports, CSS, and dead declarations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidebar imports DrawerContentBase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badge Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted passive Badge and attached NotificationBadge family, package proof, Consumer cutover, and completed dependency-led Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badge directly composes the public Atom 0.3.3 Badge subpath without Core, framework, or local behavior wrappers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/badge/Badge.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved Atom audit and released 0.3.3 server-safety patch cover semantic span output, native forwarding, ref, composition, and slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/badge-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and badge-subpath exports, declarations, required children, and all closed unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default passive span emits stable class/slot plus soft, neutral, medium, and rounded metadata without invented role, state, or focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/badge.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft, solid, and outline variants; six tones; three sizes; and rounded/pill shapes are complete and reject arbitrary color/radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Children, native props/events, class, style, ref, slot override, asChild, and render composition preserve Atom ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Badge adds no role, live region, tab stop, disabled, selected, removable, or interactive behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NotificationBadge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrapper requires one React element child and emits stable wrapper/indicator slots without mutating child semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count formatting covers one-digit circles, multi-digit pills, configurable maximum, and overflow labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dot, showZero, zero suppression, and invisible state preserve layout while controlling indicator visibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four logical placements, circular/rectangular overlap, and three indicator sizes emit closed metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicator is aria-hidden and pointer-inert; owning content retains the full localized count/status name without automatic live announcements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/badge.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled layered CSS uses Brick classes, semantic tokens, logical properties, and public component variables without global leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/badge/badge.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed light and dark matrices preserve tone, variant, inline hierarchy, count, dot, and anchor geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors emulation preserves explicit system boundaries for inline and attached indicators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logical start/end placement mirrors in RTL without physical-position props</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constrained, localized, mixed-direction, long-token, and inline-baseline scenarios stay contained without document overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interaction boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicator does not intercept pointer input or obscure the anchor focus ring; the owning control preserves at least a 44px target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class, style, slot, scoped appearance, and semantic/component-token overrides remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /badge workbench exposes defaults, complete recipes, shapes, sizes, passive-tag routing, and real contexts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counts, dots, maximum, zero, invisible, placements, overlap, icon/navigation/Avatar anchors, and contextual names are deterministic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light/dark, customization, localization, RTL, constrained width, stress, and forced-colors inspection anchors exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest and Testing Library cover defaults, recipes, native props, ref, composition, slots, and passive semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest covers count/dot union, formatting, visibility, placements, overlap, sizes, arbitrary element targets, and pointer ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, tones, shapes, counts, children, and Chip-like APIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node boundary, package export, server markup, stylesheet, declaration, and dry-pack checks include both Badge components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit Atom Badge subpath remains server-safe and clean React 18/19 packed consumers import, render, and load CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strict typecheck, build, CSS report, and 100% Brick component-source coverage pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser checks cover recipes, formatting, focus/pointer ownership, RTL, stress, axe, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical Badge route has no automatically detectable axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven reviewed Chromium baselines cover recipes, dark geometry, inline alignment, localization/RTL, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Badge release-matrix checks pass where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered Badge manual protocol covers hierarchy, recipes, zoom, VoiceOver, direction, system colors, touch/focus context, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/badge.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run records every numbered Badge and NotificationBadge result and corrects any finding before package completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide covers both roles, use/avoid boundaries, recipes, formatting, accessibility context, composition, responsiveness, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/badge/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badge component changelog records the initial public contract, Atom 0.3.3 boundary, and evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/badge/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer uses public Badge and NotificationBadge subpaths and passes production, boundary, desktop/mobile, focus, layout, dark, and axe checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh search after Avatar removal found no Core Badge dependent; source, types, defaults, resolver, base alias, and barrel export are removed and Core builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAD-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chip / Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic Chip, removable Tag, actions, and persistent selections remain excluded and route to Badge, Button, or future Toggle/Tag work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted direct Avatar, explicit image/fallback semantics, status-ring geometry, package proof, Consumer cutover, and completed Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar directly composes the public Atom 0.3.3 Avatar subpath without Core, framework, or local behavior wrappers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/avatar/Avatar.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved capability audit confirms Atom owns loading/error state, source preload, delayed fallback, native image semantics, and status callback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/avatar-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and avatar-subpath exports, declarations, required alt/fallback, optional src, and closed size/shape/status unions match the brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest fallback-only render emits a passive span with stable class/slot and md/circle defaults without leaked visual props or root role/tab stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/avatar.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One source reaches Atom Root and Image; loaded native image preserves src, required alt, crop hook, and mutual exclusion with fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informative fallback exposes role img and the full alt label; deliberate empty alt makes loaded and fallback imagery decorative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Successful and failed deterministic sources switch between Image and explicit fallback while preserving the frame and accessible identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallbackDelayMs and onLoadingStatusChange remain public Atom-owned inputs; loading and loaded callback states pass through Brick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native span attributes, ARIA/data attributes, event, class, style, overridable slot, ReactNode fallback, and HTMLSpanElement ref are preserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five exact square sizes map to 24, 32, 40, 48, and 64 CSS pixels without responsive mutation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/avatar.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circle and rounded shapes are closed recipes; image/fallback clipping and external ring inherit the selected radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online, away, busy, and offline map to success, warning, danger, and neutral semantic rings; absent status has no status metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layered external ring follows both shapes without changing 48px test dimensions, adding semantic DOM, or intercepting input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar stays passive; informative/decorative contexts and Avatar inside a named control avoid duplicate focus and speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visible localized text communicates each status; ring color is reinforcement and no automatic live announcement is added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NotificationBadge wraps Avatar and a native image; a distinct count/dot coexists without obscuring Avatar status geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled layered CSS uses Brick classes, semantic tokens, fixed logical geometry, and documented component variables without global leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/avatar/avatar.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed light/dark fallback, loaded image, shape, status, and NotificationBadge compositions preserve hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors emulation preserves an explicit system frame and shape-following status outline while visible text keeps exact meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constrained mobile, RTL, non-Latin fallback, and long localized status scenarios remain contained without document overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root class, style, slot, scoped appearance, and public component-token overrides remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /avatar workbench exposes overview, all sizes, both shapes, all statuses, and loaded/broken/missing source states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informative/decorative/control contexts, NotificationBadge/native-image targets, appearance, customization, mobile stress, and RTL are deterministic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest and Testing Library cover defaults, informative/decorative fallback, loaded/error paths, closed metadata, native props, event, ref, and ReactNode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types require alt/fallback, accept native/loading props, and reject invalid size, shape, status, color, badge, parts, and Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node boundary/export/CSS/declaration/SSR checks and dry-pack verification include the Avatar subpath and compiled styles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean React 18/19 packed consumers import root/subpath identity, render informative/decorative SSR fallback, typecheck, and load CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nine focused browser checks cover default/load, dimensions/shapes, status geometry, source states, semantics, composition, mobile/RTL, axe, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical Avatar route has no automatically detectable axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven reviewed Chromium baselines cover sizes, shapes, statuses, dark overview/composition, mobile stress/RTL, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Avatar release-matrix checks pass where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered Avatar protocol covers crop, loading, statuses, composition, keyboard/touch context, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/avatar.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run records every numbered result and corrects any finding before package completion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owner manual review intentionally deferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRA-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Drawer guide covers role, imports, anatomy, API, placement, mobile sizes, tokens, responsive behavior, accessibility, composition, and gesture exclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/drawer/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRA-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawer and package changelogs record the public component, mobile sizing, evidence, and named gesture follow-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/drawer/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRA-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer composes a public-subpath project-filter workflow and passes boundary, production, desktop/mobile interaction, layout, focus, and axe gates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRA-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Drawer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Core Drawer remains until Sidebar stops importing DrawerContentBase and a later authorized cutover removes source, types, defaults, exports, CSS, and dead declarations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidebar imports DrawerContentBase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badge Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted passive Badge and attached NotificationBadge family, package proof, Consumer cutover, and completed dependency-led Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badge directly composes the public Atom 0.3.3 Badge subpath without Core, framework, or local behavior wrappers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/badge/Badge.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-approved Atom audit and released 0.3.3 server-safety patch cover semantic span output, native forwarding, ref, composition, and slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/badge-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and badge-subpath exports, declarations, required children, and all closed unions match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default passive span emits stable class/slot plus soft, neutral, medium, and rounded metadata without invented role, state, or focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/badge.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft, solid, and outline variants; six tones; three sizes; and rounded/pill shapes are complete and reject arbitrary color/radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Children, native props/events, class, style, ref, slot override, asChild, and render composition preserve Atom ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accessibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive Badge adds no role, live region, tab stop, disabled, selected, removable, or interactive behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NotificationBadge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrapper requires one React element child and emits stable wrapper/indicator slots without mutating child semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formatting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count formatting covers one-digit circles, multi-digit pills, configurable maximum, and overflow labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dot, showZero, zero suppression, and invisible state preserve layout while controlling indicator visibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four logical placements, circular/rectangular overlap, and three indicator sizes emit closed metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicator is aria-hidden and pointer-inert; owning content retains the full localized count/status name without automatic live announcements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/badge.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled layered CSS uses Brick classes, semantic tokens, logical properties, and public component variables without global leakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/badge/badge.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewed light and dark matrices preserve tone, variant, inline hierarchy, count, dot, and anchor geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced-colors emulation preserves explicit system boundaries for inline and attached indicators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logical start/end placement mirrors in RTL without physical-position props</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constrained, localized, mixed-direction, long-token, and inline-baseline scenarios stay contained without document overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interaction boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicator does not intercept pointer input or obscure the anchor focus ring; the owning control preserves at least a 44px target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class, style, slot, scoped appearance, and semantic/component-token overrides remain local and inspectable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The /badge workbench exposes defaults, complete recipes, shapes, sizes, passive-tag routing, and real contexts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counts, dots, maximum, zero, invisible, placements, overlap, icon/navigation/Avatar anchors, and contextual names are deterministic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light/dark, customization, localization, RTL, constrained width, stress, and forced-colors inspection anchors exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest and Testing Library cover defaults, recipes, native props, ref, composition, slots, and passive semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest covers count/dot union, formatting, visibility, placements, overlap, sizes, arbitrary element targets, and pointer ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, tones, shapes, counts, children, and Chip-like APIs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node boundary, package export, server markup, stylesheet, declaration, and dry-pack checks include both Badge components</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit Atom Badge subpath remains server-safe and clean React 18/19 packed consumers import, render, and load CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strict typecheck, build, CSS report, and 100% Brick component-source coverage pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browser checks cover recipes, formatting, focus/pointer ownership, RTL, stress, axe, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical Badge route has no automatically detectable axe violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven reviewed Chromium baselines cover recipes, dark geometry, inline alignment, localization/RTL, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Badge release-matrix checks pass where applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered Badge manual protocol covers hierarchy, recipes, zoom, VoiceOver, direction, system colors, touch/focus context, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/badge.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest owner run records every numbered Badge and NotificationBadge result and corrects any finding before package completion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide covers both roles, use/avoid boundaries, recipes, formatting, accessibility context, composition, responsiveness, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/badge/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badge component changelog records the initial public contract, Atom 0.3.3 boundary, and evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/badge/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer uses public Badge and NotificationBadge subpaths and passes production, boundary, desktop/mobile, focus, layout, dark, and axe checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh search after Avatar removal found no Core Badge dependent; source, types, defaults, resolver, base alias, and barrel export are removed and Core builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAD-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chip / Tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic Chip, removable Tag, actions, and persistent selections remain excluded and route to Badge, Button, or future Toggle/Tag work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted direct Avatar, explicit image/fallback semantics, status-ring geometry, package proof, Consumer cutover, and completed Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar directly composes the public Atom 0.3.3 Avatar subpath without Core, framework, or local behavior wrappers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/avatar/Avatar.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-approved capability audit confirms Atom owns loading/error state, source preload, delayed fallback, native image semantics, and status callback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/avatar-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and avatar-subpath exports, declarations, required alt/fallback, optional src, and closed size/shape/status unions match the brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest fallback-only render emits a passive span with stable class/slot and md/circle defaults without leaked visual props or root role/tab stop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/avatar.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One source reaches Atom Root and Image; loaded native image preserves src, required alt, crop hook, and mutual exclusion with fallback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fallback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informative fallback exposes role img and the full alt label; deliberate empty alt makes loaded and fallback imagery decorative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Successful and failed deterministic sources switch between Image and explicit fallback while preserving the frame and accessible identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallbackDelayMs and onLoadingStatusChange remain public Atom-owned inputs; loading and loaded callback states pass through Brick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native span attributes, ARIA/data attributes, event, class, style, overridable slot, ReactNode fallback, and HTMLSpanElement ref are preserved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five exact square sizes map to 24, 32, 40, 48, and 64 CSS pixels without responsive mutation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/avatar.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circle and rounded shapes are closed recipes; image/fallback clipping and external ring inherit the selected radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online, away, busy, and offline map to success, warning, danger, and neutral semantic rings; absent status has no status metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layered external ring follows both shapes without changing 48px test dimensions, adding semantic DOM, or intercepting input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar stays passive; informative/decorative contexts and Avatar inside a named control avoid duplicate focus and speech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visible localized text communicates each status; ring color is reinforcement and no automatic live announcement is added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NotificationBadge wraps Avatar and a native image; a distinct count/dot coexists without obscuring Avatar status geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled layered CSS uses Brick classes, semantic tokens, fixed logical geometry, and documented component variables without global leakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/avatar/avatar.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewed light/dark fallback, loaded image, shape, status, and NotificationBadge compositions preserve hierarchy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced-colors emulation preserves an explicit system frame and shape-following status outline while visible text keeps exact meaning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constrained mobile, RTL, non-Latin fallback, and long localized status scenarios remain contained without document overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root class, style, slot, scoped appearance, and public component-token overrides remain local and inspectable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The /avatar workbench exposes overview, all sizes, both shapes, all statuses, and loaded/broken/missing source states</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informative/decorative/control contexts, NotificationBadge/native-image targets, appearance, customization, mobile stress, and RTL are deterministic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest and Testing Library cover defaults, informative/decorative fallback, loaded/error paths, closed metadata, native props, event, ref, and ReactNode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public root/subpath types require alt/fallback, accept native/loading props, and reject invalid size, shape, status, color, badge, parts, and Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node boundary/export/CSS/declaration/SSR checks and dry-pack verification include the Avatar subpath and compiled styles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean React 18/19 packed consumers import root/subpath identity, render informative/decorative SSR fallback, typecheck, and load CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nine focused browser checks cover default/load, dimensions/shapes, status geometry, source states, semantics, composition, mobile/RTL, axe, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical Avatar route has no automatically detectable axe violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven reviewed Chromium baselines cover sizes, shapes, statuses, dark overview/composition, mobile stress/RTL, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone Avatar release-matrix checks pass where applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered Avatar protocol covers crop, loading, statuses, composition, keyboard/touch context, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/avatar.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest owner run records every numbered result and corrects any finding before package completion</t>
   </si>
   <si>
     <t xml:space="preserve">AVA-35</t>
@@ -4597,7 +4597,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4619,7 +4618,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4642,7 +4640,6 @@
     <tableColumn id="13" name="Retirement gate"/>
     <tableColumn id="14" name="Status"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4664,7 +4661,6 @@
     <tableColumn id="12" name="Weight"/>
     <tableColumn id="13" name="Resolved"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4675,7 +4671,6 @@
     <tableColumn id="1" name="Topic"/>
     <tableColumn id="2" name="Rule"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4923,21 +4918,21 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIF(N8:N20,"complete")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">SUM(H8:H20)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B20,J8:J20)/SUM(B8:B20),0)</f>
-        <v>0.901234567901235</v>
+        <v>0.917695473251029</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5169,7 +5164,7 @@
       </c>
       <c r="D11" s="8" t="n">
         <f aca="false">COUNTIF(AlertDialog!H9:H47,"partial")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
         <f aca="false">COUNTIF(AlertDialog!H9:H47,"implemented")</f>
@@ -5181,7 +5176,7 @@
       </c>
       <c r="G11" s="8" t="n">
         <f aca="false">COUNTIF(AlertDialog!H9:H47,"verified")</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H11" s="8" t="n">
         <f aca="false">COUNTIF(AlertDialog!H9:H47,"blocked")</f>
@@ -5193,11 +5188,11 @@
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">IFERROR(SUM(AlertDialog!M9:M47)/SUM(AlertDialog!L9:L47),0)</f>
-        <v>0.794871794871795</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="K11" s="8" t="str">
         <f aca="false">IF(COUNTIFS(AlertDialog!E9:E47,"package",AlertDialog!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L11" s="8" t="str">
         <f aca="false">IF(COUNTIFS(AlertDialog!E9:E47,"consumer",AlertDialog!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5226,7 +5221,7 @@
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"implemented")</f>
@@ -5242,7 +5237,7 @@
       </c>
       <c r="H12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"blocked")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"not applicable")</f>
@@ -5283,7 +5278,7 @@
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">COUNTIF(Badge!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">COUNTIF(Badge!H9:H47,"implemented")</f>
@@ -5295,7 +5290,7 @@
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">COUNTIF(Badge!H9:H47,"verified")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">COUNTIF(Badge!H9:H47,"blocked")</f>
@@ -5307,11 +5302,11 @@
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">IFERROR(SUM(Badge!M9:M47)/SUM(Badge!L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="K13" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Badge!E9:E47,"package",Badge!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L13" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Badge!E9:E47,"consumer",Badge!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5323,7 +5318,7 @@
       </c>
       <c r="N13" s="1" t="str">
         <f aca="false">IF(H13&gt;0,"blocked",IF(AND(J13=1,K13="complete",L13="complete",M13="complete"),"complete",IF(J13=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5802,7 +5797,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5819,7 +5814,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5938,7 +5933,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>69</v>
@@ -5947,7 +5942,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>71</v>
@@ -5956,7 +5951,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>74</v>
@@ -5978,7 +5973,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>77</v>
@@ -5987,7 +5982,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>71</v>
@@ -5996,7 +5991,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>81</v>
@@ -6018,7 +6013,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>69</v>
@@ -6027,7 +6022,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>71</v>
@@ -6058,7 +6053,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>49</v>
@@ -6067,7 +6062,7 @@
         <v>179</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>71</v>
@@ -6076,7 +6071,7 @@
         <v>119</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>74</v>
@@ -6098,16 +6093,16 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>643</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>644</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>71</v>
@@ -6116,7 +6111,7 @@
         <v>119</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>74</v>
@@ -6138,16 +6133,16 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>646</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>647</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>71</v>
@@ -6156,7 +6151,7 @@
         <v>119</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>74</v>
@@ -6178,16 +6173,16 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>648</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>649</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>71</v>
@@ -6196,7 +6191,7 @@
         <v>119</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>74</v>
@@ -6218,16 +6213,16 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>71</v>
@@ -6236,7 +6231,7 @@
         <v>119</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>74</v>
@@ -6258,7 +6253,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>69</v>
@@ -6267,7 +6262,7 @@
         <v>179</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>71</v>
@@ -6276,7 +6271,7 @@
         <v>119</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>74</v>
@@ -6298,7 +6293,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>91</v>
@@ -6307,7 +6302,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>71</v>
@@ -6316,7 +6311,7 @@
         <v>119</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>74</v>
@@ -6338,7 +6333,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>91</v>
@@ -6347,7 +6342,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>71</v>
@@ -6356,7 +6351,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>74</v>
@@ -6378,7 +6373,7 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>18</v>
@@ -6387,7 +6382,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>71</v>
@@ -6396,7 +6391,7 @@
         <v>119</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>74</v>
@@ -6418,7 +6413,7 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>18</v>
@@ -6427,7 +6422,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>71</v>
@@ -6436,7 +6431,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>74</v>
@@ -6458,16 +6453,16 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>71</v>
@@ -6476,7 +6471,7 @@
         <v>119</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>74</v>
@@ -6498,16 +6493,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>71</v>
@@ -6516,7 +6511,7 @@
         <v>100</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>74</v>
@@ -6538,16 +6533,16 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="C24" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>669</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>670</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>71</v>
@@ -6556,7 +6551,7 @@
         <v>119</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>74</v>
@@ -6578,7 +6573,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>91</v>
@@ -6587,7 +6582,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>71</v>
@@ -6596,7 +6591,7 @@
         <v>72</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>74</v>
@@ -6618,7 +6613,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>91</v>
@@ -6627,13 +6622,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>130</v>
@@ -6658,7 +6653,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>91</v>
@@ -6667,7 +6662,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>71</v>
@@ -6676,7 +6671,7 @@
         <v>119</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>74</v>
@@ -6698,7 +6693,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>91</v>
@@ -6707,7 +6702,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>71</v>
@@ -6716,7 +6711,7 @@
         <v>119</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>74</v>
@@ -6738,16 +6733,16 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>71</v>
@@ -6756,7 +6751,7 @@
         <v>100</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>74</v>
@@ -6778,7 +6773,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>98</v>
@@ -6787,7 +6782,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>71</v>
@@ -6796,7 +6791,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>74</v>
@@ -6818,7 +6813,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>98</v>
@@ -6827,7 +6822,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>71</v>
@@ -6836,7 +6831,7 @@
         <v>100</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>74</v>
@@ -6858,7 +6853,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>117</v>
@@ -6867,7 +6862,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>71</v>
@@ -6876,7 +6871,7 @@
         <v>119</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>74</v>
@@ -6898,7 +6893,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>117</v>
@@ -6907,7 +6902,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>71</v>
@@ -6938,7 +6933,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>117</v>
@@ -6947,7 +6942,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>71</v>
@@ -6956,7 +6951,7 @@
         <v>119</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>74</v>
@@ -6978,7 +6973,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>117</v>
@@ -6987,7 +6982,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>71</v>
@@ -7018,7 +7013,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>117</v>
@@ -7027,7 +7022,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>71</v>
@@ -7036,7 +7031,7 @@
         <v>119</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>74</v>
@@ -7058,7 +7053,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>117</v>
@@ -7067,7 +7062,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>71</v>
@@ -7076,7 +7071,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -7098,7 +7093,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>117</v>
@@ -7107,7 +7102,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>71</v>
@@ -7116,7 +7111,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -7138,7 +7133,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>117</v>
@@ -7147,13 +7142,13 @@
         <v>25</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>130</v>
@@ -7178,7 +7173,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>117</v>
@@ -7187,7 +7182,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>71</v>
@@ -7218,7 +7213,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>138</v>
@@ -7227,7 +7222,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>71</v>
@@ -7236,7 +7231,7 @@
         <v>140</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>74</v>
@@ -7258,7 +7253,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>138</v>
@@ -7267,7 +7262,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>71</v>
@@ -7276,7 +7271,7 @@
         <v>140</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>346</v>
@@ -7286,7 +7281,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -7461,7 +7456,7 @@
         <v>719</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>720</v>
@@ -7476,7 +7471,7 @@
         <v>79</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>81</v>
@@ -7795,7 +7790,7 @@
         <v>77</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>728</v>
@@ -7835,7 +7830,7 @@
         <v>69</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>731</v>
@@ -8272,7 +8267,7 @@
         <v>762</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>757</v>
@@ -8284,7 +8279,7 @@
         <v>71</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>130</v>
@@ -8312,7 +8307,7 @@
         <v>764</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>757</v>
@@ -8324,7 +8319,7 @@
         <v>71</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>130</v>
@@ -8392,10 +8387,10 @@
         <v>769</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>770</v>
@@ -8435,7 +8430,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>772</v>
@@ -8475,7 +8470,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>775</v>
@@ -8484,7 +8479,7 @@
         <v>71</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>130</v>
@@ -8515,7 +8510,7 @@
         <v>91</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>777</v>
@@ -8555,7 +8550,7 @@
         <v>779</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>780</v>
@@ -8592,10 +8587,10 @@
         <v>781</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>782</v>
@@ -8607,7 +8602,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>74</v>
@@ -8635,7 +8630,7 @@
         <v>98</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>784</v>
@@ -8647,7 +8642,7 @@
         <v>100</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>74</v>
@@ -8675,7 +8670,7 @@
         <v>117</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>786</v>
@@ -8715,7 +8710,7 @@
         <v>117</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>788</v>
@@ -8755,7 +8750,7 @@
         <v>117</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>790</v>
@@ -8767,7 +8762,7 @@
         <v>119</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>74</v>
@@ -8795,7 +8790,7 @@
         <v>117</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>792</v>
@@ -8835,7 +8830,7 @@
         <v>117</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>794</v>
@@ -8875,7 +8870,7 @@
         <v>117</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>796</v>
@@ -8915,7 +8910,7 @@
         <v>117</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>798</v>
@@ -8955,7 +8950,7 @@
         <v>117</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>800</v>
@@ -8964,7 +8959,7 @@
         <v>71</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>130</v>
@@ -8995,7 +8990,7 @@
         <v>117</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>802</v>
@@ -9035,7 +9030,7 @@
         <v>138</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>804</v>
@@ -9075,7 +9070,7 @@
         <v>138</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>807</v>
@@ -9097,7 +9092,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -9195,7 +9190,7 @@
         <v>152</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>815</v>
@@ -9272,10 +9267,10 @@
         <v>819</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>820</v>
@@ -9853,7 +9848,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>130</v>
@@ -9893,7 +9888,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>130</v>
@@ -9921,7 +9916,7 @@
         <v>847</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>27</v>
@@ -10013,7 +10008,7 @@
         <v>71</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>130</v>
@@ -10041,7 +10036,7 @@
         <v>854</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>27</v>
@@ -10081,7 +10076,7 @@
         <v>856</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>27</v>
@@ -10133,7 +10128,7 @@
         <v>71</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>130</v>
@@ -10241,7 +10236,7 @@
         <v>866</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>27</v>
@@ -10256,7 +10251,7 @@
         <v>100</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>74</v>
@@ -10336,7 +10331,7 @@
         <v>100</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>74</v>
@@ -10456,7 +10451,7 @@
         <v>119</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>74</v>
@@ -10653,7 +10648,7 @@
         <v>71</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>130</v>
@@ -10748,7 +10743,7 @@
         <v>46221</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L38" s="18" t="n">
         <v>1</v>
@@ -10910,7 +10905,7 @@
         <v>46221</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -10967,7 +10962,7 @@
         <v>909</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>27</v>
@@ -11062,7 +11057,7 @@
         <v>72</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>74</v>
@@ -11908,7 +11903,7 @@
         <v>71</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>130</v>
@@ -11948,7 +11943,7 @@
         <v>71</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>130</v>
@@ -11976,7 +11971,7 @@
         <v>962</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>938</v>
@@ -11988,7 +11983,7 @@
         <v>71</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>130</v>
@@ -12016,7 +12011,7 @@
         <v>964</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>28</v>
@@ -12031,7 +12026,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>74</v>
@@ -12136,7 +12131,7 @@
         <v>970</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>28</v>
@@ -12188,7 +12183,7 @@
         <v>71</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>130</v>
@@ -12216,7 +12211,7 @@
         <v>974</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>28</v>
@@ -12231,7 +12226,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>74</v>
@@ -12311,7 +12306,7 @@
         <v>100</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>74</v>
@@ -12431,7 +12426,7 @@
         <v>119</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>74</v>
@@ -12628,7 +12623,7 @@
         <v>71</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>130</v>
@@ -12721,7 +12716,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -12896,7 +12891,7 @@
         <v>1009</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>28</v>
@@ -13923,7 +13918,7 @@
         <v>71</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>1064</v>
@@ -13965,7 +13960,7 @@
         <v>71</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>1064</v>
@@ -14007,7 +14002,7 @@
         <v>71</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>1064</v>
@@ -14283,7 +14278,7 @@
         <v>1087</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>29</v>
@@ -14338,7 +14333,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -14378,7 +14373,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -14538,7 +14533,7 @@
         <v>72</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>74</v>
@@ -14550,7 +14545,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -15725,7 +15720,7 @@
         <v>71</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>1175</v>
@@ -15767,7 +15762,7 @@
         <v>71</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>1175</v>
@@ -15809,7 +15804,7 @@
         <v>71</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>1175</v>
@@ -16047,7 +16042,7 @@
         <v>1190</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>30</v>
@@ -16089,7 +16084,7 @@
         <v>1192</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>268</v>
@@ -16146,7 +16141,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -16186,7 +16181,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -16358,7 +16353,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>518</v>
+        <v>707</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -16388,7 +16383,7 @@
         <v>72</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>74</v>
@@ -17729,7 +17724,7 @@
         <v>71</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>1281</v>
@@ -17771,7 +17766,7 @@
         <v>71</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>1281</v>
@@ -17967,7 +17962,7 @@
         <v>1293</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>31</v>
@@ -18022,7 +18017,7 @@
         <v>119</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>74</v>
@@ -18062,7 +18057,7 @@
         <v>119</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>74</v>
@@ -18222,7 +18217,7 @@
         <v>72</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>74</v>
@@ -23301,14 +23296,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.794871794871795</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -23322,7 +23317,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -23853,26 +23848,26 @@
         <v>376</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J20" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K20" s="15"/>
       <c r="L20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="18" t="n">
         <f aca="false">IF(H20="not applicable",IF(K20&lt;&gt;"",1,0),IF(I20="yes",IF(H20="verified",1,0),IF(OR(H20="tested",H20="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>49</v>
@@ -23881,7 +23876,7 @@
         <v>199</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>71</v>
@@ -23893,35 +23888,35 @@
         <v>376</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J21" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K21" s="15"/>
       <c r="L21" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="18" t="n">
         <f aca="false">IF(H21="not applicable",IF(K21&lt;&gt;"",1,0),IF(I21="yes",IF(H21="verified",1,0),IF(OR(H21="tested",H21="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>381</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>382</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>71</v>
@@ -23930,7 +23925,7 @@
         <v>119</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>74</v>
@@ -23952,7 +23947,7 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>49</v>
@@ -23961,7 +23956,7 @@
         <v>192</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>71</v>
@@ -23970,7 +23965,7 @@
         <v>119</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>74</v>
@@ -23992,7 +23987,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>91</v>
@@ -24001,7 +23996,7 @@
         <v>175</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>71</v>
@@ -24010,7 +24005,7 @@
         <v>72</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>74</v>
@@ -24032,7 +24027,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>91</v>
@@ -24041,7 +24036,7 @@
         <v>196</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>71</v>
@@ -24053,26 +24048,26 @@
         <v>376</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J25" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K25" s="15"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="18" t="n">
         <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>98</v>
@@ -24081,7 +24076,7 @@
         <v>175</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>71</v>
@@ -24090,7 +24085,7 @@
         <v>100</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>74</v>
@@ -24112,7 +24107,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>98</v>
@@ -24121,7 +24116,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>71</v>
@@ -24152,7 +24147,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>98</v>
@@ -24161,7 +24156,7 @@
         <v>196</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>71</v>
@@ -24192,7 +24187,7 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>98</v>
@@ -24213,26 +24208,26 @@
         <v>376</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J29" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K29" s="15"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="18" t="n">
         <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>98</v>
@@ -24253,26 +24248,26 @@
         <v>376</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J30" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K30" s="15"/>
       <c r="L30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M30" s="18" t="n">
         <f aca="false">IF(H30="not applicable",IF(K30&lt;&gt;"",1,0),IF(I30="yes",IF(H30="verified",1,0),IF(OR(H30="tested",H30="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>98</v>
@@ -24281,7 +24276,7 @@
         <v>175</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>71</v>
@@ -24293,26 +24288,26 @@
         <v>376</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J31" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K31" s="15"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="18" t="n">
         <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>98</v>
@@ -24321,7 +24316,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>71</v>
@@ -24352,7 +24347,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>117</v>
@@ -24361,7 +24356,7 @@
         <v>175</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>71</v>
@@ -24392,7 +24387,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>117</v>
@@ -24401,7 +24396,7 @@
         <v>165</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>71</v>
@@ -24432,7 +24427,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>117</v>
@@ -24441,7 +24436,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>71</v>
@@ -24472,16 +24467,16 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C36" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>411</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>412</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>71</v>
@@ -24512,7 +24507,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>117</v>
@@ -24521,7 +24516,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>71</v>
@@ -24552,7 +24547,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>117</v>
@@ -24561,7 +24556,7 @@
         <v>196</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>71</v>
@@ -24592,7 +24587,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>117</v>
@@ -24632,7 +24627,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>117</v>
@@ -24641,7 +24636,7 @@
         <v>175</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>71</v>
@@ -24672,7 +24667,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>117</v>
@@ -24681,7 +24676,7 @@
         <v>6</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>71</v>
@@ -24712,7 +24707,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>138</v>
@@ -24721,7 +24716,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>71</v>
@@ -24752,7 +24747,7 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>138</v>
@@ -24761,7 +24756,7 @@
         <v>175</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>71</v>
@@ -24773,26 +24768,26 @@
         <v>376</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="15" t="s">
-        <v>377</v>
-      </c>
+      <c r="J43" s="19" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K43" s="15"/>
       <c r="L43" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M43" s="18" t="n">
         <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>144</v>
@@ -24801,7 +24796,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>71</v>
@@ -24810,7 +24805,7 @@
         <v>146</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>74</v>
@@ -24832,7 +24827,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>144</v>
@@ -24841,7 +24836,7 @@
         <v>6</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>71</v>
@@ -24850,7 +24845,7 @@
         <v>146</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>74</v>
@@ -24872,7 +24867,7 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>152</v>
@@ -24881,7 +24876,7 @@
         <v>6</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>154</v>
@@ -24912,16 +24907,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C47" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>435</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>436</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>159</v>
@@ -24938,9 +24933,11 @@
       <c r="I47" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="19"/>
+      <c r="J47" s="19" t="n">
+        <v>46222</v>
+      </c>
       <c r="K47" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>
@@ -25067,7 +25064,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25084,7 +25081,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -25126,7 +25123,7 @@
       </c>
       <c r="H4" s="5" t="n">
         <f aca="false">COUNTIF(H9:H47,"blocked")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -25203,7 +25200,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>69</v>
@@ -25212,7 +25209,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>71</v>
@@ -25221,7 +25218,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>74</v>
@@ -25243,7 +25240,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>77</v>
@@ -25252,7 +25249,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>71</v>
@@ -25261,7 +25258,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>81</v>
@@ -25283,7 +25280,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>77</v>
@@ -25292,7 +25289,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>71</v>
@@ -25301,7 +25298,7 @@
         <v>79</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>81</v>
@@ -25323,7 +25320,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>69</v>
@@ -25332,7 +25329,7 @@
         <v>165</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>71</v>
@@ -25363,7 +25360,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>49</v>
@@ -25372,7 +25369,7 @@
         <v>179</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>71</v>
@@ -25381,7 +25378,7 @@
         <v>119</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>74</v>
@@ -25403,7 +25400,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>49</v>
@@ -25412,7 +25409,7 @@
         <v>268</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>71</v>
@@ -25421,7 +25418,7 @@
         <v>119</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>74</v>
@@ -25443,7 +25440,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>49</v>
@@ -25452,7 +25449,7 @@
         <v>271</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>71</v>
@@ -25461,7 +25458,7 @@
         <v>119</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>74</v>
@@ -25483,7 +25480,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>49</v>
@@ -25492,7 +25489,7 @@
         <v>275</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>71</v>
@@ -25501,7 +25498,7 @@
         <v>119</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>74</v>
@@ -25523,7 +25520,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>49</v>
@@ -25532,7 +25529,7 @@
         <v>196</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>71</v>
@@ -25541,7 +25538,7 @@
         <v>119</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>74</v>
@@ -25563,7 +25560,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>49</v>
@@ -25572,7 +25569,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>71</v>
@@ -25581,7 +25578,7 @@
         <v>119</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>74</v>
@@ -25603,7 +25600,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>49</v>
@@ -25612,7 +25609,7 @@
         <v>186</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>71</v>
@@ -25621,7 +25618,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>74</v>
@@ -25643,7 +25640,7 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>49</v>
@@ -25652,7 +25649,7 @@
         <v>189</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>71</v>
@@ -25661,7 +25658,7 @@
         <v>119</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>74</v>
@@ -25683,7 +25680,7 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>49</v>
@@ -25692,7 +25689,7 @@
         <v>287</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>71</v>
@@ -25701,7 +25698,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>74</v>
@@ -25723,7 +25720,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>49</v>
@@ -25732,7 +25729,7 @@
         <v>199</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>71</v>
@@ -25741,7 +25738,7 @@
         <v>119</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>74</v>
@@ -25763,7 +25760,7 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>49</v>
@@ -25772,7 +25769,7 @@
         <v>293</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>71</v>
@@ -25781,7 +25778,7 @@
         <v>119</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>74</v>
@@ -25803,7 +25800,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>49</v>
@@ -25812,7 +25809,7 @@
         <v>296</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>71</v>
@@ -25821,7 +25818,7 @@
         <v>119</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>74</v>
@@ -25843,7 +25840,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>91</v>
@@ -25852,7 +25849,7 @@
         <v>196</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>71</v>
@@ -25861,7 +25858,7 @@
         <v>119</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>74</v>
@@ -25883,7 +25880,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>91</v>
@@ -25892,7 +25889,7 @@
         <v>196</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>71</v>
@@ -25901,7 +25898,7 @@
         <v>119</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>74</v>
@@ -25923,7 +25920,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>91</v>
@@ -25932,7 +25929,7 @@
         <v>196</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>71</v>
@@ -25941,7 +25938,7 @@
         <v>119</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>74</v>
@@ -25963,7 +25960,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>91</v>
@@ -25972,13 +25969,13 @@
         <v>175</v>
       </c>
       <c r="D28" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>484</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>485</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>130</v>
@@ -26003,7 +26000,7 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>91</v>
@@ -26012,13 +26009,13 @@
         <v>175</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>130</v>
@@ -26043,7 +26040,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>91</v>
@@ -26052,7 +26049,7 @@
         <v>196</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>71</v>
@@ -26061,7 +26058,7 @@
         <v>119</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>74</v>
@@ -26070,7 +26067,7 @@
         <v>75</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="18" t="n">
@@ -26083,7 +26080,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>91</v>
@@ -26092,13 +26089,13 @@
         <v>175</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>130</v>
@@ -26123,7 +26120,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>91</v>
@@ -26132,7 +26129,7 @@
         <v>196</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>71</v>
@@ -26141,7 +26138,7 @@
         <v>100</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>74</v>
@@ -26163,7 +26160,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>98</v>
@@ -26172,7 +26169,7 @@
         <v>175</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>71</v>
@@ -26181,7 +26178,7 @@
         <v>100</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>74</v>
@@ -26203,7 +26200,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>98</v>
@@ -26212,7 +26209,7 @@
         <v>175</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>71</v>
@@ -26221,7 +26218,7 @@
         <v>100</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>74</v>
@@ -26243,7 +26240,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>117</v>
@@ -26252,7 +26249,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>71</v>
@@ -26261,7 +26258,7 @@
         <v>119</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>74</v>
@@ -26283,7 +26280,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>117</v>
@@ -26292,7 +26289,7 @@
         <v>165</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>71</v>
@@ -26323,7 +26320,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>117</v>
@@ -26332,7 +26329,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>71</v>
@@ -26341,7 +26338,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -26363,7 +26360,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>117</v>
@@ -26372,7 +26369,7 @@
         <v>6</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>71</v>
@@ -26381,7 +26378,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -26390,7 +26387,7 @@
         <v>75</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="18" t="n">
@@ -26403,7 +26400,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>117</v>
@@ -26412,7 +26409,7 @@
         <v>196</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>71</v>
@@ -26421,7 +26418,7 @@
         <v>119</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>74</v>
@@ -26443,7 +26440,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>117</v>
@@ -26452,13 +26449,13 @@
         <v>175</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>130</v>
@@ -26483,7 +26480,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>117</v>
@@ -26492,7 +26489,7 @@
         <v>6</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>71</v>
@@ -26523,7 +26520,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>138</v>
@@ -26532,7 +26529,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>71</v>
@@ -26541,7 +26538,7 @@
         <v>140</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>74</v>
@@ -26563,7 +26560,7 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>138</v>
@@ -26572,7 +26569,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>71</v>
@@ -26581,17 +26578,19 @@
         <v>140</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>346</v>
+        <v>252</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J43" s="19"/>
+      <c r="J43" s="19" t="n">
+        <v>46222</v>
+      </c>
       <c r="K43" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1</v>
@@ -26603,7 +26602,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>144</v>
@@ -26612,7 +26611,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>71</v>
@@ -26621,7 +26620,7 @@
         <v>146</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>74</v>
@@ -26643,7 +26642,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>144</v>
@@ -26652,7 +26651,7 @@
         <v>6</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>71</v>
@@ -26661,7 +26660,7 @@
         <v>146</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>74</v>
@@ -26683,7 +26682,7 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>152</v>
@@ -26692,7 +26691,7 @@
         <v>6</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>154</v>
@@ -26723,16 +26722,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C47" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>528</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>529</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>159</v>
@@ -26753,7 +26752,7 @@
         <v>46221</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>
@@ -26880,7 +26879,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -26897,7 +26896,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -26925,14 +26924,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -26946,7 +26945,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -27016,7 +27015,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>69</v>
@@ -27025,7 +27024,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>71</v>
@@ -27034,7 +27033,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>74</v>
@@ -27056,16 +27055,16 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>77</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>537</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>538</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>71</v>
@@ -27074,7 +27073,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>81</v>
@@ -27096,16 +27095,16 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>71</v>
@@ -27136,7 +27135,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>49</v>
@@ -27145,7 +27144,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>71</v>
@@ -27154,7 +27153,7 @@
         <v>119</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>74</v>
@@ -27176,7 +27175,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>91</v>
@@ -27185,7 +27184,7 @@
         <v>24</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>71</v>
@@ -27194,7 +27193,7 @@
         <v>119</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>74</v>
@@ -27216,7 +27215,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>69</v>
@@ -27225,7 +27224,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>71</v>
@@ -27234,7 +27233,7 @@
         <v>119</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>74</v>
@@ -27256,16 +27255,16 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>549</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>550</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>71</v>
@@ -27274,7 +27273,7 @@
         <v>119</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>74</v>
@@ -27296,16 +27295,16 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>554</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>71</v>
@@ -27336,16 +27335,16 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="C17" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>556</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>557</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>71</v>
@@ -27354,7 +27353,7 @@
         <v>119</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>74</v>
@@ -27376,16 +27375,16 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>558</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>556</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>559</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>71</v>
@@ -27394,7 +27393,7 @@
         <v>119</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>74</v>
@@ -27416,16 +27415,16 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>561</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>562</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>71</v>
@@ -27434,7 +27433,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>74</v>
@@ -27456,16 +27455,16 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>550</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>71</v>
@@ -27474,7 +27473,7 @@
         <v>119</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>74</v>
@@ -27496,16 +27495,16 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>71</v>
@@ -27514,7 +27513,7 @@
         <v>72</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>74</v>
@@ -27536,22 +27535,22 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>130</v>
@@ -27576,16 +27575,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>71</v>
@@ -27594,7 +27593,7 @@
         <v>119</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>74</v>
@@ -27616,16 +27615,16 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>71</v>
@@ -27634,7 +27633,7 @@
         <v>119</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>74</v>
@@ -27656,16 +27655,16 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>71</v>
@@ -27674,7 +27673,7 @@
         <v>119</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>74</v>
@@ -27696,16 +27695,16 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="C26" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>578</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>579</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>71</v>
@@ -27714,7 +27713,7 @@
         <v>119</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>74</v>
@@ -27736,16 +27735,16 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>580</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C27" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>581</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>537</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>582</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>71</v>
@@ -27754,7 +27753,7 @@
         <v>100</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>74</v>
@@ -27776,16 +27775,16 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>71</v>
@@ -27794,7 +27793,7 @@
         <v>100</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>74</v>
@@ -27816,16 +27815,16 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>71</v>
@@ -27834,7 +27833,7 @@
         <v>100</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>74</v>
@@ -27856,16 +27855,16 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>71</v>
@@ -27874,7 +27873,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>74</v>
@@ -27896,7 +27895,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>117</v>
@@ -27905,7 +27904,7 @@
         <v>24</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>71</v>
@@ -27914,7 +27913,7 @@
         <v>119</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>74</v>
@@ -27936,16 +27935,16 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>71</v>
@@ -27954,7 +27953,7 @@
         <v>119</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>74</v>
@@ -27976,16 +27975,16 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>71</v>
@@ -28016,16 +28015,16 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>71</v>
@@ -28034,7 +28033,7 @@
         <v>119</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>74</v>
@@ -28056,7 +28055,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>117</v>
@@ -28065,7 +28064,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>71</v>
@@ -28096,16 +28095,16 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>71</v>
@@ -28114,7 +28113,7 @@
         <v>119</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>74</v>
@@ -28136,16 +28135,16 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>71</v>
@@ -28154,7 +28153,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -28176,16 +28175,16 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>71</v>
@@ -28194,7 +28193,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -28216,22 +28215,22 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>71</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>130</v>
@@ -28256,16 +28255,16 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>71</v>
@@ -28296,16 +28295,16 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>138</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>71</v>
@@ -28314,7 +28313,7 @@
         <v>140</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>74</v>
@@ -28336,16 +28335,16 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>138</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>71</v>
@@ -28354,38 +28353,38 @@
         <v>140</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="15" t="s">
-        <v>518</v>
-      </c>
+      <c r="J42" s="19" t="n">
+        <v>46223</v>
+      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M42" s="18" t="n">
         <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>144</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>71</v>
@@ -28394,7 +28393,7 @@
         <v>146</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>74</v>
@@ -28416,16 +28415,16 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>144</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>71</v>
@@ -28434,7 +28433,7 @@
         <v>146</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>74</v>
@@ -28456,16 +28455,16 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>152</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>154</v>
@@ -28496,16 +28495,16 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C46" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>623</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>624</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>159</v>
@@ -28536,16 +28535,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="C47" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>627</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>628</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>71</v>
@@ -28554,7 +28553,7 @@
         <v>79</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>81</v>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="1314">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -2182,307 +2182,307 @@
     <t xml:space="preserve">Latest owner run records every numbered result and corrects any finding before package completion</t>
   </si>
   <si>
+    <t xml:space="preserve">AVA-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide covers use boundaries, explicit alt/fallback, sizes, shapes, status meaning, composition, loading, accessibility, native/ref, and CSS hooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/avatar/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar component changelog records the initial direct contract, status rings, evidence, and deferred AvatarGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/avatar/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer uses the public Avatar subpath for loaded and fallback collaborators, visible statuses, and NotificationBadge composition across desktop/mobile and axe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Avatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh searches found no Core consumers; Avatar/AvatarGroup source, aliases, barrel export, and obsolete live examples are removed and Core builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVA-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AvatarGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AvatarGroup remains deliberately excluded until a real grouped-identity workflow defines semantics, order, overflow, hidden members, and Consumer proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle Family Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for adopted Toggle and ToggleGroup APIs, Atom-owned interaction, package proof, Consumer cutover, and completed Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle directly composes public Atom 0.3.3 Toggle.Root without Core, framework, or local behavior state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/toggle/Toggle.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved capability audit confirms Atom owns pressed/value state, activation, disabled semantics, roving focus, orientation, looping, RTL, composition, slots, and refs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/toggle-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and toggle/toggle-group subpath exports, declarations, direct Toggle, compound Group namespace, named parts, and closed unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest Toggle emits a native type=button with stable class/slot, false aria-pressed, off state, and soft/md/rounded defaults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/toggle.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atom-owned uncontrolled pointer, Space, and controlled pressed paths update aria-pressed and onPressedChange without Brick state duplication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native/ARIA/data props, class, style, slot, icon-only metadata, ref, asChild, and render composition are preserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft, outline, and ghost variants; sm/md/lg sizes; rounded/pill shapes; and icon-only geometry form closed recipes without tone or arbitrary radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, hover, active, focus-visible, selected, disabled, and selected-disabled recipes use semantic tokens and preserve native disabled behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/toggle.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ToggleGroup.Root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root emits a named role=group with stable class/slot, separated horizontal layout, soft/md/rounded defaults, and no extra behavior layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discriminated single string and multiple string-array contracts forward controlled/uncontrolled values and narrowed callbacks without a second store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ToggleGroup.Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item requires value, emits native pressed button metadata, preserves disabled/native/composition/ref paths, and exposes only item iconOnly presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ToggleGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One roving Tab stop plus Arrow, Home, End, looping, activation, and disabled-item skipping remain Atom-owned and pass in real browsers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal/vertical orientation metadata drives layout and Atom mirrors horizontal Arrow navigation in RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separated default preserves inter-item gap and natural wrapping for localized multiple filter pills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attached horizontal and vertical groups collapse adjacent borders and apply logical outer radii for rounded and pill shapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fullWidth fills available inline size and distributes items without changing Atom selection behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable visible or explicit icon labels, group naming, aria-pressed, disabled state, and controlled required-view handling preserve understandable semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and documented --brick-toggle variables without global leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/toggle/toggle.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed light/dark baselines preserve neutral rest, accent selected hierarchy, sizes, shapes, and attached/separated group geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors emulation preserves explicit selected, disabled, border, and focus boundaries without color-only state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constrained mobile, long unbroken/localized labels, wrapping, mixed direction, and RTL remain contained without document overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root class, style, slot, scoped appearance, group variables, and component-token overrides remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /toggle workbench exposes overview, complete standalone recipes, sizes/shapes/icons, attached single, separated multiple, vertical/disabled, customization, mobile stress, and RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest and Testing Library cover defaults, recipes, activation, callbacks, native props, refs, disabled paths, composition, and discriminated values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject standalone value, tone, invalid recipes, mismatched multiple values, item recipe overrides, and callable Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node package boundary, export identity, stylesheet, declarations, deterministic SSR, and dry-pack checks include both public subpaths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean packed React 18/19 consumers import root/subpath identities, SSR-render Toggle and ToggleGroup, typecheck, and load compiled CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strict typecheck, production build, CSS report, and 100% Brick component-source line coverage pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven focused browser checks cover standalone activation, recipes, single/multiple state, roving focus, disabled behavior, mobile/RTL, axe, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical Toggle route has no automatically detectable axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven reviewed Chromium baselines cover recipes, sizes/shapes, attached single, dark standalone/multiple, mobile RTL stress, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone focused release-matrix checks pass where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered Toggle protocol covers hierarchy, activation, keyboard/roving focus, selection modes, geometry, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/toggle.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run records every numbered Toggle and ToggleGroup result and corrects any finding before package completion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owner manual review intentionally deferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide covers use boundaries, explicit alt/fallback, sizes, shapes, status meaning, composition, loading, accessibility, native/ref, and CSS hooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/avatar/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar component changelog records the initial direct contract, status rings, evidence, and deferred AvatarGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/avatar/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer uses the public Avatar subpath for loaded and fallback collaborators, visible statuses, and NotificationBadge composition across desktop/mobile and axe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Avatar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh searches found no Core consumers; Avatar/AvatarGroup source, aliases, barrel export, and obsolete live examples are removed and Core builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVA-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvatarGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvatarGroup remains deliberately excluded until a real grouped-identity workflow defines semantics, order, overflow, hidden members, and Consumer proof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle Family Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for adopted Toggle and ToggleGroup APIs, Atom-owned interaction, package proof, Consumer cutover, and completed Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle directly composes public Atom 0.3.3 Toggle.Root without Core, framework, or local behavior state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/toggle/Toggle.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-approved capability audit confirms Atom owns pressed/value state, activation, disabled semantics, roving focus, orientation, looping, RTL, composition, slots, and refs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/toggle-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and toggle/toggle-group subpath exports, declarations, direct Toggle, compound Group namespace, named parts, and closed unions match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest Toggle emits a native type=button with stable class/slot, false aria-pressed, off state, and soft/md/rounded defaults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/toggle.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atom-owned uncontrolled pointer, Space, and controlled pressed paths update aria-pressed and onPressedChange without Brick state duplication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native/ARIA/data props, class, style, slot, icon-only metadata, ref, asChild, and render composition are preserved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft, outline, and ghost variants; sm/md/lg sizes; rounded/pill shapes; and icon-only geometry form closed recipes without tone or arbitrary radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, hover, active, focus-visible, selected, disabled, and selected-disabled recipes use semantic tokens and preserve native disabled behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/toggle.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ToggleGroup.Root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root emits a named role=group with stable class/slot, separated horizontal layout, soft/md/rounded defaults, and no extra behavior layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discriminated single string and multiple string-array contracts forward controlled/uncontrolled values and narrowed callbacks without a second store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ToggleGroup.Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item requires value, emits native pressed button metadata, preserves disabled/native/composition/ref paths, and exposes only item iconOnly presentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ToggleGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One roving Tab stop plus Arrow, Home, End, looping, activation, and disabled-item skipping remain Atom-owned and pass in real browsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal/vertical orientation metadata drives layout and Atom mirrors horizontal Arrow navigation in RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separated default preserves inter-item gap and natural wrapping for localized multiple filter pills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attached horizontal and vertical groups collapse adjacent borders and apply logical outer radii for rounded and pill shapes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fullWidth fills available inline size and distributes items without changing Atom selection behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stable visible or explicit icon labels, group naming, aria-pressed, disabled state, and controlled required-view handling preserve understandable semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and documented --brick-toggle variables without global leakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/toggle/toggle.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewed light/dark baselines preserve neutral rest, accent selected hierarchy, sizes, shapes, and attached/separated group geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced-colors emulation preserves explicit selected, disabled, border, and focus boundaries without color-only state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constrained mobile, long unbroken/localized labels, wrapping, mixed direction, and RTL remain contained without document overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root class, style, slot, scoped appearance, group variables, and component-token overrides remain local and inspectable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The /toggle workbench exposes overview, complete standalone recipes, sizes/shapes/icons, attached single, separated multiple, vertical/disabled, customization, mobile stress, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest and Testing Library cover defaults, recipes, activation, callbacks, native props, refs, disabled paths, composition, and discriminated values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject standalone value, tone, invalid recipes, mismatched multiple values, item recipe overrides, and callable Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node package boundary, export identity, stylesheet, declarations, deterministic SSR, and dry-pack checks include both public subpaths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean packed React 18/19 consumers import root/subpath identities, SSR-render Toggle and ToggleGroup, typecheck, and load compiled CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strict typecheck, production build, CSS report, and 100% Brick component-source line coverage pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven focused browser checks cover standalone activation, recipes, single/multiple state, roving focus, disabled behavior, mobile/RTL, axe, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical Toggle route has no automatically detectable axe violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven reviewed Chromium baselines cover recipes, sizes/shapes, attached single, dark standalone/multiple, mobile RTL stress, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone focused release-matrix checks pass where applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered Toggle protocol covers hierarchy, activation, keyboard/roving focus, selection modes, geometry, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/toggle.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest owner run records every numbered Toggle and ToggleGroup result and corrects any finding before package completion</t>
   </si>
   <si>
     <t xml:space="preserve">TOG-35</t>
@@ -4273,7 +4273,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4459,22 +4459,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF991B1B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92400E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -4918,7 +4902,7 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIF(N8:N20,"complete")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
@@ -4932,7 +4916,7 @@
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B20,J8:J20)/SUM(B8:B20),0)</f>
-        <v>0.917695473251029</v>
+        <v>0.919753086419753</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5335,7 +5319,7 @@
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">COUNTIF(Avatar!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
         <f aca="false">COUNTIF(Avatar!H9:H47,"implemented")</f>
@@ -5347,7 +5331,7 @@
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">COUNTIF(Avatar!H9:H47,"verified")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="8" t="n">
         <f aca="false">COUNTIF(Avatar!H9:H47,"blocked")</f>
@@ -5359,11 +5343,11 @@
       </c>
       <c r="J14" s="9" t="n">
         <f aca="false">IFERROR(SUM(Avatar!M9:M47)/SUM(Avatar!L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="K14" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Avatar!E9:E47,"package",Avatar!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L14" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Avatar!E9:E47,"consumer",Avatar!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5375,7 +5359,7 @@
       </c>
       <c r="N14" s="1" t="str">
         <f aca="false">IF(H14&gt;0,"blocked",IF(AND(J14=1,K14="complete",L14="complete",M14="complete"),"complete",IF(J14=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5842,14 +5826,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -5863,7 +5847,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -7274,26 +7258,26 @@
         <v>704</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="15" t="s">
-        <v>707</v>
-      </c>
+      <c r="J42" s="19" t="n">
+        <v>46223</v>
+      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M42" s="18" t="n">
         <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>144</v>
@@ -7302,7 +7286,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>71</v>
@@ -7311,7 +7295,7 @@
         <v>146</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>74</v>
@@ -7333,7 +7317,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>144</v>
@@ -7342,7 +7326,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>71</v>
@@ -7351,7 +7335,7 @@
         <v>146</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>74</v>
@@ -7373,7 +7357,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>152</v>
@@ -7382,7 +7366,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>154</v>
@@ -7413,16 +7397,16 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>157</v>
       </c>
       <c r="C46" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>717</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>718</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>159</v>
@@ -7453,16 +7437,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>625</v>
       </c>
       <c r="C47" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>720</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>721</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>71</v>
@@ -7608,7 +7592,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7625,7 +7609,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7744,7 +7728,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>69</v>
@@ -7753,7 +7737,7 @@
         <v>26</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>71</v>
@@ -7762,7 +7746,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>74</v>
@@ -7784,7 +7768,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>77</v>
@@ -7793,7 +7777,7 @@
         <v>536</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>71</v>
@@ -7802,7 +7786,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>81</v>
@@ -7824,7 +7808,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>69</v>
@@ -7833,7 +7817,7 @@
         <v>536</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>71</v>
@@ -7864,7 +7848,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>49</v>
@@ -7873,7 +7857,7 @@
         <v>26</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>71</v>
@@ -7882,7 +7866,7 @@
         <v>119</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>74</v>
@@ -7904,16 +7888,16 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>735</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>736</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>71</v>
@@ -7922,7 +7906,7 @@
         <v>119</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>74</v>
@@ -7944,7 +7928,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>69</v>
@@ -7953,7 +7937,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>71</v>
@@ -7962,7 +7946,7 @@
         <v>119</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>74</v>
@@ -7984,7 +7968,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>91</v>
@@ -7993,7 +7977,7 @@
         <v>26</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>71</v>
@@ -8002,7 +7986,7 @@
         <v>119</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>74</v>
@@ -8024,16 +8008,16 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>742</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>743</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>71</v>
@@ -8042,7 +8026,7 @@
         <v>119</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>74</v>
@@ -8064,16 +8048,16 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>747</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>748</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>71</v>
@@ -8082,7 +8066,7 @@
         <v>119</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>74</v>
@@ -8104,16 +8088,16 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="C18" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>750</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>747</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>751</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>71</v>
@@ -8144,16 +8128,16 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>753</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>754</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>71</v>
@@ -8162,7 +8146,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>74</v>
@@ -8184,16 +8168,16 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>756</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>757</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>758</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>71</v>
@@ -8202,7 +8186,7 @@
         <v>119</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>74</v>
@@ -8224,16 +8208,16 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>759</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="C21" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>760</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>757</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>761</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>71</v>
@@ -8242,7 +8226,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>74</v>
@@ -8264,16 +8248,16 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>560</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>71</v>
@@ -8304,16 +8288,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>560</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>71</v>
@@ -8344,16 +8328,16 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>766</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="C24" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>767</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>757</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>768</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>71</v>
@@ -8362,7 +8346,7 @@
         <v>119</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>74</v>
@@ -8384,7 +8368,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>549</v>
@@ -8393,7 +8377,7 @@
         <v>536</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>71</v>
@@ -8402,7 +8386,7 @@
         <v>119</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>74</v>
@@ -8424,7 +8408,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>91</v>
@@ -8433,7 +8417,7 @@
         <v>536</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>71</v>
@@ -8442,7 +8426,7 @@
         <v>72</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>74</v>
@@ -8464,7 +8448,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>91</v>
@@ -8473,7 +8457,7 @@
         <v>536</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>71</v>
@@ -8504,7 +8488,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>91</v>
@@ -8513,7 +8497,7 @@
         <v>536</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>71</v>
@@ -8522,7 +8506,7 @@
         <v>119</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>74</v>
@@ -8544,16 +8528,16 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>778</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>779</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>536</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>71</v>
@@ -8562,7 +8546,7 @@
         <v>119</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>74</v>
@@ -8584,7 +8568,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>580</v>
@@ -8593,7 +8577,7 @@
         <v>536</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>71</v>
@@ -8624,7 +8608,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>98</v>
@@ -8633,7 +8617,7 @@
         <v>536</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>71</v>
@@ -8664,7 +8648,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>117</v>
@@ -8673,7 +8657,7 @@
         <v>536</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>71</v>
@@ -8682,7 +8666,7 @@
         <v>119</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>74</v>
@@ -8704,7 +8688,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>117</v>
@@ -8713,7 +8697,7 @@
         <v>536</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>71</v>
@@ -8744,7 +8728,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>117</v>
@@ -8753,7 +8737,7 @@
         <v>536</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>71</v>
@@ -8784,7 +8768,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>117</v>
@@ -8793,7 +8777,7 @@
         <v>536</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>71</v>
@@ -8824,7 +8808,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>117</v>
@@ -8833,7 +8817,7 @@
         <v>536</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>71</v>
@@ -8842,7 +8826,7 @@
         <v>119</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>74</v>
@@ -8864,7 +8848,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>117</v>
@@ -8873,7 +8857,7 @@
         <v>536</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>71</v>
@@ -8882,7 +8866,7 @@
         <v>119</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>74</v>
@@ -8904,7 +8888,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>117</v>
@@ -8913,7 +8897,7 @@
         <v>536</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>71</v>
@@ -8922,7 +8906,7 @@
         <v>119</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>74</v>
@@ -8944,7 +8928,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>117</v>
@@ -8953,7 +8937,7 @@
         <v>536</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>71</v>
@@ -8984,7 +8968,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>117</v>
@@ -8993,7 +8977,7 @@
         <v>536</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>71</v>
@@ -9024,7 +9008,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>138</v>
@@ -9033,7 +9017,7 @@
         <v>536</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>71</v>
@@ -9042,7 +9026,7 @@
         <v>140</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>74</v>
@@ -9064,7 +9048,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>138</v>
@@ -9073,7 +9057,7 @@
         <v>536</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>71</v>
@@ -9082,7 +9066,7 @@
         <v>140</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>346</v>
@@ -9092,7 +9076,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -9150,7 +9134,7 @@
         <v>144</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>812</v>
@@ -9282,7 +9266,7 @@
         <v>79</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>81</v>
@@ -9796,7 +9780,7 @@
         <v>841</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>27</v>
@@ -9996,7 +9980,7 @@
         <v>852</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>27</v>
@@ -10196,7 +10180,7 @@
         <v>864</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>27</v>
@@ -10743,7 +10727,7 @@
         <v>46221</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L38" s="18" t="n">
         <v>1</v>
@@ -10905,7 +10889,7 @@
         <v>46221</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -12051,7 +12035,7 @@
         <v>966</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>28</v>
@@ -12091,7 +12075,7 @@
         <v>968</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>28</v>
@@ -12716,7 +12700,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -13740,7 +13724,7 @@
         <v>1049</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>29</v>
@@ -13780,7 +13764,7 @@
         <v>1051</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>29</v>
@@ -14072,7 +14056,7 @@
         <v>1073</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>196</v>
@@ -14112,7 +14096,7 @@
         <v>1075</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>196</v>
@@ -14194,7 +14178,7 @@
         <v>1081</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>29</v>
@@ -14545,7 +14529,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -15462,7 +15446,7 @@
         <v>1158</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>30</v>
@@ -15502,7 +15486,7 @@
         <v>1160</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>30</v>
@@ -15542,7 +15526,7 @@
         <v>1162</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>30</v>
@@ -15582,7 +15566,7 @@
         <v>1164</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>30</v>
@@ -15834,7 +15818,7 @@
         <v>1180</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>196</v>
@@ -15874,7 +15858,7 @@
         <v>1182</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>196</v>
@@ -15958,7 +15942,7 @@
         <v>1186</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>30</v>
@@ -16353,7 +16337,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>707</v>
+        <v>807</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -17512,7 +17496,7 @@
         <v>1267</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>31</v>
@@ -17552,7 +17536,7 @@
         <v>1269</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>31</v>
@@ -17592,7 +17576,7 @@
         <v>1271</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>1272</v>
@@ -17632,7 +17616,7 @@
         <v>1274</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>1275</v>
@@ -17796,7 +17780,7 @@
         <v>1284</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>196</v>
@@ -17836,7 +17820,7 @@
         <v>1286</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>196</v>
@@ -17878,7 +17862,7 @@
         <v>1289</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>31</v>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5160" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5159" uniqueCount="1420">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">TOG-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft, outline, and ghost variants; sm/md/lg sizes; rounded/pill shapes; and icon-only geometry form closed recipes without tone or arbitrary radius</t>
+    <t xml:space="preserve">Solid, soft, outline, and ghost variants; sm/md/lg sizes; rounded/pill shapes; and icon-only geometry form closed recipes without tone or arbitrary radius</t>
   </si>
   <si>
     <t xml:space="preserve">TOG-08</t>
@@ -2486,265 +2486,265 @@
     <t xml:space="preserve">Latest owner run records every numbered Toggle and ToggleGroup result and corrects any finding before package completion</t>
   </si>
   <si>
+    <t xml:space="preserve">TOG-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Toggle guide covers role boundaries, stable labels, behavior/native/ref contract, visual API, accessibility, CSS hooks, and preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/toggle/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public ToggleGroup guide and both changelogs cover discriminated selection, naming, keyboard, separated/attached/full-width geometry, ownership, and evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/toggle-group/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer uses public Toggle and ToggleGroup subpaths for appearance and Cards/List view and passes production, boundary, desktop/mobile, state, layout, and axe checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Toggle family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh searches found no live dependents; Core Toggle/ToggleGroup sources and input-barrel exports are removed and Core builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOG-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tone, generic Chip/Tag, required single-selection behavior, item-level recipe overrides, navigation, disclosure, and form-setting semantics remain deliberately excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconButton Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted IconButton API, Atom-owned action/link behavior, package proof, Consumer integration, and non-applicable legacy slice retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconButton directly styles public Atom 0.3.3 Button.Root without Core, framework, or local behavior state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/icon-button/IconButton.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved audit confirms IconButton is an icon-only Button specialization and no separate IconLink is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/icon-button-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and icon-button subpath exports, declarations, direct component, closed recipes, and inherited native contracts match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest action emits one native button with stable class/slot and ghost/neutral/md/rounded defaults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/icon-button-app-bar.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every icon-only action requires an accessible name supplied by aria-label or aria-labelledby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/icon-button-app-bar.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">href renders a genuine anchor and preserves target plus safe rel behavior through Atom Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pointer, keyboard, onPress, disabled, loading, native props, composition, and refs remain Atom-owned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solid, soft, outline, and ghost variants form a closed presentation matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral, accent, info, success, warning, and danger tones use semantic Brick tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xs through xl sizes retain square hit geometry and rounded/circle shapes without arbitrary radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The visual icon is presentation-only while the control name remains on the interactive element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, hover, active, focus-visible, disabled, and loading recipes remain visibly distinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading retains the accessible name, exposes Atom busy state, and replaces only the visual icon with a spinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus visibility, native disabled semantics, link semantics, and named controls pass real-browser and axe checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed light and dark baselines preserve hierarchy and icon contrast across variants and tones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors preserves boundaries and loading indication; reduced-motion slows spinner animation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrow mobile and RTL stress examples remain contained without changing square control geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class, style, slot, scoped appearance, and documented component variables remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and no global leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/icon-button/icon-button.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /icon-button workbench exposes overview, variants, tones, sizes, shapes, disabled/loading/link states, mobile stress, and RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest covers defaults, recipes, links, events, disabled/loading behavior, composition, and refs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, tones, sizes, and shapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node boundary, export identity, stylesheet, declarations, SSR, and dry-pack checks include the icon-button subpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean packed React 18/19 consumers import, SSR-render, typecheck, and load IconButton CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strict typecheck, production build, CSS report, and 100% component-source coverage pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused browser checks cover action/link semantics, recipes, inactive states, mobile/RTL, axe, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone release-matrix checks pass where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four reviewed Chromium baselines cover variants, dark tones, forced-colors states, and mobile RTL stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered protocol covers semantics, pointer/keyboard, link, recipes, states, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/icon-button-app-bar.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run records every numbered IconButton result and corrects any finding before package completion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owner manual review intentionally deferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Toggle guide covers role boundaries, stable labels, behavior/native/ref contract, visual API, accessibility, CSS hooks, and preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/toggle/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public ToggleGroup guide and both changelogs cover discriminated selection, naming, keyboard, separated/attached/full-width geometry, ownership, and evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/toggle-group/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer uses public Toggle and ToggleGroup subpaths for appearance and Cards/List view and passes production, boundary, desktop/mobile, state, layout, and axe checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Toggle family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh searches found no live dependents; Core Toggle/ToggleGroup sources and input-barrel exports are removed and Core builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOG-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tone, generic Chip/Tag, required single-selection behavior, item-level recipe overrides, navigation, disclosure, and form-setting semantics remain deliberately excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IconButton Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted IconButton API, Atom-owned action/link behavior, package proof, Consumer integration, and non-applicable legacy slice retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IconButton directly styles public Atom 0.3.3 Button.Root without Core, framework, or local behavior state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/icon-button/IconButton.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-approved audit confirms IconButton is an icon-only Button specialization and no separate IconLink is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/icon-button-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and icon-button subpath exports, declarations, direct component, closed recipes, and inherited native contracts match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest action emits one native button with stable class/slot and ghost/neutral/md/rounded defaults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/icon-button-app-bar.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every icon-only action requires an accessible name supplied by aria-label or aria-labelledby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/icon-button-app-bar.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">href renders a genuine anchor and preserves target plus safe rel behavior through Atom Button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pointer, keyboard, onPress, disabled, loading, native props, composition, and refs remain Atom-owned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solid, soft, outline, and ghost variants form a closed presentation matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neutral, accent, info, success, warning, and danger tones use semantic Brick tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xs through xl sizes retain square hit geometry and rounded/circle shapes without arbitrary radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The visual icon is presentation-only while the control name remains on the interactive element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, hover, active, focus-visible, disabled, and loading recipes remain visibly distinct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loading retains the accessible name, exposes Atom busy state, and replaces only the visual icon with a spinner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus visibility, native disabled semantics, link semantics, and named controls pass real-browser and axe checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewed light and dark baselines preserve hierarchy and icon contrast across variants and tones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced-colors preserves boundaries and loading indication; reduced-motion slows spinner animation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrow mobile and RTL stress examples remain contained without changing square control geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">class, style, slot, scoped appearance, and documented component variables remain local and inspectable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and no global leakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/icon-button/icon-button.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The /icon-button workbench exposes overview, variants, tones, sizes, shapes, disabled/loading/link states, mobile stress, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest covers defaults, recipes, links, events, disabled/loading behavior, composition, and refs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, tones, sizes, and shapes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node boundary, export identity, stylesheet, declarations, SSR, and dry-pack checks include the icon-button subpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean packed React 18/19 consumers import, SSR-render, typecheck, and load IconButton CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strict typecheck, production build, CSS report, and 100% component-source coverage pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focused browser checks cover action/link semantics, recipes, inactive states, mobile/RTL, axe, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit, Pixel, and iPhone release-matrix checks pass where applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four reviewed Chromium baselines cover variants, dark tones, forced-colors states, and mobile RTL stress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered protocol covers semantics, pointer/keyboard, link, recipes, states, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/icon-button-app-bar.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest owner run records every numbered IconButton result and corrects any finding before package completion</t>
   </si>
   <si>
     <t xml:space="preserve">ICB-31</t>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIF(N8:N21,"complete")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B21,J8:J21)/SUM(B8:B21),0)</f>
-        <v>0.916190476190476</v>
+        <v>0.918095238095238</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">COUNTIF(Toggle!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8" t="n">
         <f aca="false">COUNTIF(Toggle!H9:H47,"implemented")</f>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">COUNTIF(Toggle!H9:H47,"verified")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="8" t="n">
         <f aca="false">COUNTIF(Toggle!H9:H47,"blocked")</f>
@@ -5719,11 +5719,11 @@
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">IFERROR(SUM(Toggle!M9:M47)/SUM(Toggle!L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="K15" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Toggle!E9:E47,"package",Toggle!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L15" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Toggle!E9:E47,"consumer",Toggle!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="N15" s="1" t="str">
         <f aca="false">IF(H15&gt;0,"blocked",IF(AND(J15=1,K15="complete",L15="complete",M15="complete"),"complete",IF(J15=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8013,14 +8013,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -8371,7 +8371,7 @@
         <v>76</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="18" t="n">
@@ -9445,26 +9445,26 @@
         <v>805</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="15" t="s">
-        <v>808</v>
-      </c>
+      <c r="J42" s="19" t="n">
+        <v>46223</v>
+      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M42" s="18" t="n">
         <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>145</v>
@@ -9473,7 +9473,7 @@
         <v>26</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -9482,7 +9482,7 @@
         <v>147</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>75</v>
@@ -9504,7 +9504,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>145</v>
@@ -9513,7 +9513,7 @@
         <v>757</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -9522,7 +9522,7 @@
         <v>147</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>75</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>153</v>
@@ -9553,7 +9553,7 @@
         <v>537</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>155</v>
@@ -9584,16 +9584,16 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C46" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>818</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>819</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>160</v>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>626</v>
@@ -9633,7 +9633,7 @@
         <v>537</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>72</v>
@@ -9777,7 +9777,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9794,7 +9794,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9913,7 +9913,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>70</v>
@@ -9922,7 +9922,7 @@
         <v>27</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>72</v>
@@ -9931,7 +9931,7 @@
         <v>73</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>75</v>
@@ -9953,7 +9953,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -9962,7 +9962,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>72</v>
@@ -9971,7 +9971,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>82</v>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>70</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>72</v>
@@ -10033,7 +10033,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>50</v>
@@ -10042,7 +10042,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>72</v>
@@ -10051,7 +10051,7 @@
         <v>120</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>75</v>
@@ -10073,16 +10073,16 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>835</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>836</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>72</v>
@@ -10091,7 +10091,7 @@
         <v>120</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>75</v>
@@ -10113,16 +10113,16 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>839</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>840</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>72</v>
@@ -10131,7 +10131,7 @@
         <v>120</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>75</v>
@@ -10153,7 +10153,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>736</v>
@@ -10162,7 +10162,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>72</v>
@@ -10171,7 +10171,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>75</v>
@@ -10193,7 +10193,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>92</v>
@@ -10202,7 +10202,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>72</v>
@@ -10233,7 +10233,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>92</v>
@@ -10242,7 +10242,7 @@
         <v>27</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>72</v>
@@ -10273,7 +10273,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>561</v>
@@ -10282,7 +10282,7 @@
         <v>27</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>72</v>
@@ -10291,7 +10291,7 @@
         <v>120</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>75</v>
@@ -10313,16 +10313,16 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
+        <v>849</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>850</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>851</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>72</v>
@@ -10331,7 +10331,7 @@
         <v>120</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>75</v>
@@ -10353,7 +10353,7 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>743</v>
@@ -10362,7 +10362,7 @@
         <v>27</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>72</v>
@@ -10393,7 +10393,7 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>649</v>
@@ -10402,7 +10402,7 @@
         <v>27</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>72</v>
@@ -10411,7 +10411,7 @@
         <v>120</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>75</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>550</v>
@@ -10442,7 +10442,7 @@
         <v>27</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>72</v>
@@ -10451,7 +10451,7 @@
         <v>120</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>75</v>
@@ -10473,16 +10473,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>859</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>860</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>72</v>
@@ -10513,16 +10513,16 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
+        <v>861</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>862</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>863</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>72</v>
@@ -10531,7 +10531,7 @@
         <v>120</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>75</v>
@@ -10553,7 +10553,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>779</v>
@@ -10562,7 +10562,7 @@
         <v>27</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>72</v>
@@ -10571,7 +10571,7 @@
         <v>120</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>75</v>
@@ -10593,7 +10593,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>581</v>
@@ -10602,7 +10602,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>72</v>
@@ -10633,7 +10633,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>92</v>
@@ -10642,7 +10642,7 @@
         <v>27</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>72</v>
@@ -10651,7 +10651,7 @@
         <v>73</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>75</v>
@@ -10673,7 +10673,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>99</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>72</v>
@@ -10713,7 +10713,7 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>118</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>72</v>
@@ -10731,7 +10731,7 @@
         <v>120</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>75</v>
@@ -10753,7 +10753,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>118</v>
@@ -10762,7 +10762,7 @@
         <v>27</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>72</v>
@@ -10793,7 +10793,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>118</v>
@@ -10802,7 +10802,7 @@
         <v>27</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>72</v>
@@ -10833,7 +10833,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>118</v>
@@ -10842,7 +10842,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>72</v>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>118</v>
@@ -10882,7 +10882,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>72</v>
@@ -10891,7 +10891,7 @@
         <v>120</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>75</v>
@@ -10913,7 +10913,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>118</v>
@@ -10922,7 +10922,7 @@
         <v>27</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>72</v>
@@ -10931,7 +10931,7 @@
         <v>120</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>75</v>
@@ -10953,7 +10953,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>118</v>
@@ -10962,7 +10962,7 @@
         <v>27</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>72</v>
@@ -10993,7 +10993,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>118</v>
@@ -11002,7 +11002,7 @@
         <v>27</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>72</v>
@@ -11033,7 +11033,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>139</v>
@@ -11042,7 +11042,7 @@
         <v>27</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>72</v>
@@ -11051,7 +11051,7 @@
         <v>141</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>75</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>139</v>
@@ -11082,7 +11082,7 @@
         <v>27</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>72</v>
@@ -11091,7 +11091,7 @@
         <v>141</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>347</v>
@@ -11103,7 +11103,7 @@
         <v>46221</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="L38" s="18" t="n">
         <v>1</v>
@@ -11265,7 +11265,7 @@
         <v>46221</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -11337,7 +11337,7 @@
         <v>80</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>82</v>
@@ -11866,7 +11866,7 @@
         <v>120</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>75</v>
@@ -11906,7 +11906,7 @@
         <v>120</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>75</v>
@@ -11946,7 +11946,7 @@
         <v>120</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>75</v>
@@ -11986,7 +11986,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>75</v>
@@ -12026,7 +12026,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>75</v>
@@ -12066,7 +12066,7 @@
         <v>120</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>75</v>
@@ -12106,7 +12106,7 @@
         <v>120</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>75</v>
@@ -12146,7 +12146,7 @@
         <v>120</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>75</v>
@@ -12186,7 +12186,7 @@
         <v>120</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>75</v>
@@ -12226,7 +12226,7 @@
         <v>120</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>75</v>
@@ -12426,7 +12426,7 @@
         <v>120</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>75</v>
@@ -12466,7 +12466,7 @@
         <v>120</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>75</v>
@@ -12506,7 +12506,7 @@
         <v>120</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>75</v>
@@ -12531,7 +12531,7 @@
         <v>973</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>28</v>
@@ -12706,7 +12706,7 @@
         <v>120</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>75</v>
@@ -12857,7 +12857,7 @@
         <v>28</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>72</v>
@@ -12866,7 +12866,7 @@
         <v>120</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>75</v>
@@ -12906,7 +12906,7 @@
         <v>120</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>75</v>
@@ -12937,7 +12937,7 @@
         <v>28</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>72</v>
@@ -13026,7 +13026,7 @@
         <v>141</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>75</v>
@@ -13066,7 +13066,7 @@
         <v>141</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>347</v>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -14020,7 +14020,7 @@
         <v>1044</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>269</v>
@@ -14060,7 +14060,7 @@
         <v>1048</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>197</v>
@@ -14266,7 +14266,7 @@
         <v>1063</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>197</v>
@@ -14308,7 +14308,7 @@
         <v>1067</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>197</v>
@@ -14350,7 +14350,7 @@
         <v>1069</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>1042</v>
@@ -14596,7 +14596,7 @@
         <v>1085</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>29</v>
@@ -14905,7 +14905,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -15702,7 +15702,7 @@
         <v>1152</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>269</v>
@@ -15742,7 +15742,7 @@
         <v>1155</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>197</v>
@@ -15782,7 +15782,7 @@
         <v>1157</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>197</v>
@@ -16068,7 +16068,7 @@
         <v>1174</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>197</v>
@@ -16110,7 +16110,7 @@
         <v>1177</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>197</v>
@@ -16152,7 +16152,7 @@
         <v>1179</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>1042</v>
@@ -16360,7 +16360,7 @@
         <v>1189</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>30</v>
@@ -16713,7 +16713,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -17752,7 +17752,7 @@
         <v>1258</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>197</v>
@@ -17792,7 +17792,7 @@
         <v>1261</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>183</v>
@@ -18032,7 +18032,7 @@
         <v>1278</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>197</v>
@@ -18072,7 +18072,7 @@
         <v>1280</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>197</v>
@@ -18114,7 +18114,7 @@
         <v>1283</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>1042</v>
@@ -18280,7 +18280,7 @@
         <v>1292</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>31</v>
@@ -19502,7 +19502,7 @@
         <v>1356</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>1332</v>
@@ -19542,7 +19542,7 @@
         <v>1358</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>1335</v>
@@ -19742,7 +19742,7 @@
         <v>1369</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>1318</v>
@@ -20348,7 +20348,7 @@
         <v>1408</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>1318</v>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5159" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5132" uniqueCount="1423">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">DRA-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Implementation directly composes public Atom 0.3.2 Drawer behavior and Modal.Branch without Core or local headless wrappers</t>
+    <t xml:space="preserve">Implementation directly composes public Atom 0.6.7 Drawer behavior and Modal.Branch without Core or local headless wrappers</t>
   </si>
   <si>
     <t xml:space="preserve">../src/components/drawer/Drawer.tsx</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">Latest owner manual run records every numbered result and corrects any finding before package completion</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner run completed: eight steps pass; iOS Safari 26.5.2 Hide Toolbar reproduces a shared Atom modal scroll-lock/visual-viewport blocker in Drawer and Dialog.</t>
+    <t xml:space="preserve">Owner run completed: eight steps pass. Exact Atom 0.6.7 root-overflow modal scroll-lock patch is installed; physical iPhone/iPad Safari confirmation remains pending.</t>
   </si>
   <si>
     <t xml:space="preserve">DRA-36</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">Numbered protocol covers semantics, pointer/keyboard, link, recipes, states, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
   </si>
   <si>
-    <t xml:space="preserve">manual-tests/icon-button-app-bar.md</t>
+    <t xml:space="preserve">manual-tests/icon-button.md</t>
   </si>
   <si>
     <t xml:space="preserve">ICB-30</t>
@@ -2744,1552 +2744,1561 @@
     <t xml:space="preserve">Latest owner run records every numbered IconButton result and corrects any finding before package completion</t>
   </si>
   <si>
+    <t xml:space="preserve">ICB-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide covers naming, action/link routing, Atom-owned behavior, recipes, accessibility, CSS hooks, and preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/icon-button/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component changelog records the initial public contract and evidence boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/icon-button/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer uses the public icon-button subpath for a real AppBar anchor action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../../../apps/brick-consumer/src/App.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer boundary, production, desktop/mobile, layout, state, and axe gates pass with IconButton integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy icon-only styling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core has no standalone IconButton slice; deleting shared Button iconOnly support is outside this component's authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No standalone legacy component exists; shared Button dependencies remain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle state, disclosure, tooltip generation, badges, arbitrary children, and application navigation policy remain excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package metadata publishes the icon-button subpath and compiled CSS through stable public entrypoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../package.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar composes the public IconButton rather than reproducing icon-only Button styling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICB-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Atom release is required because released Button behavior already satisfies the complete contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/icon-button-component-research.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted compound AppBar API, positioning/layout contract, package proof, Consumer cutover, and completed Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar.Root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root directly styles public Atom 0.3.3 AppBar.Root without Core, framework, scroll listeners, or local behavior state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/app-bar/AppBar.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-approved audit defines AppBar as a top surface and one-row alignment structure rather than application navigation policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/app-bar-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and app-bar subpath exports, declarations, exact frozen namespace, named parts, and closed unions match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The namespace exposes exactly Root, Toolbar, Start, Center, and End and is not callable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest root emits a header landmark with stable class/slot and surface/static defaults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar.Toolbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toolbar is a layout wrapper without an invented ARIA toolbar role and forwards compact/comfortable density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar.Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start supplies the logical leading region with stable class and slot metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar.Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center supplies the flexible middle region while application CSS may hide or replace navigation responsively</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppBar.End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End supplies the logical trailing action region with stable class and slot metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static remains the safe default and participates in normal document flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute positions to the containing block while the application owns containment and offsets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sticky pins to the logical top within its scroll container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed pins to the viewport while the application explicitly owns content offset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solid, surface, and transparent variants form a closed background hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bordered, elevated, and blurred options compose independently without scroll-driven behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compact and comfortable densities preserve a deliberate one-row alignment contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand, links, Avatar, IconButton, and Toggle remain ordinary application-owned children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long brand text, narrow mobile layouts, hidden center policy, and RTL remain contained without forced second-row wrapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logical Start/End alignment mirrors in RTL without reversing application content semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landmark labeling, ordinary navigation semantics, named controls, and axe checks pass without invented interaction roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors preserves surface and action boundaries and blur degrades safely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root/part class, style, slot, scoped appearance, and documented component variables remain local and inspectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and no global page-offset rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/app-bar/app-bar.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The /app-bar workbench exposes overview, variants, density, options, all position modes, mobile stress, and RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitest covers exact anatomy, defaults, props, refs, composition, positions, variants, and options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, positions, density, and callable namespace use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node boundary, export identity, stylesheet, declarations, deterministic SSR, and dry-pack checks include app-bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean packed React 18/19 consumers import, SSR-render, typecheck, and load AppBar CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused browser checks cover anatomy, positions, responsive/RTL containment, axe, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four reviewed Chromium baselines cover light variants, dark options, mobile/RTL stress, and forced-colors density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered protocol covers hierarchy, anatomy, positions, keyboard/landmarks, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/app-bar.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest owner run records every numbered AppBar result and corrects any finding before package completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide covers scope, exact anatomy, positions, fixed-offset ownership, responsive policy, semantics, CSS hooks, and preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/app-bar/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/app-bar/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Consumer uses public AppBar/IconButton subpaths for a sticky application header after correcting unrelated layout regressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy AppBar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh searches found no live Core dependents; legacy AppBar sources and navigation-barrel export are removed and Core builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic hide/elevate-on-scroll, generated navigation, responsive overflow menus, page offsets, and app-shell orchestration remain excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tooltip Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted eight-part Tooltip API, Atom 0.3.5 behavior boundary, package proof, Consumer cutover, manual review, and blocked Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly styles public Atom 0.3.5 Tooltip without Core or local behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/tooltip/Tooltip.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-adopted brief defines supplemental non-interactive plain and rich content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/tooltip-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and tooltip subpath exports and declarations match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen namespace exposes exactly eight parts and is not callable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/tooltip.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider forwards shared timing policy and renders no Brick wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root forwards state, delays, disabled, and plain/rich variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger supports asChild/render, ref, class, style, and stable slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal forwards Atom container/disabled behavior without wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content owns stable hooks, defaults sideOffset to 8, and omits label overrides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rich title is presentational, composable, native-prop and ref capable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rich description is presentational, composable, native-prop and ref capable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional arrow forwards Atom geometry/composition with stable shared hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger retains an independent accessible name and Tooltip remains supplemental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">browser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/tooltip.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain and rich content remain non-interactive role=tooltip descriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard focus opens and Escape closes without moving trigger focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hover bridge, delays, pointer grace, and provider skip-delay match Atom 0.3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/tooltip.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick tap, deliberate hold, text selection prevention, release/outside/scroll dismissal pass on iPhone Safari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android Chrome touch behavior matches the adopted mobile contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android Chrome device unavailable; iPhone Safari passed published Atom 0.6.1 touch contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain neutral inverse recipe is visually approved in light and dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/tooltip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rich title/description recipe is visually approved in light and dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared floating-arrow geometry and fill/border alignment are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top/right/bottom/left positioning and collision-resolved arrow remain aligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256px RTL layout remains within viewport without page overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200% and 400% zoom wrapping and reachability are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long localized content wraps within closed plain/rich maximum widths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTL trigger, content, and logical text alignment are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced-motion behavior and visible forced-colors boundary are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced motion passed; forced colors unavailable without a Windows device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused playground surface has no axe violations excluding portalled landmark best-practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes tooltip recipes, shared arrow primitive, tokens, RTL/reflow/preference rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packed metadata exposes tooltip subpath and exact Atom 0.3.5 dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated React 18 and React 19 package consumers import Tooltip and CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide documents use, anatomy, rich boundary, hooks, and imports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/tooltip/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component and package changelogs record the addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/tooltip/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deterministic workbench covers overview, placement, rich, stress, mobile, and RTL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owner manual review intentionally deferred</t>
   </si>
   <si>
-    <t xml:space="preserve">ICB-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide covers naming, action/link routing, Atom-owned behavior, recipes, accessibility, CSS hooks, and preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/icon-button/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component changelog records the initial public contract and evidence boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/icon-button/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer uses the public icon-button subpath for a real AppBar anchor action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../../../apps/brick-consumer/src/App.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer boundary, production, desktop/mobile, layout, state, and axe gates pass with IconButton integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy icon-only styling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core has no standalone IconButton slice; deleting shared Button iconOnly support is outside this component's authority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No standalone legacy component exists; shared Button dependencies remain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle state, disclosure, tooltip generation, badges, arbitrary children, and application navigation policy remain excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package metadata publishes the icon-button subpath and compiled CSS through stable public entrypoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../package.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar composes the public IconButton rather than reproducing icon-only Button styling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICB-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Atom release is required because released Button behavior already satisfies the complete contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/icon-button-component-research.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted compound AppBar API, positioning/layout contract, package proof, Consumer cutover, and completed Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar.Root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root directly styles public Atom 0.3.3 AppBar.Root without Core, framework, scroll listeners, or local behavior state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/app-bar/AppBar.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-approved audit defines AppBar as a top surface and one-row alignment structure rather than application navigation policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/app-bar-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and app-bar subpath exports, declarations, exact frozen namespace, named parts, and closed unions match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The namespace exposes exactly Root, Toolbar, Start, Center, and End and is not callable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest root emits a header landmark with stable class/slot and surface/static defaults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar.Toolbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toolbar is a layout wrapper without an invented ARIA toolbar role and forwards compact/comfortable density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar.Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start supplies the logical leading region with stable class and slot metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar.Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center supplies the flexible middle region while application CSS may hide or replace navigation responsively</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppBar.End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End supplies the logical trailing action region with stable class and slot metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static remains the safe default and participates in normal document flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute positions to the containing block while the application owns containment and offsets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sticky pins to the logical top within its scroll container</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed pins to the viewport while the application explicitly owns content offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solid, surface, and transparent variants form a closed background hierarchy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bordered, elevated, and blurred options compose independently without scroll-driven behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compact and comfortable densities preserve a deliberate one-row alignment contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand, links, Avatar, IconButton, and Toggle remain ordinary application-owned children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long brand text, narrow mobile layouts, hidden center policy, and RTL remain contained without forced second-row wrapping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logical Start/End alignment mirrors in RTL without reversing application content semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landmark labeling, ordinary navigation semantics, named controls, and axe checks pass without invented interaction roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced-colors preserves surface and action boundaries and blur degrades safely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root/part class, style, slot, scoped appearance, and documented component variables remain local and inspectable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compiled layered CSS uses Brick classes, logical properties, semantic tokens, and no global page-offset rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/app-bar/app-bar.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The /app-bar workbench exposes overview, variants, density, options, all position modes, mobile stress, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitest covers exact anatomy, defaults, props, refs, composition, positions, variants, and options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public root/subpath types accept supported contracts and reject invalid variants, positions, density, and callable namespace use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node boundary, export identity, stylesheet, declarations, deterministic SSR, and dry-pack checks include app-bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean packed React 18/19 consumers import, SSR-render, typecheck, and load AppBar CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focused browser checks cover anatomy, positions, responsive/RTL containment, axe, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four reviewed Chromium baselines cover light variants, dark options, mobile/RTL stress, and forced-colors density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered protocol covers hierarchy, anatomy, positions, keyboard/landmarks, zoom/mobile/RTL, VoiceOver, preferences, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest owner run records every numbered AppBar result and corrects any finding before package completion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide covers scope, exact anatomy, positions, fixed-offset ownership, responsive policy, semantics, CSS hooks, and preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/app-bar/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/app-bar/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Consumer uses public AppBar/IconButton subpaths for a sticky application header after correcting unrelated layout regressions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy AppBar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh searches found no live Core dependents; legacy AppBar sources and navigation-barrel export are removed and Core builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic hide/elevate-on-scroll, generated navigation, responsive overflow menus, page offsets, and app-shell orchestration remain excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tooltip Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted eight-part Tooltip API, Atom 0.3.5 behavior boundary, package proof, Consumer cutover, manual review, and blocked Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directly styles public Atom 0.3.5 Tooltip without Core or local behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/tooltip/Tooltip.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-adopted brief defines supplemental non-interactive plain and rich content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/tooltip-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and tooltip subpath exports and declarations match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen namespace exposes exactly eight parts and is not callable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/tooltip.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provider forwards shared timing policy and renders no Brick wrapper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root forwards state, delays, disabled, and plain/rich variant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger supports asChild/render, ref, class, style, and stable slot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal forwards Atom container/disabled behavior without wrapper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content owns stable hooks, defaults sideOffset to 8, and omits label overrides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich title is presentational, composable, native-prop and ref capable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich description is presentational, composable, native-prop and ref capable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional arrow forwards Atom geometry/composition with stable shared hook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger retains an independent accessible name and Tooltip remains supplemental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">browser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/tooltip.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain and rich content remain non-interactive role=tooltip descriptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyboard focus opens and Escape closes without moving trigger focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hover bridge, delays, pointer grace, and provider skip-delay match Atom 0.3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/tooltip.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner manual review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Touch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quick tap, deliberate hold, text selection prevention, release/outside/scroll dismissal pass on iPhone Safari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner physical-device review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android Chrome touch behavior matches the adopted mobile contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android device review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain neutral inverse recipe is visually approved in light and dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/tooltip</t>
+    <t xml:space="preserve">TTP-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered desktop/mobile protocol has a completed owner run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brick Consumer uses Tooltip on two real AppBar controls via public subpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../../apps/brick-consumer/src/App.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer build, package boundary, and focused browser interaction pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../../apps/brick-consumer/tests/consumer.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core Tooltip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core Tooltip remains because Sidebar imports its callable API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked by later Sidebar redesign and cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTP-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package, Consumer, workbook, and owner manual evidence are complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component-coverage.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HoverCard Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted five-part HoverCard API, Atom 0.3.5 behavior boundary, package proof, Consumer cutover, owner review, and gated Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly styles public Atom 0.3.5 HoverCard without Core or local behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/hover-card/HoverCard.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-adopted brief defines a genuine-link, non-interactive, nonessential preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/hover-card-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and hover-card subpath exports and declarations match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen namespace exposes exactly five parts and is not callable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/hover-card.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root forwards state, 700/300 delays, disabled, and children without DOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger preserves link semantics plus asChild/render, refs, classes, and slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal forwards Atom container/disabled behavior without a wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content has stable hooks, default 8px offset, closed sizes, and no label override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional Arrow forwards Atom geometry, ref, native props, and stable shared hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical triggers are genuine named links with destinations independent of preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/hover-card.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content remains generic with no role, name, expanded state, or trigger relationship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical examples contain no focusable or interactive descendants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard focus opens; Escape closes without moving trigger focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pointer bridge keeps Content open across Trigger-to-Content movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disabled state blocks preview and controlled/default timing examples remain available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700/300 timing, collision, portal modes, presence, scroll, and resize remain released Atom behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@flowstack-ui/atom@0.6.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical iPhone Safari link activation works without preview reliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/hover-card.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link activation passed; intermittent touch preview opening remains a non-blocking Atom follow-up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Android Chrome link activation works without preview reliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No physical Android device was available for this owner run; automated mobile Chromium coverage passed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elevated surface hierarchy is approved in light and dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/hover-card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sm, md, and lg bounded widths are visually distinct and intentional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared Arrow fill, border, optional absence, and collision alignment are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256px RTL content remains within the viewport without page overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200% and 400% zoom wrapping, overflow, reachability, and trigger visibility pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long unbroken and localized content wraps within dynamic viewport bounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTL internal composition and logical collision alignment are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced-motion behavior and forced-colors surface/Arrow boundaries are approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused playground surface has no axe violations after portalled-region exception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen reader announces the complete link without popup state or preview promise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes bounded sizes, shared Arrow, reflow, motion, and forced-colors rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packed metadata exposes hover-card subpath and exact Atom 0.6.6 dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated React 18 and React 19 package consumers import HoverCard and CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuine link Trigger renders server-safe without popup ARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide documents use, anatomy, noninteractive rule, hooks, and imports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/hover-card/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/hover-card/CHANGELOG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workbench covers sizes, placement, state, composition, stress, mobile, and RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brick Consumer uses a public-subpath collaborator link preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer build, boundary, focused interaction, and genuine-link activation pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVC-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core HoverCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core HoverCard slice is retired after owner manual and final replacement gates pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popover Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted twelve-part Popover API, Atom 0.6.10 behavior boundary, package proof, Consumer cutover, owner review, and Sidebar-blocked Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly styles public Atom 0.6.10 Popover without Core or local behavior workarounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/popover/Popover.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-adopted brief defines intentional compact interactive anchored content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/popover-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root and popover subpath exports and declarations match the adopted brief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen non-callable namespace exposes exactly the twelve adopted parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/popover.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root forwards state, modal, dismissal, and disabled while rejecting hover mode and delays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor forwards Atom composition, native hooks, and ref for separate positioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger preserves button semantics, composition, refs, classes, and slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal forwards Atom container and disabled modes without a wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content forwards native ARIA/focus/placement, default 8px offset, hooks, refs, and closed sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header is presentational and supports native props, refs, asChild, render, class, style, and slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Atom Title supplies a server-stable generated accessible name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Atom Description supplies a server-stable generated accessible description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body / Footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentational Body scrolls and Footer wraps actions with native composition hooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close forwards Atom button/composition behavior and stable Brick hooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit Arrow forwards Atom geometry/ref/native props and shared styling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visible direct Title and Description generate dialog name and description relationships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/popover.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native heading and paragraph content use documented explicit relationships without Brick registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/popover/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atom 0.6.10 owns initial/final focus, touch-safe outside dismissal, root-overflow modal locking, measured floating bounds, the non-clipping internal viewport, and portalled logical direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@flowstack-ui/atom@0.6.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard activation, Escape close, and trigger focus restoration pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit Escape/outside dismissal policy is preserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal mode exposes aria-modal and traps Tab until visible Close dismissal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nested top-layer Escape closes child then parent in order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sm, md, and lg expose bounded preferred widths and stable component-owned control heights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elevated surface hierarchy and compact structural spacing are owner-approved in light and dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/popover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner approved the light and dark elevated surface hierarchy and spacing during the manual run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared Arrow fill, border, and collision alignment are owner-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner approved Arrow fill, boundary, and resolved-side alignment during the manual run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256px RTL content remains within the viewport without horizontal page overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200% and 400% zoom preserve scrolling, action reachability, and trigger visibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual-tests/popover.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner confirmed 200% and 400% zoom scrolling and action reachability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTL internal alignment, action order, and collision placement are owner-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner confirmed RTL alignment, action order, and collision placement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced-motion and forced-colors surface, Arrow, controls, and boundaries are owner-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced-colors owner verification was not applicable because no Windows device was available; reduced motion passed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused 256px RTL surface has no axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes tokens, sizes, structure, Arrow, reflow, motion, and forced-colors rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata exposes popover subpath and exact Atom 0.6.10 dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated React 18 and React 19 packed consumers import root/subpath Popover and CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct semantic parts render stable name/description IDs and relationships on the server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public guide and changelogs document routing, API, semantics, hooks, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workbench covers anatomy, sizes, modal/state, Anchor, placement, nesting, stress, mobile, and RTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered desktop, screen-reader, zoom, preference, and physical-mobile protocol has an owner run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 13 owner-run steps pass. iOS focus zoom from the raw sub-16px input fixture is assigned to future Brick Input work and does not block Popover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brick Consumer public-subpath AppBar settings panel passes desktop/mobile browser and boundary suites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core Popover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Core Popover remains while Sidebar imports its callable flyout API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form Foundation Evidence Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence gates for the adopted direct Form and complete Field/Fieldset APIs, Atom 0.5.3 behavior boundary, package proof, Consumer integration, owner review, and dependency-led Core retirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly styles public Atom 0.5.3 Form, Field, and Fieldset without Core or local behavior workarounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/form/Form.tsx; ../src/components/field/Field.tsx; ../src/components/fieldset/Fieldset.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-adopted brief defines complete direct Form plus compound Field and Fieldset contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/form-foundation-component-brief.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root, form, field, and fieldset subpath exports and declarations match the adopted anatomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/types/form-foundation.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form is direct, has no Root namespace, renders form, and forwards HTMLFormElement ref/native props</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/form-foundation.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen namespace exposes exactly Root, Label, Description, Error, and RequiredIndicator plus direct exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fieldset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen namespace exposes exactly Root, Legend, Description, and Error plus direct exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default, render, and strict asChild paths preserve native form semantics, props, classes, slots, and refs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every Field part supports mutually exclusive render/asChild typing and preserves semantic adapters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every Fieldset part supports mutually exclusive render/asChild typing and preserves native grouping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default and Root asChild server markup retain styled Description/Error discovery and control relationships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../test/components/form-foundation.test.tsx; ../test/package/ssr.test.mjs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default and Root asChild server markup retain Legend/Description/Error discovery and group relationships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callback validation, submitting, submitted, rejected error visibility, and native reset metadata pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/form-foundation.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required, optional, disabled, read-only, invalid, forced, and matched Error states are implemented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required, disabled, invalid, forced Error, and group-versus-item state preserve native semantics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label activation and generated Description/Error relationships work while explicit native ARIA remains authoritative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native fieldset/legend naming, disabled propagation, and grouped-control descriptions pass without invalid aria-required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native URL/function action/callback models, FormData, external controls, and reset remain supported without Brick policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical source order and intrinsic horizontal two-to-one-column reflow pass exact browser geometry assertions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain borderless group rhythm supports grouped controls and nested Fields without becoming a Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../src/components/fieldset/fieldset.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256 CSS-pixel English/RTL fixtures remain contained with no horizontal page overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light/dark hierarchy, invalid boundaries, RTL stress, and forced colors have stable visual baselines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required, invalid, disabled, grouped, constrained, and RTL fixtures have no axe violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Announcements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field and Fieldset Error have no forced live role and accept deliberate native live-region props</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes complete spacing tokens and visible callback-state treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes stable anatomy classes, slots, complete tokens, state, orientation, reflow, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production CSS includes stable anatomy classes, slots, complete tokens, native reset, state, and forced colors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata exposes all three subpaths and pins exact public Atom 0.5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated React 18 and React 19 packed consumers import root/subpath APIs and CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Form guide/changelog document routing, native API, submission models, states, hooks, and customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/form/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Field guide/changelog document complete anatomy, state, relationships, composition, reflow, and tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/field/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Fieldset guide/changelog document native grouping, anatomy, state, relationships, composition, and tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../docs/components/fieldset/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nine-section workbench covers APIs, models, state, reflow, groups, composition, appearance, relationships, and stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered visual, keyboard, touch, screen-reader, zoom, direction, preference, composition, and Consumer protocol has an owner run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../docs/manual-tests/form-foundation.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner run pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner approves finished hierarchy, disabled/read-only distinction, error presentation, responsive reflow, and control alignment</t>
   </si>
   <si>
     <t xml:space="preserve">Owner visual review pending</t>
   </si>
   <si>
-    <t xml:space="preserve">TTP-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich title/description recipe is visually approved in light and dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared floating-arrow geometry and fill/border alignment are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top/right/bottom/left positioning and collision-resolved arrow remain aligned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256px RTL layout remains within viewport without page overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200% and 400% zoom wrapping and reachability are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner zoom review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Localization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long localized content wraps within closed plain/rich maximum widths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTL trigger, content, and logical text alignment are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner RTL review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduced-motion behavior and visible forced-colors boundary are approved</t>
+    <t xml:space="preserve">FFB-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical touch label activation, 200%/400% reflow, and mobile screen-reader behavior are owner-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner mobile and zoom review pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFB-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced motion and forced colors/Windows High Contrast boundaries are owner-approved where available</t>
   </si>
   <si>
     <t xml:space="preserve">Owner preference review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focused playground surface has no axe violations excluding portalled landmark best-practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">axe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes tooltip recipes, shared arrow primitive, tokens, RTL/reflow/preference rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packed metadata exposes tooltip subpath and exact Atom 0.3.5 dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated React 18 and React 19 package consumers import Tooltip and CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide documents use, anatomy, rich boundary, hooks, and imports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/tooltip/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component and package changelogs record the addition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/tooltip/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deterministic workbench covers overview, placement, rich, stress, mobile, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered desktop/mobile protocol has a completed owner run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner run pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brick Consumer uses Tooltip on two real AppBar controls via public subpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../../apps/brick-consumer/src/App.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer build, package boundary, and focused browser interaction pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../../apps/brick-consumer/tests/consumer.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core Tooltip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Core Tooltip remains because Sidebar imports its callable API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blocker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked by later Sidebar redesign and cutover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTP-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package, Consumer, workbook, and owner manual evidence are complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">component-coverage.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner manual review and full gates pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HoverCard Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted five-part HoverCard API, Atom 0.3.5 behavior boundary, package proof, Consumer cutover, owner review, and gated Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directly styles public Atom 0.3.5 HoverCard without Core or local behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/hover-card/HoverCard.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-adopted brief defines a genuine-link, non-interactive, nonessential preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/hover-card-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and hover-card subpath exports and declarations match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen namespace exposes exactly five parts and is not callable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/hover-card.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root forwards state, 700/300 delays, disabled, and children without DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger preserves link semantics plus asChild/render, refs, classes, and slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal forwards Atom container/disabled behavior without a wrapper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content has stable hooks, default 8px offset, closed sizes, and no label override</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional Arrow forwards Atom geometry, ref, native props, and stable shared hook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical triggers are genuine named links with destinations independent of preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/hover-card.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content remains generic with no role, name, expanded state, or trigger relationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical examples contain no focusable or interactive descendants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyboard focus opens; Escape closes without moving trigger focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pointer bridge keeps Content open across Trigger-to-Content movement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disabled state blocks preview and controlled/default timing examples remain available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700/300 timing, collision, portal modes, presence, scroll, and resize remain released Atom behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@flowstack-ui/atom@0.3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical iPhone Safari link activation works without preview reliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/hover-card.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical Android Chrome link activation works without preview reliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elevated surface hierarchy is approved in light and dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/hover-card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sm, md, and lg bounded widths are visually distinct and intentional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared Arrow fill, border, optional absence, and collision alignment are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256px RTL content remains within the viewport without page overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200% and 400% zoom wrapping, overflow, reachability, and trigger visibility pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long unbroken and localized content wraps within dynamic viewport bounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTL internal composition and logical collision alignment are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduced-motion behavior and forced-colors surface/Arrow boundaries are approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focused playground surface has no axe violations after portalled-region exception</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screen reader announces the complete link without popup state or preview promise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner screen-reader review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes bounded sizes, shared Arrow, reflow, motion, and forced-colors rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packed metadata exposes hover-card subpath and exact Atom 0.3.5 dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated React 18 and React 19 package consumers import HoverCard and CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genuine link Trigger renders server-safe without popup ARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide documents use, anatomy, noninteractive rule, hooks, and imports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/hover-card/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/hover-card/CHANGELOG.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workbench covers sizes, placement, state, composition, stress, mobile, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brick Consumer uses a public-subpath collaborator link preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer build, boundary, focused interaction, and genuine-link activation pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVC-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core HoverCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Core slice remains until owner manual and final replacement gates pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner manual and final retirement audit pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popover Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted twelve-part Popover API, Atom 0.4.0 behavior boundary, package proof, Consumer cutover, owner review, and Sidebar-blocked Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directly styles public Atom 0.4.0 Popover without Core or local behavior workarounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/popover/Popover.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-adopted brief defines intentional compact interactive anchored content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/popover-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root and popover subpath exports and declarations match the adopted brief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen non-callable namespace exposes exactly the twelve adopted parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/popover.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root forwards state, modal, dismissal, and disabled while rejecting hover mode and delays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchor forwards Atom composition, native hooks, and ref for separate positioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger preserves button semantics, composition, refs, classes, and slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal forwards Atom container and disabled modes without a wrapper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content forwards native ARIA/focus/placement, default 8px offset, hooks, refs, and closed sizes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header is presentational and supports native props, refs, asChild, render, class, style, and slot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct Atom Title supplies a server-stable generated accessible name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct Atom Description supplies a server-stable generated accessible description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Body / Footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presentational Body scrolls and Footer wraps actions with native composition hooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close forwards Atom button/composition behavior and stable Brick hooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit Arrow forwards Atom geometry/ref/native props and shared styling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visible direct Title and Description generate dialog name and description relationships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/popover.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native heading and paragraph content use documented explicit relationships without Brick registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/popover/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atom 0.4.0 owns initial/final focus controls and touch-safe default behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@flowstack-ui/atom@0.4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyboard activation, Escape close, and trigger focus restoration pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit Escape/outside dismissal policy is preserved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modal mode exposes aria-modal and traps Tab until visible Close dismissal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nested top-layer Escape closes child then parent in order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sm, md, and lg expose bounded preferred widths and stable component-owned control heights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elevated surface hierarchy and compact structural spacing are owner-approved in light and dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/popover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared Arrow fill, border, and collision alignment are owner-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256px RTL content remains within the viewport without horizontal page overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200% and 400% zoom preserve scrolling, action reachability, and trigger visibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual-tests/popover.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTL internal alignment, action order, and collision placement are owner-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduced-motion and forced-colors surface, Arrow, controls, and boundaries are owner-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focused 256px RTL surface has no axe violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes tokens, sizes, structure, Arrow, reflow, motion, and forced-colors rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata exposes popover subpath and exact Atom 0.4.0 dependency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated React 18 and React 19 packed consumers import root/subpath Popover and CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct semantic parts render stable name/description IDs and relationships on the server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public guide and changelogs document routing, API, semantics, hooks, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workbench covers anatomy, sizes, modal/state, Anchor, placement, nesting, stress, mobile, and RTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered desktop, screen-reader, zoom, preference, and physical-mobile protocol has an owner run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brick Consumer public-subpath AppBar settings panel passes desktop/mobile browser and boundary suites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core Popover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy Core Popover remains while Sidebar imports its callable flyout API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form Foundation Evidence Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence gates for the adopted direct Form and complete Field/Fieldset APIs, Atom 0.5.3 behavior boundary, package proof, Consumer integration, owner review, and dependency-led Core retirement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directly styles public Atom 0.5.3 Form, Field, and Fieldset without Core or local behavior workarounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/form/Form.tsx; ../src/components/field/Field.tsx; ../src/components/fieldset/Fieldset.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-adopted brief defines complete direct Form plus compound Field and Fieldset contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/form-foundation-component-brief.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root, form, field, and fieldset subpath exports and declarations match the adopted anatomy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/types/form-foundation.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form is direct, has no Root namespace, renders form, and forwards HTMLFormElement ref/native props</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/form-foundation.test.tsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen namespace exposes exactly Root, Label, Description, Error, and RequiredIndicator plus direct exports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fieldset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen namespace exposes exactly Root, Legend, Description, and Error plus direct exports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default, render, and strict asChild paths preserve native form semantics, props, classes, slots, and refs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every Field part supports mutually exclusive render/asChild typing and preserves semantic adapters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every Fieldset part supports mutually exclusive render/asChild typing and preserves native grouping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default and Root asChild server markup retain styled Description/Error discovery and control relationships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../test/components/form-foundation.test.tsx; ../test/package/ssr.test.mjs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default and Root asChild server markup retain Legend/Description/Error discovery and group relationships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callback validation, submitting, submitted, rejected error visibility, and native reset metadata pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/form-foundation.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required, optional, disabled, read-only, invalid, forced, and matched Error states are implemented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required, disabled, invalid, forced Error, and group-versus-item state preserve native semantics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label activation and generated Description/Error relationships work while explicit native ARIA remains authoritative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native fieldset/legend naming, disabled propagation, and grouped-control descriptions pass without invalid aria-required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native URL/function action/callback models, FormData, external controls, and reset remain supported without Brick policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical source order and intrinsic horizontal two-to-one-column reflow pass exact browser geometry assertions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain borderless group rhythm supports grouped controls and nested Fields without becoming a Card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../src/components/fieldset/fieldset.css</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256 CSS-pixel English/RTL fixtures remain contained with no horizontal page overflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light/dark hierarchy, invalid boundaries, RTL stress, and forced colors have stable visual baselines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required, invalid, disabled, grouped, constrained, and RTL fixtures have no axe violations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Announcements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field and Fieldset Error have no forced live role and accept deliberate native live-region props</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes complete spacing tokens and visible callback-state treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes stable anatomy classes, slots, complete tokens, state, orientation, reflow, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production CSS includes stable anatomy classes, slots, complete tokens, native reset, state, and forced colors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata exposes all three subpaths and pins exact public Atom 0.5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated React 18 and React 19 packed consumers import root/subpath APIs and CSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Form guide/changelog document routing, native API, submission models, states, hooks, and customization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/form/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Field guide/changelog document complete anatomy, state, relationships, composition, reflow, and tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/field/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Fieldset guide/changelog document native grouping, anatomy, state, relationships, composition, and tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../docs/components/fieldset/README.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nine-section workbench covers APIs, models, state, reflow, groups, composition, appearance, relationships, and stress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numbered visual, keyboard, touch, screen-reader, zoom, direction, preference, composition, and Consumer protocol has an owner run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../docs/manual-tests/form-foundation.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner approves finished hierarchy, disabled/read-only distinction, error presentation, responsive reflow, and control alignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical touch label activation, 200%/400% reflow, and mobile screen-reader behavior are owner-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner mobile and zoom review pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFB-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduced motion and forced colors/Windows High Contrast boundaries are owner-approved where available</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-37</t>
@@ -4592,7 +4601,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4778,6 +4787,22 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF991B1B"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92400E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -5221,21 +5246,21 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIF(N8:N21,"complete")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">SUM(H8:H21)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B21,J8:J21)/SUM(B8:B21),0)</f>
-        <v>0.918095238095238</v>
+        <v>0.975238095238095</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5524,7 +5549,7 @@
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"partial")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"implemented")</f>
@@ -5540,7 +5565,7 @@
       </c>
       <c r="H12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"blocked")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="8" t="n">
         <f aca="false">COUNTIF(Drawer!H9:H47,"not applicable")</f>
@@ -5752,7 +5777,7 @@
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">COUNTIF(IconButton!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
         <f aca="false">COUNTIF(IconButton!H9:H47,"implemented")</f>
@@ -5764,7 +5789,7 @@
       </c>
       <c r="G16" s="8" t="n">
         <f aca="false">COUNTIF(IconButton!H9:H47,"verified")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="8" t="n">
         <f aca="false">COUNTIF(IconButton!H9:H47,"blocked")</f>
@@ -5776,11 +5801,11 @@
       </c>
       <c r="J16" s="9" t="n">
         <f aca="false">IFERROR(SUM(IconButton!M9:M47)/SUM(IconButton!L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="K16" s="8" t="str">
         <f aca="false">IF(COUNTIFS(IconButton!E9:E47,"package",IconButton!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L16" s="8" t="str">
         <f aca="false">IF(COUNTIFS(IconButton!E9:E47,"consumer",IconButton!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5792,7 +5817,7 @@
       </c>
       <c r="N16" s="1" t="str">
         <f aca="false">IF(H16&gt;0,"blocked",IF(AND(J16=1,K16="complete",L16="complete",M16="complete"),"complete",IF(J16=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5809,7 +5834,7 @@
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">COUNTIF(AppBar!H9:H47,"partial")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">COUNTIF(AppBar!H9:H47,"implemented")</f>
@@ -5821,7 +5846,7 @@
       </c>
       <c r="G17" s="8" t="n">
         <f aca="false">COUNTIF(AppBar!H9:H47,"verified")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="8" t="n">
         <f aca="false">COUNTIF(AppBar!H9:H47,"blocked")</f>
@@ -5833,11 +5858,11 @@
       </c>
       <c r="J17" s="9" t="n">
         <f aca="false">IFERROR(SUM(AppBar!M9:M47)/SUM(AppBar!L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="K17" s="8" t="str">
         <f aca="false">IF(COUNTIFS(AppBar!E9:E47,"package",AppBar!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L17" s="8" t="str">
         <f aca="false">IF(COUNTIFS(AppBar!E9:E47,"consumer",AppBar!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5849,7 +5874,7 @@
       </c>
       <c r="N17" s="1" t="str">
         <f aca="false">IF(H17&gt;0,"blocked",IF(AND(J17=1,K17="complete",L17="complete",M17="complete"),"complete",IF(J17=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5866,7 +5891,7 @@
       </c>
       <c r="D18" s="8" t="n">
         <f aca="false">COUNTIF(Tooltip!H9:H47,"partial")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
         <f aca="false">COUNTIF(Tooltip!H9:H47,"implemented")</f>
@@ -5878,7 +5903,7 @@
       </c>
       <c r="G18" s="8" t="n">
         <f aca="false">COUNTIF(Tooltip!H9:H47,"verified")</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H18" s="8" t="n">
         <f aca="false">COUNTIF(Tooltip!H9:H47,"blocked")</f>
@@ -5886,15 +5911,15 @@
       </c>
       <c r="I18" s="8" t="n">
         <f aca="false">COUNTIF(Tooltip!H9:H47,"not applicable")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">IFERROR(SUM(Tooltip!M9:M47)/SUM(Tooltip!L9:L47),0)</f>
-        <v>0.692307692307692</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="K18" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Tooltip!E9:E47,"package",Tooltip!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L18" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Tooltip!E9:E47,"consumer",Tooltip!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5923,7 +5948,7 @@
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">COUNTIF(HoverCard!H9:H47,"partial")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8" t="n">
         <f aca="false">COUNTIF(HoverCard!H9:H47,"implemented")</f>
@@ -5935,7 +5960,7 @@
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">COUNTIF(HoverCard!H9:H47,"verified")</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H19" s="8" t="n">
         <f aca="false">COUNTIF(HoverCard!H9:H47,"blocked")</f>
@@ -5943,15 +5968,15 @@
       </c>
       <c r="I19" s="8" t="n">
         <f aca="false">COUNTIF(HoverCard!H9:H47,"not applicable")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="9" t="n">
         <f aca="false">IFERROR(SUM(HoverCard!M9:M47)/SUM(HoverCard!L9:L47),0)</f>
-        <v>0.717948717948718</v>
+        <v>1</v>
       </c>
       <c r="K19" s="8" t="str">
         <f aca="false">IF(COUNTIFS(HoverCard!E9:E47,"package",HoverCard!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L19" s="8" t="str">
         <f aca="false">IF(COUNTIFS(HoverCard!E9:E47,"consumer",HoverCard!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -5959,11 +5984,11 @@
       </c>
       <c r="M19" s="8" t="str">
         <f aca="false">IF(COUNTIFS(HoverCard!E9:E47,"retirement",HoverCard!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="N19" s="1" t="str">
         <f aca="false">IF(H19&gt;0,"blocked",IF(AND(J19=1,K19="complete",L19="complete",M19="complete"),"complete",IF(J19=0,"not started","in progress")))</f>
-        <v>in progress</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5980,7 +6005,7 @@
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">COUNTIF(Popover!H9:H47,"partial")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
         <f aca="false">COUNTIF(Popover!H9:H47,"implemented")</f>
@@ -5992,7 +6017,7 @@
       </c>
       <c r="G20" s="8" t="n">
         <f aca="false">COUNTIF(Popover!H9:H47,"verified")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20" s="8" t="n">
         <f aca="false">COUNTIF(Popover!H9:H47,"blocked")</f>
@@ -6000,15 +6025,15 @@
       </c>
       <c r="I20" s="8" t="n">
         <f aca="false">COUNTIF(Popover!H9:H47,"not applicable")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">IFERROR(SUM(Popover!M9:M47)/SUM(Popover!L9:L47),0)</f>
-        <v>0.820512820512821</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="K20" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Popover!E9:E47,"package",Popover!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L20" s="8" t="str">
         <f aca="false">IF(COUNTIFS(Popover!E9:E47,"consumer",Popover!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -9822,14 +9847,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -9843,7 +9868,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -11094,28 +11119,26 @@
         <v>891</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>894</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K38" s="15"/>
       <c r="L38" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M38" s="18" t="n">
         <f aca="false">IF(H38="not applicable",IF(K38&lt;&gt;"",1,0),IF(I38="yes",IF(H38="verified",1,0),IF(OR(H38="tested",H38="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>145</v>
@@ -11124,7 +11147,7 @@
         <v>27</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>72</v>
@@ -11133,7 +11156,7 @@
         <v>147</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>75</v>
@@ -11155,7 +11178,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>145</v>
@@ -11164,7 +11187,7 @@
         <v>27</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>72</v>
@@ -11173,7 +11196,7 @@
         <v>147</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>75</v>
@@ -11195,7 +11218,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>153</v>
@@ -11204,7 +11227,7 @@
         <v>27</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>155</v>
@@ -11213,7 +11236,7 @@
         <v>155</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>75</v>
@@ -11235,7 +11258,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>153</v>
@@ -11244,7 +11267,7 @@
         <v>27</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>155</v>
@@ -11264,9 +11287,7 @@
       <c r="J42" s="19" t="n">
         <v>46221</v>
       </c>
-      <c r="K42" s="15" t="s">
-        <v>894</v>
-      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
@@ -11277,16 +11298,16 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C43" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="D43" s="15" t="s">
         <v>907</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>908</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>160</v>
@@ -11307,7 +11328,7 @@
         <v>46221</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1</v>
@@ -11319,7 +11340,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>626</v>
@@ -11328,7 +11349,7 @@
         <v>27</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -11359,25 +11380,25 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>912</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>913</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D45" s="15" t="s">
+        <v>913</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="16" t="s">
         <v>914</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>915</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>75</v>
@@ -11399,16 +11420,16 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="B46" s="15" t="s">
         <v>916</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>917</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>72</v>
@@ -11439,16 +11460,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
+        <v>918</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>919</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>920</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>72</v>
@@ -11457,7 +11478,7 @@
         <v>80</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>82</v>
@@ -11545,8 +11566,8 @@
     <hyperlink ref="G34" r:id="rId26" display="tests/icon-button-app-bar.spec.ts"/>
     <hyperlink ref="G35" r:id="rId27" display="../playwright.config.ts"/>
     <hyperlink ref="G36" r:id="rId28" display="tests/visual.spec.ts"/>
-    <hyperlink ref="G37" r:id="rId29" display="manual-tests/icon-button-app-bar.md"/>
-    <hyperlink ref="G38" r:id="rId30" display="manual-tests/icon-button-app-bar.md"/>
+    <hyperlink ref="G37" r:id="rId29" display="manual-tests/icon-button.md"/>
+    <hyperlink ref="G38" r:id="rId30" display="manual-tests/icon-button.md"/>
     <hyperlink ref="G39" r:id="rId31" display="../docs/components/icon-button/README.md"/>
     <hyperlink ref="G40" r:id="rId32" display="../docs/components/icon-button/CHANGELOG.md"/>
     <hyperlink ref="G41" r:id="rId33" display="../../../../apps/brick-consumer/src/App.tsx"/>
@@ -11592,7 +11613,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11609,7 +11630,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11637,14 +11658,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.974358974358974</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -11658,7 +11679,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -11728,16 +11749,16 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>926</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>927</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>72</v>
@@ -11746,7 +11767,7 @@
         <v>73</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>75</v>
@@ -11768,7 +11789,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -11777,7 +11798,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>72</v>
@@ -11786,7 +11807,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>82</v>
@@ -11808,7 +11829,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>70</v>
@@ -11817,7 +11838,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>72</v>
@@ -11848,7 +11869,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>50</v>
@@ -11857,7 +11878,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>72</v>
@@ -11888,16 +11909,16 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>72</v>
@@ -11928,16 +11949,16 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>939</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>940</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>72</v>
@@ -11968,16 +11989,16 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>942</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>943</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>72</v>
@@ -12008,16 +12029,16 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>944</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>945</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>946</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>72</v>
@@ -12048,16 +12069,16 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>948</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>949</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>72</v>
@@ -12088,16 +12109,16 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
+        <v>949</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="C18" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>951</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>952</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>72</v>
@@ -12128,16 +12149,16 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>953</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>954</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>72</v>
@@ -12168,16 +12189,16 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
+        <v>954</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>955</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>956</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>72</v>
@@ -12208,16 +12229,16 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>956</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>957</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>958</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>72</v>
@@ -12248,16 +12269,16 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>72</v>
@@ -12288,16 +12309,16 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>72</v>
@@ -12328,16 +12349,16 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>561</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>72</v>
@@ -12368,7 +12389,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>669</v>
@@ -12377,7 +12398,7 @@
         <v>28</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>72</v>
@@ -12408,7 +12429,7 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>779</v>
@@ -12417,7 +12438,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>72</v>
@@ -12448,7 +12469,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>760</v>
@@ -12457,7 +12478,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>72</v>
@@ -12488,7 +12509,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>550</v>
@@ -12497,7 +12518,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>72</v>
@@ -12528,7 +12549,7 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>862</v>
@@ -12537,7 +12558,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>72</v>
@@ -12568,7 +12589,7 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>581</v>
@@ -12577,7 +12598,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>72</v>
@@ -12608,7 +12629,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>92</v>
@@ -12617,7 +12638,7 @@
         <v>28</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>72</v>
@@ -12626,7 +12647,7 @@
         <v>73</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>75</v>
@@ -12648,7 +12669,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>99</v>
@@ -12657,7 +12678,7 @@
         <v>28</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>72</v>
@@ -12688,7 +12709,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>118</v>
@@ -12697,7 +12718,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>72</v>
@@ -12728,7 +12749,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>118</v>
@@ -12737,7 +12758,7 @@
         <v>28</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>72</v>
@@ -12768,7 +12789,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>118</v>
@@ -12777,7 +12798,7 @@
         <v>28</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>72</v>
@@ -12808,7 +12829,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>118</v>
@@ -12817,7 +12838,7 @@
         <v>28</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>72</v>
@@ -12848,7 +12869,7 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>118</v>
@@ -12888,7 +12909,7 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>118</v>
@@ -12897,7 +12918,7 @@
         <v>28</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>72</v>
@@ -12928,7 +12949,7 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>118</v>
@@ -12968,7 +12989,7 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>118</v>
@@ -12977,7 +12998,7 @@
         <v>28</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>72</v>
@@ -13008,7 +13029,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>139</v>
@@ -13017,7 +13038,7 @@
         <v>28</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>72</v>
@@ -13026,7 +13047,7 @@
         <v>141</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>891</v>
+        <v>997</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>75</v>
@@ -13066,24 +13087,24 @@
         <v>141</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>891</v>
+        <v>997</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="15" t="s">
-        <v>894</v>
-      </c>
+      <c r="J42" s="19" t="n">
+        <v>46223</v>
+      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M42" s="18" t="n">
         <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13137,7 +13158,7 @@
         <v>28</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -13186,7 +13207,7 @@
         <v>155</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>75</v>
@@ -13266,7 +13287,7 @@
         <v>80</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>82</v>
@@ -13358,8 +13379,8 @@
     <hyperlink ref="G38" r:id="rId30" display="tests/icon-button-app-bar.spec.ts"/>
     <hyperlink ref="G39" r:id="rId31" display="../playwright.config.ts"/>
     <hyperlink ref="G40" r:id="rId32" display="tests/visual.spec.ts"/>
-    <hyperlink ref="G41" r:id="rId33" display="manual-tests/icon-button-app-bar.md"/>
-    <hyperlink ref="G42" r:id="rId34" display="manual-tests/icon-button-app-bar.md"/>
+    <hyperlink ref="G41" r:id="rId33" display="manual-tests/app-bar.md"/>
+    <hyperlink ref="G42" r:id="rId34" display="manual-tests/app-bar.md"/>
     <hyperlink ref="G43" r:id="rId35" display="../docs/components/app-bar/README.md"/>
     <hyperlink ref="G44" r:id="rId36" display="../docs/components/app-bar/CHANGELOG.md"/>
     <hyperlink ref="G45" r:id="rId37" display="../../../../apps/brick-consumer/src/App.tsx"/>
@@ -13446,14 +13467,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.692307692307692</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -13467,7 +13488,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -14158,37 +14179,35 @@
         <v>1054</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>1055</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K24" s="15"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M24" s="18" t="n">
         <f aca="false">IF(H24="not applicable",IF(K24&lt;&gt;"",1,0),IF(I24="yes",IF(H24="verified",1,0),IF(OR(H24="tested",H24="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>1056</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>1057</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>72</v>
@@ -14200,37 +14219,35 @@
         <v>1054</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>1059</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K25" s="15"/>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="18" t="n">
         <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>72</v>
@@ -14242,28 +14259,28 @@
         <v>1054</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="18" t="n">
         <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>859</v>
@@ -14272,7 +14289,7 @@
         <v>197</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>72</v>
@@ -14281,31 +14298,29 @@
         <v>485</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K27" s="15"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="18" t="n">
         <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>859</v>
@@ -14314,7 +14329,7 @@
         <v>197</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>72</v>
@@ -14323,31 +14338,29 @@
         <v>485</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K28" s="15"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="18" t="n">
         <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>859</v>
@@ -14356,7 +14369,7 @@
         <v>1042</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>72</v>
@@ -14365,40 +14378,38 @@
         <v>485</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K29" s="15"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="18" t="n">
         <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>72</v>
@@ -14429,7 +14440,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>779</v>
@@ -14438,7 +14449,7 @@
         <v>197</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>72</v>
@@ -14469,7 +14480,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>779</v>
@@ -14478,7 +14489,7 @@
         <v>197</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>72</v>
@@ -14490,37 +14501,35 @@
         <v>1054</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J32" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>1078</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K32" s="15"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="18" t="n">
         <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>72</v>
@@ -14551,7 +14560,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>760</v>
@@ -14560,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>72</v>
@@ -14572,28 +14581,26 @@
         <v>1054</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>1084</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K34" s="15"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="18" t="n">
         <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>862</v>
@@ -14602,7 +14609,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>72</v>
@@ -14614,28 +14621,28 @@
         <v>1054</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="18" t="n">
         <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>550</v>
@@ -14644,13 +14651,13 @@
         <v>29</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>1047</v>
@@ -14675,16 +14682,16 @@
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>72</v>
@@ -14715,16 +14722,16 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>72</v>
@@ -14755,16 +14762,16 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>72</v>
@@ -14795,16 +14802,16 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>72</v>
@@ -14813,7 +14820,7 @@
         <v>147</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>75</v>
@@ -14835,16 +14842,16 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>72</v>
@@ -14853,7 +14860,7 @@
         <v>147</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>75</v>
@@ -14875,7 +14882,7 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>99</v>
@@ -14884,7 +14891,7 @@
         <v>29</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>72</v>
@@ -14905,7 +14912,7 @@
         <v>46222</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>894</v>
+        <v>1103</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -14917,16 +14924,16 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -14938,28 +14945,26 @@
         <v>1054</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>1111</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K43" s="15"/>
       <c r="L43" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M43" s="18" t="n">
         <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>153</v>
@@ -14968,7 +14973,7 @@
         <v>29</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>155</v>
@@ -14977,7 +14982,7 @@
         <v>73</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>75</v>
@@ -14999,7 +15004,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>153</v>
@@ -15008,7 +15013,7 @@
         <v>29</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>155</v>
@@ -15017,7 +15022,7 @@
         <v>120</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>75</v>
@@ -15039,22 +15044,22 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>252</v>
@@ -15069,7 +15074,7 @@
         <v>46221</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="L46" s="18" t="n">
         <v>1</v>
@@ -15081,44 +15086,42 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>1128</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="K47" s="15"/>
       <c r="L47" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M47" s="18" t="n">
         <f aca="false">IF(H47="not applicable",IF(K47&lt;&gt;"",1,0),IF(I47="yes",IF(H47="verified",1,0),IF(OR(H47="tested",H47="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15203,7 +15206,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15220,7 +15223,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15248,14 +15251,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.717948717948718</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -15269,14 +15272,14 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"retirement",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15339,7 +15342,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>70</v>
@@ -15348,7 +15351,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>72</v>
@@ -15357,7 +15360,7 @@
         <v>73</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>75</v>
@@ -15379,7 +15382,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -15388,7 +15391,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>72</v>
@@ -15397,7 +15400,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>82</v>
@@ -15419,7 +15422,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>1021</v>
@@ -15428,7 +15431,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>72</v>
@@ -15459,7 +15462,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>50</v>
@@ -15468,7 +15471,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>72</v>
@@ -15477,7 +15480,7 @@
         <v>120</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>75</v>
@@ -15499,7 +15502,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>50</v>
@@ -15508,7 +15511,7 @@
         <v>180</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>72</v>
@@ -15517,7 +15520,7 @@
         <v>73</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>75</v>
@@ -15539,7 +15542,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>50</v>
@@ -15548,7 +15551,7 @@
         <v>269</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>72</v>
@@ -15557,7 +15560,7 @@
         <v>120</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>75</v>
@@ -15579,7 +15582,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>50</v>
@@ -15588,7 +15591,7 @@
         <v>272</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>72</v>
@@ -15597,7 +15600,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>75</v>
@@ -15619,7 +15622,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>50</v>
@@ -15628,7 +15631,7 @@
         <v>197</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>72</v>
@@ -15659,7 +15662,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>50</v>
@@ -15668,7 +15671,7 @@
         <v>1042</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>72</v>
@@ -15677,7 +15680,7 @@
         <v>120</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>75</v>
@@ -15699,7 +15702,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>835</v>
@@ -15708,7 +15711,7 @@
         <v>269</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>72</v>
@@ -15717,7 +15720,7 @@
         <v>1046</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>75</v>
@@ -15739,7 +15742,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>835</v>
@@ -15748,7 +15751,7 @@
         <v>197</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>72</v>
@@ -15757,7 +15760,7 @@
         <v>1046</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>75</v>
@@ -15779,7 +15782,7 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>835</v>
@@ -15788,7 +15791,7 @@
         <v>197</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>72</v>
@@ -15797,7 +15800,7 @@
         <v>1046</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>75</v>
@@ -15819,7 +15822,7 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>736</v>
@@ -15828,7 +15831,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>72</v>
@@ -15837,7 +15840,7 @@
         <v>1046</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>75</v>
@@ -15859,7 +15862,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>736</v>
@@ -15868,7 +15871,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>72</v>
@@ -15877,7 +15880,7 @@
         <v>1046</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>75</v>
@@ -15899,7 +15902,7 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>736</v>
@@ -15908,7 +15911,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>72</v>
@@ -15917,7 +15920,7 @@
         <v>1046</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>75</v>
@@ -15939,7 +15942,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>736</v>
@@ -15948,16 +15951,16 @@
         <v>30</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>75</v>
@@ -15968,9 +15971,7 @@
       <c r="J24" s="19" t="n">
         <v>46222</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>1055</v>
-      </c>
+      <c r="K24" s="15"/>
       <c r="L24" s="18" t="n">
         <v>1</v>
       </c>
@@ -15981,16 +15982,16 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>269</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>72</v>
@@ -15999,40 +16000,40 @@
         <v>141</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>1059</v>
+        <v>1166</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="18" t="n">
         <f aca="false">IF(H25="not applicable",IF(K25&lt;&gt;"",1,0),IF(I25="yes",IF(H25="verified",1,0),IF(OR(H25="tested",H25="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>269</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>72</v>
@@ -16041,31 +16042,31 @@
         <v>141</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>1062</v>
+        <v>1169</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="18" t="n">
         <f aca="false">IF(H26="not applicable",IF(K26&lt;&gt;"",1,0),IF(I26="yes",IF(H26="verified",1,0),IF(OR(H26="tested",H26="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>859</v>
@@ -16074,7 +16075,7 @@
         <v>197</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>72</v>
@@ -16083,31 +16084,29 @@
         <v>485</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K27" s="15"/>
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="18" t="n">
         <f aca="false">IF(H27="not applicable",IF(K27&lt;&gt;"",1,0),IF(I27="yes",IF(H27="verified",1,0),IF(OR(H27="tested",H27="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>859</v>
@@ -16116,7 +16115,7 @@
         <v>197</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>72</v>
@@ -16125,31 +16124,29 @@
         <v>485</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K28" s="15"/>
       <c r="L28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M28" s="18" t="n">
         <f aca="false">IF(H28="not applicable",IF(K28&lt;&gt;"",1,0),IF(I28="yes",IF(H28="verified",1,0),IF(OR(H28="tested",H28="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>859</v>
@@ -16158,7 +16155,7 @@
         <v>1042</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>72</v>
@@ -16167,31 +16164,29 @@
         <v>485</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>1066</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K29" s="15"/>
       <c r="L29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="18" t="n">
         <f aca="false">IF(H29="not applicable",IF(K29&lt;&gt;"",1,0),IF(I29="yes",IF(H29="verified",1,0),IF(OR(H29="tested",H29="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>779</v>
@@ -16200,7 +16195,7 @@
         <v>197</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>72</v>
@@ -16209,7 +16204,7 @@
         <v>1046</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>75</v>
@@ -16231,7 +16226,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>779</v>
@@ -16240,7 +16235,7 @@
         <v>197</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>72</v>
@@ -16249,40 +16244,38 @@
         <v>141</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>1078</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K31" s="15"/>
       <c r="L31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="18" t="n">
         <f aca="false">IF(H31="not applicable",IF(K31&lt;&gt;"",1,0),IF(I31="yes",IF(H31="verified",1,0),IF(OR(H31="tested",H31="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>72</v>
@@ -16291,7 +16284,7 @@
         <v>1046</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>75</v>
@@ -16300,11 +16293,9 @@
         <v>76</v>
       </c>
       <c r="J32" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>1078</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K32" s="15"/>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
@@ -16315,7 +16306,7 @@
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>760</v>
@@ -16324,7 +16315,7 @@
         <v>30</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>72</v>
@@ -16333,31 +16324,29 @@
         <v>141</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>1084</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K33" s="15"/>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="18" t="n">
         <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>862</v>
@@ -16366,7 +16355,7 @@
         <v>30</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>72</v>
@@ -16375,31 +16364,29 @@
         <v>141</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>1087</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K34" s="15"/>
       <c r="L34" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M34" s="18" t="n">
         <f aca="false">IF(H34="not applicable",IF(K34&lt;&gt;"",1,0),IF(I34="yes",IF(H34="verified",1,0),IF(OR(H34="tested",H34="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>550</v>
@@ -16408,16 +16395,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>75</v>
@@ -16426,11 +16413,9 @@
         <v>76</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>1087</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K35" s="15"/>
       <c r="L35" s="18" t="n">
         <v>1</v>
       </c>
@@ -16441,7 +16426,7 @@
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>550</v>
@@ -16450,7 +16435,7 @@
         <v>269</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>72</v>
@@ -16459,40 +16444,38 @@
         <v>141</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>1195</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K36" s="15"/>
       <c r="L36" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M36" s="18" t="n">
         <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>72</v>
@@ -16523,16 +16506,16 @@
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>72</v>
@@ -16563,16 +16546,16 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>72</v>
@@ -16603,16 +16586,16 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>269</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>72</v>
@@ -16643,16 +16626,16 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>72</v>
@@ -16661,7 +16644,7 @@
         <v>147</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>75</v>
@@ -16683,16 +16666,16 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>72</v>
@@ -16701,7 +16684,7 @@
         <v>147</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>75</v>
@@ -16710,11 +16693,9 @@
         <v>76</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>894</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K42" s="15"/>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
@@ -16725,7 +16706,7 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>99</v>
@@ -16734,7 +16715,7 @@
         <v>30</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -16752,11 +16733,9 @@
         <v>76</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>1111</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K43" s="15"/>
       <c r="L43" s="18" t="n">
         <v>1</v>
       </c>
@@ -16767,16 +16746,16 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -16785,31 +16764,29 @@
         <v>141</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>1111</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K44" s="15"/>
       <c r="L44" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M44" s="18" t="n">
         <f aca="false">IF(H44="not applicable",IF(K44&lt;&gt;"",1,0),IF(I44="yes",IF(H44="verified",1,0),IF(OR(H44="tested",H44="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>153</v>
@@ -16818,7 +16795,7 @@
         <v>30</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>155</v>
@@ -16827,7 +16804,7 @@
         <v>73</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>75</v>
@@ -16849,7 +16826,7 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>153</v>
@@ -16858,7 +16835,7 @@
         <v>30</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>155</v>
@@ -16867,7 +16844,7 @@
         <v>120</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>75</v>
@@ -16876,11 +16853,9 @@
         <v>76</v>
       </c>
       <c r="J46" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>1122</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K46" s="15"/>
       <c r="L46" s="18" t="n">
         <v>1</v>
       </c>
@@ -16891,44 +16866,42 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>252</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>1220</v>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="K47" s="15"/>
       <c r="L47" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M47" s="18" t="n">
         <f aca="false">IF(H47="not applicable",IF(K47&lt;&gt;"",1,0),IF(I47="yes",IF(H47="verified",1,0),IF(OR(H47="tested",H47="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16953,7 +16926,7 @@
     <hyperlink ref="G21" r:id="rId13" display="tests/hover-card.spec.ts"/>
     <hyperlink ref="G22" r:id="rId14" display="tests/hover-card.spec.ts"/>
     <hyperlink ref="G23" r:id="rId15" display="tests/hover-card.spec.ts"/>
-    <hyperlink ref="G24" r:id="rId16" display="@flowstack-ui/atom@0.3.5"/>
+    <hyperlink ref="G24" r:id="rId16" display="@flowstack-ui/atom@0.6.6"/>
     <hyperlink ref="G25" r:id="rId17" display="manual-tests/hover-card.md"/>
     <hyperlink ref="G26" r:id="rId18" display="manual-tests/hover-card.md"/>
     <hyperlink ref="G27" r:id="rId19" display="/hover-card"/>
@@ -17013,7 +16986,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17030,7 +17003,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17058,14 +17031,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.820512820512821</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -17079,7 +17052,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -17149,7 +17122,7 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>70</v>
@@ -17158,7 +17131,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>72</v>
@@ -17167,7 +17140,7 @@
         <v>73</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>75</v>
@@ -17176,7 +17149,7 @@
         <v>76</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="18" t="n">
@@ -17189,7 +17162,7 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>78</v>
@@ -17198,7 +17171,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>72</v>
@@ -17207,7 +17180,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>82</v>
@@ -17229,7 +17202,7 @@
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>1021</v>
@@ -17238,7 +17211,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>72</v>
@@ -17269,7 +17242,7 @@
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>50</v>
@@ -17278,7 +17251,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>72</v>
@@ -17287,7 +17260,7 @@
         <v>120</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>75</v>
@@ -17309,7 +17282,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>50</v>
@@ -17318,7 +17291,7 @@
         <v>180</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>72</v>
@@ -17349,16 +17322,16 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>72</v>
@@ -17367,7 +17340,7 @@
         <v>120</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>75</v>
@@ -17389,7 +17362,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>50</v>
@@ -17398,7 +17371,7 @@
         <v>269</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>72</v>
@@ -17407,7 +17380,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>75</v>
@@ -17429,7 +17402,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>50</v>
@@ -17438,7 +17411,7 @@
         <v>272</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>72</v>
@@ -17447,7 +17420,7 @@
         <v>73</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>75</v>
@@ -17469,7 +17442,7 @@
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>50</v>
@@ -17478,7 +17451,7 @@
         <v>197</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>72</v>
@@ -17487,7 +17460,7 @@
         <v>120</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>75</v>
@@ -17509,7 +17482,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>50</v>
@@ -17518,7 +17491,7 @@
         <v>183</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>72</v>
@@ -17527,7 +17500,7 @@
         <v>120</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>75</v>
@@ -17549,7 +17522,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>50</v>
@@ -17558,7 +17531,7 @@
         <v>187</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>72</v>
@@ -17589,7 +17562,7 @@
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>50</v>
@@ -17598,7 +17571,7 @@
         <v>190</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>72</v>
@@ -17629,16 +17602,16 @@
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>72</v>
@@ -17647,7 +17620,7 @@
         <v>73</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>75</v>
@@ -17669,7 +17642,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>50</v>
@@ -17678,7 +17651,7 @@
         <v>294</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>72</v>
@@ -17687,7 +17660,7 @@
         <v>120</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>75</v>
@@ -17709,7 +17682,7 @@
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>50</v>
@@ -17718,7 +17691,7 @@
         <v>1042</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>72</v>
@@ -17727,7 +17700,7 @@
         <v>120</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>75</v>
@@ -17749,7 +17722,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>835</v>
@@ -17758,7 +17731,7 @@
         <v>197</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>72</v>
@@ -17767,7 +17740,7 @@
         <v>1046</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>75</v>
@@ -17789,7 +17762,7 @@
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>835</v>
@@ -17798,7 +17771,7 @@
         <v>183</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>72</v>
@@ -17807,7 +17780,7 @@
         <v>147</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>75</v>
@@ -17829,25 +17802,25 @@
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>75</v>
@@ -17856,7 +17829,7 @@
         <v>76</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K26" s="15"/>
       <c r="L26" s="18" t="n">
@@ -17869,7 +17842,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>736</v>
@@ -17878,7 +17851,7 @@
         <v>31</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>72</v>
@@ -17887,7 +17860,7 @@
         <v>1046</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>75</v>
@@ -17909,7 +17882,7 @@
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>736</v>
@@ -17918,7 +17891,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>72</v>
@@ -17927,7 +17900,7 @@
         <v>1046</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>75</v>
@@ -17949,16 +17922,16 @@
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>736</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>72</v>
@@ -17967,7 +17940,7 @@
         <v>1046</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>75</v>
@@ -17989,16 +17962,16 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>736</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>72</v>
@@ -18007,7 +17980,7 @@
         <v>1046</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>75</v>
@@ -18029,7 +18002,7 @@
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>859</v>
@@ -18038,7 +18011,7 @@
         <v>197</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>72</v>
@@ -18047,7 +18020,7 @@
         <v>1046</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>75</v>
@@ -18069,7 +18042,7 @@
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>859</v>
@@ -18078,7 +18051,7 @@
         <v>197</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>72</v>
@@ -18087,31 +18060,31 @@
         <v>485</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J32" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>1066</v>
+        <v>1277</v>
       </c>
       <c r="L32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M32" s="18" t="n">
         <f aca="false">IF(H32="not applicable",IF(K32&lt;&gt;"",1,0),IF(I32="yes",IF(H32="verified",1,0),IF(OR(H32="tested",H32="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>859</v>
@@ -18120,7 +18093,7 @@
         <v>1042</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>72</v>
@@ -18129,31 +18102,31 @@
         <v>485</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>1066</v>
+        <v>1280</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="18" t="n">
         <f aca="false">IF(H33="not applicable",IF(K33&lt;&gt;"",1,0),IF(I33="yes",IF(H33="verified",1,0),IF(OR(H33="tested",H33="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>779</v>
@@ -18162,7 +18135,7 @@
         <v>197</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>72</v>
@@ -18171,7 +18144,7 @@
         <v>1046</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>75</v>
@@ -18193,7 +18166,7 @@
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>779</v>
@@ -18202,7 +18175,7 @@
         <v>197</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>72</v>
@@ -18211,31 +18184,31 @@
         <v>141</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>1078</v>
+        <v>1286</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="18" t="n">
         <f aca="false">IF(H35="not applicable",IF(K35&lt;&gt;"",1,0),IF(I35="yes",IF(H35="verified",1,0),IF(OR(H35="tested",H35="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>760</v>
@@ -18244,7 +18217,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>72</v>
@@ -18253,31 +18226,31 @@
         <v>141</v>
       </c>
       <c r="G36" s="16" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>46224</v>
+      </c>
+      <c r="K36" s="15" t="s">
         <v>1289</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>46222</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>1084</v>
       </c>
       <c r="L36" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M36" s="18" t="n">
         <f aca="false">IF(H36="not applicable",IF(K36&lt;&gt;"",1,0),IF(I36="yes",IF(H36="verified",1,0),IF(OR(H36="tested",H36="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>862</v>
@@ -18286,7 +18259,7 @@
         <v>31</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>72</v>
@@ -18295,31 +18268,31 @@
         <v>141</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>1087</v>
+        <v>1292</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M37" s="18" t="n">
         <f aca="false">IF(H37="not applicable",IF(K37&lt;&gt;"",1,0),IF(I37="yes",IF(H37="verified",1,0),IF(OR(H37="tested",H37="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>550</v>
@@ -18328,16 +18301,16 @@
         <v>31</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>75</v>
@@ -18359,16 +18332,16 @@
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>72</v>
@@ -18399,16 +18372,16 @@
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>72</v>
@@ -18426,7 +18399,7 @@
         <v>76</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K40" s="15"/>
       <c r="L40" s="18" t="n">
@@ -18439,16 +18412,16 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>72</v>
@@ -18479,16 +18452,16 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>197</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>72</v>
@@ -18519,16 +18492,16 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -18537,7 +18510,7 @@
         <v>147</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>75</v>
@@ -18559,7 +18532,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>99</v>
@@ -18568,7 +18541,7 @@
         <v>31</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -18599,16 +18572,16 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>72</v>
@@ -18617,26 +18590,26 @@
         <v>141</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>1111</v>
+        <v>1309</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M45" s="18" t="n">
         <f aca="false">IF(H45="not applicable",IF(K45&lt;&gt;"",1,0),IF(I45="yes",IF(H45="verified",1,0),IF(OR(H45="tested",H45="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18659,7 +18632,7 @@
         <v>120</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>75</v>
@@ -18696,7 +18669,7 @@
         <v>160</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>252</v>
@@ -18711,7 +18684,7 @@
         <v>46222</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>
@@ -18745,7 +18718,7 @@
     <hyperlink ref="G23" r:id="rId15" display="../test/components/popover.test.tsx"/>
     <hyperlink ref="G24" r:id="rId16" display="tests/popover.spec.ts"/>
     <hyperlink ref="G25" r:id="rId17" display="../docs/components/popover/README.md"/>
-    <hyperlink ref="G26" r:id="rId18" display="@flowstack-ui/atom@0.4.0"/>
+    <hyperlink ref="G26" r:id="rId18" display="@flowstack-ui/atom@0.6.10"/>
     <hyperlink ref="G27" r:id="rId19" display="tests/popover.spec.ts"/>
     <hyperlink ref="G28" r:id="rId20" display="tests/popover.spec.ts"/>
     <hyperlink ref="G29" r:id="rId21" display="tests/popover.spec.ts"/>
@@ -19302,7 +19275,7 @@
         <v>1343</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>1332</v>
@@ -19342,7 +19315,7 @@
         <v>1346</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>1335</v>
@@ -19794,7 +19767,7 @@
         <v>72</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>1351</v>
@@ -19862,7 +19835,7 @@
         <v>1377</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>1328</v>
@@ -19902,7 +19875,7 @@
         <v>1379</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>1332</v>
@@ -19942,7 +19915,7 @@
         <v>1381</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>1335</v>
@@ -19982,7 +19955,7 @@
         <v>1383</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>1318</v>
@@ -20022,7 +19995,7 @@
         <v>1385</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>1318</v>
@@ -20062,7 +20035,7 @@
         <v>1387</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>1328</v>
@@ -20102,7 +20075,7 @@
         <v>1390</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>1332</v>
@@ -20142,7 +20115,7 @@
         <v>1393</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>1335</v>
@@ -20222,7 +20195,7 @@
         <v>1398</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>1318</v>
@@ -20249,7 +20222,7 @@
         <v>46223</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>1111</v>
+        <v>1401</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>1</v>
@@ -20261,16 +20234,16 @@
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>1318</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>72</v>
@@ -20291,7 +20264,7 @@
         <v>46223</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>1066</v>
+        <v>1405</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
@@ -20303,16 +20276,16 @@
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>1318</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -20333,7 +20306,7 @@
         <v>46223</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1</v>
@@ -20345,7 +20318,7 @@
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>862</v>
@@ -20354,7 +20327,7 @@
         <v>1318</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -20375,7 +20348,7 @@
         <v>46223</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>1087</v>
+        <v>1412</v>
       </c>
       <c r="L44" s="18" t="n">
         <v>1</v>
@@ -20387,7 +20360,7 @@
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>153</v>
@@ -20396,7 +20369,7 @@
         <v>1318</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>155</v>
@@ -20405,7 +20378,7 @@
         <v>120</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>75</v>
@@ -20427,7 +20400,7 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>158</v>
@@ -20436,13 +20409,13 @@
         <v>1328</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>252</v>
@@ -20457,7 +20430,7 @@
         <v>46223</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="L46" s="18" t="n">
         <v>1</v>
@@ -20469,22 +20442,22 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>252</v>
@@ -20499,7 +20472,7 @@
         <v>46223</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>
@@ -27304,7 +27277,7 @@
       </c>
       <c r="H4" s="5" t="n">
         <f aca="false">COUNTIF(H9:H47,"blocked")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>15</v>
@@ -27408,7 +27381,7 @@
         <v>76</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="18" t="n">
@@ -28762,13 +28735,13 @@
         <v>515</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>253</v>
+        <v>347</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="K43" s="15" t="s">
         <v>518</v>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5132" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5132" uniqueCount="1421">
   <si>
     <t xml:space="preserve">Brick Component Coverage Index</t>
   </si>
@@ -4253,52 +4253,46 @@
     <t xml:space="preserve">FFB-32</t>
   </si>
   <si>
-    <t xml:space="preserve">Nine-section workbench covers APIs, models, state, reflow, groups, composition, appearance, relationships, and stress</t>
+    <t xml:space="preserve">Nine-scenario workbench separates Form, Field, and Fieldset review sections plus shared integration, composition, appearance, relationships, and stress evidence</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-33</t>
   </si>
   <si>
-    <t xml:space="preserve">Numbered visual, keyboard, touch, screen-reader, zoom, direction, preference, composition, and Consumer protocol has an owner run</t>
+    <t xml:space="preserve">Fourteen-step owner protocol has dedicated Form, Field, and Fieldset sections plus foundation integration checks</t>
   </si>
   <si>
     <t xml:space="preserve">../../docs/manual-tests/form-foundation.md</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner run pending</t>
+    <t xml:space="preserve">Owner protocol passed July 21, 2026; Windows forced colors not tested (no device)</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-34</t>
   </si>
   <si>
-    <t xml:space="preserve">Visual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner approves finished hierarchy, disabled/read-only distinction, error presentation, responsive reflow, and control alignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner visual review pending</t>
+    <t xml:space="preserve">Owner approves native submission models, callback state, reset, keyboard/touch behavior, and visible feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner Form review passed July 21, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-35</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical touch label activation, 200%/400% reflow, and mobile screen-reader behavior are owner-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner mobile and zoom review pending</t>
+    <t xml:space="preserve">Owner approves one-control anatomy, states, relationships, orientation, composition, touch, screen-reader, and zoom behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner Field review passed July 21, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-36</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduced motion and forced colors/Windows High Contrast boundaries are owner-approved where available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner preference review pending</t>
+    <t xml:space="preserve">Owner approves native group anatomy, states, relationships, composition, choice interaction, direction, and preferences where available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner Fieldset review passed July 21, 2026; Windows forced colors not tested (no device)</t>
   </si>
   <si>
     <t xml:space="preserve">FFB-37</t>
@@ -5260,7 +5254,7 @@
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(B8:B21,J8:J21)/SUM(B8:B21),0)</f>
-        <v>0.975238095238095</v>
+        <v>0.982857142857143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6062,7 +6056,7 @@
       </c>
       <c r="D21" s="8" t="n">
         <f aca="false">COUNTIF('Form Foundation'!H9:H47,"partial")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8" t="n">
         <f aca="false">COUNTIF('Form Foundation'!H9:H47,"implemented")</f>
@@ -6074,7 +6068,7 @@
       </c>
       <c r="G21" s="8" t="n">
         <f aca="false">COUNTIF('Form Foundation'!H9:H47,"verified")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" s="8" t="n">
         <f aca="false">COUNTIF('Form Foundation'!H9:H47,"blocked")</f>
@@ -6086,11 +6080,11 @@
       </c>
       <c r="J21" s="9" t="n">
         <f aca="false">IFERROR(SUM('Form Foundation'!M9:M47)/SUM('Form Foundation'!L9:L47),0)</f>
-        <v>0.871794871794872</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="K21" s="8" t="str">
         <f aca="false">IF(COUNTIFS('Form Foundation'!E9:E47,"package",'Form Foundation'!M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="L21" s="8" t="str">
         <f aca="false">IF(COUNTIFS('Form Foundation'!E9:E47,"consumer",'Form Foundation'!M9:M47,"&lt;1")=0,"complete","open")</f>
@@ -18821,14 +18815,14 @@
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">SUM(M9:M47)</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IFERROR(D4/SUM(L9:L47),0)</f>
-        <v>0.871794871794872</v>
+        <v>0.974358974358974</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>4</v>
@@ -18842,7 +18836,7 @@
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(COUNTIFS(E9:E47,"package",M9:M47,"&lt;1")=0,"complete","open")</f>
-        <v>open</v>
+        <v>complete</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>17</v>
@@ -20213,13 +20207,13 @@
         <v>1400</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K41" s="15" t="s">
         <v>1401</v>
@@ -20229,7 +20223,7 @@
       </c>
       <c r="M41" s="18" t="n">
         <f aca="false">IF(H41="not applicable",IF(K41&lt;&gt;"",1,0),IF(I41="yes",IF(H41="verified",1,0),IF(OR(H41="tested",H41="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20237,13 +20231,13 @@
         <v>1402</v>
       </c>
       <c r="B42" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>1403</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>1404</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>72</v>
@@ -20255,37 +20249,37 @@
         <v>1400</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="L42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M42" s="18" t="n">
         <f aca="false">IF(H42="not applicable",IF(K42&lt;&gt;"",1,0),IF(I42="yes",IF(H42="verified",1,0),IF(OR(H42="tested",H42="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D43" s="15" t="s">
         <v>1406</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>1408</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>72</v>
@@ -20297,37 +20291,37 @@
         <v>1400</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M43" s="18" t="n">
         <f aca="false">IF(H43="not applicable",IF(K43&lt;&gt;"",1,0),IF(I43="yes",IF(H43="verified",1,0),IF(OR(H43="tested",H43="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>862</v>
+        <v>1105</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>1318</v>
+        <v>1335</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>72</v>
@@ -20339,28 +20333,28 @@
         <v>1400</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>83</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="L44" s="18" t="n">
         <v>1</v>
       </c>
       <c r="M44" s="18" t="n">
         <f aca="false">IF(H44="not applicable",IF(K44&lt;&gt;"",1,0),IF(I44="yes",IF(H44="verified",1,0),IF(OR(H44="tested",H44="verified"),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>153</v>
@@ -20369,7 +20363,7 @@
         <v>1318</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>155</v>
@@ -20400,7 +20394,7 @@
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>158</v>
@@ -20409,13 +20403,13 @@
         <v>1328</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>252</v>
@@ -20430,7 +20424,7 @@
         <v>46223</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="L46" s="18" t="n">
         <v>1</v>
@@ -20442,16 +20436,16 @@
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>158</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>160</v>
@@ -20472,7 +20466,7 @@
         <v>46223</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>1</v>

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -39,9 +39,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surface" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divider" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scroll Area" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Block" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
@@ -1098,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -1117,7 +1119,7 @@
     <row r="2" ht="27.75" customHeight="1" s="17">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Current package evidence across 29 independently exported components.</t>
+          <t>Current package evidence across 31 independently exported components.</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2768,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" s="17">
       <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Scroll Area</t>
@@ -2821,8 +2823,118 @@
         <v/>
       </c>
     </row>
+    <row r="37" s="17">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B37" s="23">
+        <f>INDIRECT("'"&amp;A37&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I37" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A37&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J37" s="24">
+        <f>INDIRECT("'"&amp;A37&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K37" s="23">
+        <f>INDIRECT("'"&amp;A37&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L37" s="23">
+        <f>INDIRECT("'"&amp;A37&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M37" s="23">
+        <f>IF(AND(J37=1,K37="complete",L37="complete"),"complete",IF(H37&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" s="17">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="B38" s="23">
+        <f>INDIRECT("'"&amp;A38&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I38" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A38&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J38" s="24">
+        <f>INDIRECT("'"&amp;A38&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K38" s="23">
+        <f>INDIRECT("'"&amp;A38&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L38" s="23">
+        <f>INDIRECT("'"&amp;A38&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M38" s="23">
+        <f>IF(AND(J38=1,K38="complete",L38="complete"),"complete",IF(H38&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:M34"/>
+  <autoFilter ref="A7:M38"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -29513,6 +29625,2225 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Code Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level inline semantics, recipes, browser, human-review, documentation, Consumer, and adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A25)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M25)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I25,"yes",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E25,"consumer",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>CO-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Native code host, refs, slots, classes, styles, and closed recipes render from one server-safe component.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>CO-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Root and Code subpath exports expose the runtime and every public type.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>CO-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Recipes, native attributes, content, and HTMLElement ref contracts type-check.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/code.test.ts</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>CO-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships inline recipes, wrapping, forced colors, and public variables.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code/code.css</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>CO-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, recipes, native forwarding, ref, events, and semantic host pass focused tests.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/code/code.test.tsx</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>CO-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Inline context, native output, wrapping, RTL, zoom, and focus neutrality pass.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>CO-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Native semantics, meaningful prose context, text spacing, and axe remain correct.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CO-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, recipes, appearances, customization, narrow layout, and RTL own baselines.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K16" s="27" t="inlineStr">
+        <is>
+          <t>Human snapshot review is pending.</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CO-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Long literals, narrow widths, RTL prose, zoom, and text spacing remain readable.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code.md</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; human run is pending.</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CO-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>The component-owned protocol covers every Code playground scenario.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code.md</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; human run is pending.</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CO-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed usage, recipes, semantics, API, tokens, and exclusions pass.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code/README.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K19" s="27" t="n"/>
+      <c r="L19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CO-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Code owns a public changelog and the package changelog records its addition.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; the owner deferred the human run.</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CO-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>The packed Consumer proves the public subpath in realistic prose.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K21" s="27" t="n"/>
+      <c r="L21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CO-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Inline technical displays adopt Code and raw code hosts are rejected.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>docs/code-adoption-audit.md; ../scripts/verify-playground-code.mjs</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CO-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, tarball, consumers, browser matrix, and adoption checks pass.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>../test/package; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Automated and human release gates are pending.</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="26" t="n"/>
+      <c r="M24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Code Block Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level compound source, Clipboard, overflow, browser, human-review, documentation, Consumer, and adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A25)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M25)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I25,"yes",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E25,"consumer",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>CB-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Root and anatomy</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Atom Clipboard Root plus Header, Title, Language, Actions, Content, and copy parts compose correctly.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code-block</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>CB-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Content composes one Scroll Area viewport and canonical pre &gt; Brick Code markup.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/code-block/code-block.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>CB-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Clipboard</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Copy parts</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>CopyTrigger, indicators, status, pending, success, failure, timeout, and disabled state use Atom Clipboard.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/code-block/code-block.test.tsx</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>CB-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Root and Code Block subpath exports expose the compound runtime and every public type.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>CB-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Anatomy, recipes, wrap policy, Clipboard props, native props, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/code-block.test.ts</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>CB-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships surfaces, density, overflow, wrapping, selection, focus, forced colors, and tokens.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code-block/code-block.css</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>CB-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Overflow, wrap, copy outcomes, focus retention, disabled state, RTL, and reflow pass.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>CB-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Content and copy</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Named scroll content, truthful live feedback, keyboard reachability, and axe pass.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>CB-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, recipes, anatomy, content, overflow, copy, appearances, mobile, and RTL own baselines.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>Human snapshot review is pending.</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CB-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Mobile, zoom, long lines, many lines, RTL chrome, LTR source, and selection remain usable.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code-block.md</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; human run is pending.</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>CB-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>The component-owned protocol covers every Code Block playground scenario.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code-block.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; human run is pending.</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>CB-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed anatomy, copy ownership, highlighting boundary, accessibility, API, and tokens pass.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code-block/README.md</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; the owner deferred the human run.</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>CB-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Code Block owns a public changelog and the package changelog records its addition.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code-block/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K21" s="27" t="n"/>
+      <c r="L21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>CB-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>The packed Consumer proves public subpath anatomy, native source, and copy action.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CB-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Structured technical displays adopt Code Block with no raw pre/code hosts.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>docs/code-adoption-audit.md; ../scripts/verify-playground-code.mjs</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K23" s="27" t="n"/>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>CB-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Code Block</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, Atom dependency, tarball, consumers, browser matrix, and adoption pass.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../test/package; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>Automated and human release gates are pending.</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -41,6 +41,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scroll Area" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Block" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nav List" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$38</definedName>
@@ -1100,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -2930,6 +2931,61 @@
       </c>
       <c r="M38" s="23">
         <f>IF(AND(J38=1,K38="complete",L38="complete"),"complete",IF(H38&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>INDIRECT("'"&amp;A39&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I39" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A39&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J39" s="24">
+        <f>INDIRECT("'"&amp;A39&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K39" s="23">
+        <f>INDIRECT("'"&amp;A39&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L39" s="23">
+        <f>INDIRECT("'"&amp;A39&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M39" s="23">
+        <f>IF(AND(J39=1,K39="complete",L39="complete"),"complete",IF(H39&gt;0,"blocked","open"))</f>
         <v/>
       </c>
     </row>
@@ -31844,6 +31900,1185 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Nav List Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom anatomy, recipes, disclosure, browser, human-review, documentation, Consumer, and adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A25)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M25)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I25,"yes",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E25,"consumer",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>NL-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Root and anatomy</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Root, List, Item, Link, Section, SectionLabel, SectionTrigger, and SectionContent compose correctly.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code-block</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr"/>
+      <c r="M9" s="26">
+        <f>IF(OR(H9="not started",H9="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>NL-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Soft, solid, and outline; accent and neutral; small, medium, and large preserve declared defaults.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/code-block/code-block.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr"/>
+      <c r="M10" s="26">
+        <f>IF(OR(H10="not started",H10="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>NL-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Leading content, trailing content, descriptions, current, disabled, and composition remain aligned and semantic.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/code-block/code-block.test.tsx</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr"/>
+      <c r="M11" s="26">
+        <f>IF(OR(H11="not started",H11="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>NL-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Labeled, controlled, uncontrolled, disabled, and non-collapsible sections preserve Atom relationships.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr"/>
+      <c r="M12" s="26">
+        <f>IF(OR(H12="not started",H12="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>NL-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Root and Nav List subpath exports expose the compound runtime and every public type.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/code-block.test.ts</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr"/>
+      <c r="M13" s="26">
+        <f>IF(OR(H13="not started",H13="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>NL-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Anatomy, recipes, native props, composition, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/code-block/code-block.css</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K14" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr"/>
+      <c r="M14" s="26">
+        <f>IF(OR(H14="not started",H14="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>NL-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships state, orientation, focus, forced-colors, logical layout, and public tokens.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr"/>
+      <c r="M15" s="26">
+        <f>IF(OR(H15="not started",H15="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>NL-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, disclosure, disabled state, composition, horizontal wrapping, and RTL pass.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K16" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr"/>
+      <c r="M16" s="26">
+        <f>IF(OR(H16="not started",H16="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Navigation anatomy</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Names, lists, current state, disabled state, disclosure relationships, keyboard use, and axe pass.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/code-block/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="inlineStr"/>
+      <c r="M17" s="26">
+        <f>IF(OR(H17="not started",H17="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>NL-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, recipes, content, sections, output, appearances, mobile, RTL, and forced colors own baselines.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code-block.md</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="inlineStr"/>
+      <c r="M18" s="26">
+        <f>IF(OR(H18="not started",H18="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>NL-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>The component-owned protocol covers every Nav List playground scenario.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/code-block.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="inlineStr"/>
+      <c r="M19" s="26">
+        <f>IF(OR(H19="not started",H19="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>NL-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed ownership, anatomy, accessibility, API, CSS, and examples pass the documentation contract.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code-block/README.md</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="inlineStr"/>
+      <c r="M20" s="26">
+        <f>IF(OR(H20="not started",H20="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>NL-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Nav List owns a public changelog and the package changelog records its addition.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/code-block/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="inlineStr"/>
+      <c r="M21" s="26">
+        <f>IF(OR(H21="not started",H21="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>NL-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>The packed Consumer proves the public subpath in realistic workspace navigation.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="inlineStr"/>
+      <c r="M22" s="26">
+        <f>IF(OR(H22="not started",H22="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>NL-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>The route covers all approved scenarios and the shell adopts public Nav List anatomy.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>docs/code-adoption-audit.md; ../scripts/verify-playground-code.mjs</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="inlineStr"/>
+      <c r="M23" s="26">
+        <f>IF(OR(H23="not started",H23="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>NL-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Nav List</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, Atom dependency, tarball, consumers, browser matrix, and adoption pass.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../test/package; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="inlineStr"/>
+      <c r="M24" s="26">
+        <f>IF(OR(H24="not started",H24="partial"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Block" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nav List" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sidebar" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$38</definedName>
@@ -1101,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -2986,6 +2987,61 @@
       </c>
       <c r="M39" s="23">
         <f>IF(AND(J39=1,K39="complete",L39="complete"),"complete",IF(H39&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B40" s="23">
+        <f>INDIRECT("'"&amp;A40&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A40&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24">
+        <f>INDIRECT("'"&amp;A40&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K40" s="23">
+        <f>INDIRECT("'"&amp;A40&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L40" s="23">
+        <f>INDIRECT("'"&amp;A40&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M40" s="23">
+        <f>IF(AND(J40=1,K40="complete",L40="complete"),"complete",IF(H40&gt;0,"blocked","open"))</f>
         <v/>
       </c>
     </row>
@@ -33079,6 +33135,1101 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Sidebar Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom anatomy, app-shell geometry, recipes, states, browser, human-review, documentation, Consumer, and adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A25)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M25)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I25,"yes",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E25,"consumer",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Seven parts</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Root, Trigger, Panel, Header, Content, Footer, and Main compose with exact Atom and Brick ownership.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/sidebar</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr"/>
+      <c r="K9" s="27" t="inlineStr"/>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(H9="not started",H9="partial",H9="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Controlled/uncontrolled expanded, rail, offcanvas, targets, side, and disabled state preserve Atom 0.8.0.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/sidebar/sidebar.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr"/>
+      <c r="K10" s="27" t="inlineStr"/>
+      <c r="L10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(H10="not started",H10="partial",H10="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Root and Panel</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Docked/floating, small/medium/large, and static/sticky preserve declared defaults and geometry.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/sidebar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr"/>
+      <c r="K11" s="27" t="inlineStr"/>
+      <c r="L11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(H11="not started",H11="partial",H11="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>SB-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Trigger and Panel</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Generated relationships, native activation, disabled state, inert offcanvas content, landmarks, and rail names pass.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/sidebar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr"/>
+      <c r="K12" s="27" t="inlineStr"/>
+      <c r="L12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(H12="not started",H12="partial",H12="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>SB-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Native props, refs, render, asChild, classes, styles, and slot overrides preserve output.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/sidebar/sidebar.test.tsx</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr"/>
+      <c r="K13" s="27" t="inlineStr"/>
+      <c r="L13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(H13="not started",H13="partial",H13="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>SB-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Root and Sidebar subpath exports expose runtime and public types.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr"/>
+      <c r="K14" s="27" t="inlineStr"/>
+      <c r="L14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(H14="not started",H14="partial",H14="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>SB-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Recipes, Atom props, refs, composition, and Root size collision type-check.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/sidebar.test.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr"/>
+      <c r="K15" s="27" t="inlineStr"/>
+      <c r="L15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(H15="not started",H15="partial",H15="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>SB-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships state/side geometry, regions, focus, motion preferences, forced colors, and public variables.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/sidebar/sidebar.css</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr"/>
+      <c r="K16" s="27" t="inlineStr"/>
+      <c r="L16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(H16="not started",H16="partial",H16="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>SB-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, states, variants, sizes, placement, regions, behavior, appearance, stress, and forced colors own reviewed baselines.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/sidebar/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr"/>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(H17="not started",H17="partial",H17="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>SB-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Main containment, zero offcanvas track, right placement, sticky height, narrow floating, low height, zoom, and reduced motion remain usable.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/sidebar.md</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr"/>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(H18="not started",H18="partial",H18="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>SB-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>The component-owned protocol covers every Sidebar playground scenario.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/sidebar.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr"/>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(H19="not started",H19="partial",H19="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>SB-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed ownership, anatomy, states, recipes, Drawer boundary, accessibility, API, and tokens pass.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/sidebar/README.md</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr"/>
+      <c r="K20" s="27" t="inlineStr"/>
+      <c r="L20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(H20="not started",H20="partial",H20="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>SB-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Sidebar owns a public changelog and package changelog entry.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/sidebar/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr"/>
+      <c r="K21" s="27" t="inlineStr"/>
+      <c r="L21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(H21="not started",H21="partial",H21="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>SB-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>The packed Consumer proves public Sidebar with Nav List and an external Trigger.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr"/>
+      <c r="K22" s="27" t="inlineStr"/>
+      <c r="L22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(H22="not started",H22="partial",H22="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>SB-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>The route covers all scenarios and desktop shell adopts Sidebar while mobile Drawer policy remains application-owned.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>adoption</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>../scripts/verify-playground-sidebar.mjs</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr"/>
+      <c r="K23" s="27" t="inlineStr"/>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(H23="not started",H23="partial",H23="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>SB-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, Atom dependency, tarball, consumers, browser matrix, and adoption pass.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr"/>
+      <c r="K24" s="27" t="inlineStr"/>
+      <c r="L24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(OR(H24="not started",H24="partial",H24="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -43,9 +43,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Block" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nav List" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sidebar" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Icon" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$8:$M$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
@@ -1102,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -3045,8 +3046,63 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="B41" s="23">
+        <f>INDIRECT("'"&amp;A41&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I41" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A41&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24">
+        <f>INDIRECT("'"&amp;A41&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K41" s="23">
+        <f>INDIRECT("'"&amp;A41&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L41" s="23">
+        <f>INDIRECT("'"&amp;A41&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M41" s="23">
+        <f>IF(AND(J41=1,K41="complete",L41="complete"),"complete",IF(H41&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:M38"/>
+  <autoFilter ref="A8:M41"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -34230,6 +34286,1142 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Icon Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level SVG presentation, accessibility, recipes, browser, human-review, documentation, Consumer, and scoped adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A25)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M25)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I25,"yes",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E25,"consumer",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>IC-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Default wrapper and SVG-only asChild composition preserve one source graphic with deterministic props and ref.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/icon</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(H9="not started",H9="partial",H9="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>IC-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Decorative default, direct label, and label-reference modes emit mutually exclusive native image semantics.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/icon/icon.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(H10="not started",H10="partial",H10="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>IC-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Six sizes, nine semantic tones, default medium inherited presentation, and currentColor remain exact.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/icon/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(H11="not started",H11="partial",H11="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>IC-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Only directional icons mirror in genuine RTL; non-directional sources retain identity.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/icon/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(H12="not started",H12="partial",H12="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>IC-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Graphic</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Inline, reusable React SVG, external-library-shaped, and fixed multicolor sources preserve authored geometry and fills.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../playground/src/components/icon/IconPage.tsx</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(H13="not started",H13="partial",H13="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>IC-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Native props, classes, styles, slot override, wrapper-free SVG, and ref composition preserve output.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/icon/icon.test.tsx</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(H14="not started",H14="partial",H14="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>IC-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Root and Icon subpath exports expose runtime and public types.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(H15="not started",H15="partial",H15="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>IC-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Closed recipes and mutually exclusive accessibility modes reject invalid hosts, colors, sizes, and label combinations.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/icon.test.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(H16="not started",H16="partial",H16="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>IC-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships sizing, semantic foregrounds, direction, forced colors, and documented public properties.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/icon/icon.css</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(H17="not started",H17="partial",H17="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>IC-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, sizes, tones, sources, direction, appearance, stress, and forced colors own reviewable baselines.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/icon/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(H18="not started",H18="partial",H18="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>IC-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Narrow frames, large sizes, long referenced labels, zoom, text spacing, and mobile widths remain contained.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/icon.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(H19="not started",H19="partial",H19="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>IC-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>The concise protocol covers every Icon playground scenario and assistive-technology mode.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/icon.md</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="n"/>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Human run pending.</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(H20="not started",H20="partial",H20="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>IC-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed ownership, SVG boundary, accessibility, API, recipes, tokens, and composition pass.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/icon/README.md</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="27" t="n"/>
+      <c r="L21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(H21="not started",H21="partial",H21="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>IC-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Icon owns a public changelog and package changelog entry.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/icon/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(H22="not started",H22="partial",H22="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>IC-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>The Consumer proves the public Icon subpath inside a named IconButton.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="27" t="n"/>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(H23="not started",H23="partial",H23="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>IC-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>The route covers all scenarios and shell adoption follows explicit component-owned exclusions.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>adoption</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../scripts/verify-playground-icon.mjs; ../playground/docs/icon-adoption-audit.md</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(OR(H24="not started",H24="partial",H24="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>IC-17</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR-safe import, exports, CSS, tarball, Consumer, browser, and adoption checks pass.</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="26">
+        <f>IF(OR(H25="not started",H25="partial",H25="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nav List" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sidebar" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Icon" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Image" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$8:$M$41</definedName>
@@ -1103,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -3098,6 +3099,61 @@
       </c>
       <c r="M41" s="23">
         <f>IF(AND(J41=1,K41="complete",L41="complete"),"complete",IF(H41&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="B42" s="23">
+        <f>INDIRECT("'"&amp;A42&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I42" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A42&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J42" s="24">
+        <f>INDIRECT("'"&amp;A42&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K42" s="23">
+        <f>INDIRECT("'"&amp;A42&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L42" s="23">
+        <f>INDIRECT("'"&amp;A42&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M42" s="23">
+        <f>IF(AND(J42=1,K42="complete",L42="complete"),"complete",IF(H42&gt;0,"blocked","open"))</f>
         <v/>
       </c>
     </row>
@@ -35422,6 +35478,1592 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M200"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Image Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level media lifecycle, accessibility, recipes, native output, browser, human-review, documentation, Consumer, and scoped adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A30)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M30)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E25,"package",M9:M25,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I30,"yes",M9:M30,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E30,"consumer",M9:M30,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>IM-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Root / Content / Fallback</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Atom Image anatomy is styled without replacing source lifecycle, refs, or conditional parts.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/image</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(H9="not started",H9="partial",H9="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>IM-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Source state</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Idle, loading, loaded, error, source replacement, and stale-event rejection remain Atom-owned and observable.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>atom</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>@flowstack-ui/atom@0.9.0 Image tests; ../test/components/image/image.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(H10="not started",H10="partial",H10="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>IM-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Native output</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Required authored alt plus intrinsic, responsive, loading, decoding, priority, event, slot, and ref props reach the native image.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/image/image.test.tsx; ../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(H11="not started",H11="partial",H11="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>IM-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Authored idle, loading, and error fallbacks are mutually exclusive with Content and preserve reserved geometry.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(H12="not started",H12="partial",H12="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>IM-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Cover, contain, fill, none, and scale-down change only object fit inside controlled fixtures.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(H13="not started",H13="partial",H13="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>IM-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Center, top, bottom, logical start, and logical end move focal content; start/end reverse in RTL without mirroring pixels.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(H14="not started",H14="partial",H14="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>IM-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Five radius recipes, transparent/subtle frame, and explicit Atom Aspect Ratio preserve one clipped media box.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(H15="not started",H15="partial",H15="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>IM-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Content / Fallback</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Informative, decorative, and named-action alt ownership is explicit; fallback adds no focus or live-region policy.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(H16="not started",H16="partial",H16="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>IM-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Default, asChild, render, native props, custom slots, styles, and refs preserve Atom composition and valid hosts.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/image/image.test.tsx</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(H17="not started",H17="partial",H17="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>IM-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Package root and Image subpath expose one runtime namespace and public types.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="27" t="n"/>
+      <c r="L18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(H18="not started",H18="partial",H18="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>IM-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Required alt, closed recipes, root source ownership, native responsive props, and refs are enforced.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/image.test.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="27" t="n"/>
+      <c r="L19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(H19="not started",H19="partial",H19="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>IM-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships fit, logical position, clipping, frame, fallback, forced colors, and documented public properties.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/image/image.css</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="n"/>
+      <c r="K20" s="27" t="n"/>
+      <c r="L20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(H20="not started",H20="partial",H20="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>IM-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Idle/loading fallback output and recipe metadata render deterministically without a CSS loader.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="27" t="n"/>
+      <c r="L21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(H21="not started",H21="partial",H21="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>IM-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Nine numbered scenarios cover defaults, accessibility, fits, positions, geometry, native output, states, appearance, and stress.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>../playground/src/components/image/ImagePage.tsx; ../playground/tests/components/image/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(H22="not started",H22="partial",H22="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>IM-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, fits, positions, geometry, fallback, appearance, mobile, and forced colors own reviewed-risk baselines.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>../playground/tests/components/image/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Owner manual review pending.</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(H23="not started",H23="partial",H23="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>IM-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>Narrow, long fallback, RTL, mobile, zoom, text spacing, and physical-device containment are reviewed.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/image.md</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>Owner manual review pending.</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(OR(H24="not started",H24="partial",H24="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>IM-17</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>The concise protocol covers every Image scenario, source flow, appearance, device, and assistive-technology judgment.</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>../playground/manual-tests/image.md</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>Owner manual review pending.</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="26">
+        <f>IF(OR(H25="not started",H25="partial",H25="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1" s="17">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>IM-18</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed ownership, alt guidance, API, recipes, native attrs, tokens, composition, and exclusions pass.</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/image/README.md</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="27" t="n"/>
+      <c r="L26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="26">
+        <f>IF(OR(H26="not started",H26="partial",H26="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="17">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>IM-19</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Image owns a public changelog and package release-facing entry.</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/image/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="n"/>
+      <c r="K27" s="27" t="n"/>
+      <c r="L27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="26">
+        <f>IF(OR(H27="not started",H27="partial",H27="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1" s="17">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>IM-20</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>Consumer proves the public Image subpath as informative project media inside Card on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="28" t="n"/>
+      <c r="K28" s="27" t="n"/>
+      <c r="L28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="26">
+        <f>IF(OR(H28="not started",H28="partial",H28="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1" s="17">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>IM-21</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>Card finished media and Consumer adopt Image while Avatar and Icon Button native child evidence remain correctly owned.</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>adoption</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>../scripts/verify-playground-image.mjs; ../playground/docs/image-adoption-audit.md</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="n"/>
+      <c r="K29" s="27" t="n"/>
+      <c r="L29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="26">
+        <f>IF(OR(H29="not started",H29="partial",H29="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1" s="17">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>IM-22</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, archive, Consumer, browser, visual, docs, and adoption gates pass.</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F30" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs</t>
+        </is>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" s="28" t="n"/>
+      <c r="K30" s="27" t="n"/>
+      <c r="L30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="26">
+        <f>IF(OR(H30="not started",H30="partial",H30="implemented"),0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -45,10 +45,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sidebar" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Icon" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Image" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List" sheetId="39" ns1:id="rId39"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$8:$M$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$M$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$M$43</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
 </workbook>
@@ -1104,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="23" min="1" max="1"/>
@@ -1123,7 +1124,7 @@
     <row r="2" ht="27.75" customHeight="1" s="17">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Current package evidence across 31 independently exported components.</t>
+          <t>Current package evidence across 36 independently exported components.</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1135,7 @@
         </is>
       </c>
       <c r="B4" s="21">
-        <f>COUNTA(A8:A36)</f>
+        <f>COUNTA(A8:A43)</f>
         <v/>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -1143,7 +1144,7 @@
         </is>
       </c>
       <c r="E4" s="21">
-        <f>COUNTIF(M8:M36,"complete")</f>
+        <f>COUNTIF(M8:M43,"complete")</f>
         <v/>
       </c>
       <c r="G4" s="20" t="inlineStr">
@@ -1152,7 +1153,7 @@
         </is>
       </c>
       <c r="H4" s="21">
-        <f>COUNTIF(M8:M36,"blocked")</f>
+        <f>COUNTIF(M8:M43,"blocked")</f>
         <v/>
       </c>
       <c r="J4" s="20" t="inlineStr">
@@ -3157,8 +3158,63 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="B43" s="23">
+        <f>INDIRECT("'"&amp;A43&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I43" s="23">
+        <f>COUNTIF(INDIRECT("'"&amp;A43&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J43" s="24">
+        <f>INDIRECT("'"&amp;A43&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K43" s="23">
+        <f>INDIRECT("'"&amp;A43&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L43" s="23">
+        <f>INDIRECT("'"&amp;A43&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M43" s="23">
+        <f>IF(AND(J43=1,K43="complete",L43="complete"),"complete",IF(H43&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A8:M41"/>
+  <autoFilter ref="A7:M43"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -37064,6 +37120,1299 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="23" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="23" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="23" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="23" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="23" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="23" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="25" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="23" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="23" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>List Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level native semantics, anatomy, recipes, browser, human-review, documentation, Consumer, and adoption evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A27)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M27)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E27,"package",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I27,"yes",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E27,"consumer",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>L-01</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Root and Item</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Root and Item adapt released Atom List while preserving native ul, ol, li, attributes, slots, composition, refs, and authored children.</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/list</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="26">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>L-02</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Leading, Content, Title, Description, Trailing</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>All five optional structured parts expose stable native hosts, refs, slots, and aligned passive row anatomy.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/list/list.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="26">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>L-03</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Root and List subpath exports expose the compound runtime and every public List type.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../test/package/ssr.test.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="26">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>L-04</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Recipes, ordered attributes, native props, refs, disabled metadata, and Root/Item composition type-check.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>../test/types/components/list.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="26">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>L-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Static CSS ships variants, sizes, densities, all markers, structured anatomy, nesting, forced colors, and public variables.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>../src/components/list/list.css</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="26">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>L-06</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Defaults, recipes, native ordered output, disabled metadata, parts, composition, refs, and overrides pass focused tests.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>../test/components/list/list.test.tsx</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K14" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" s="26">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>L-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Browser</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Recipes and semantics</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Real-browser defaults, ordered and unordered output, variants, sizes, densities, markers, nesting, and native attributes pass.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/list/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" s="26">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>L-08</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Structured rows</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Leading, content, and trailing columns align, descriptions wrap, actions stay contained, and logical placement reverses in RTL.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/list/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K16" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" s="26">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>L-09</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Native list</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>List roles, item relationships, marker-free semantics, authored controls, disabled metadata, and axe pass without invented interaction.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/list/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" s="26">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>L-10</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Reviewed baselines cover defaults, boundaries, sizing, marker recipes, anatomy, dark customization, mobile RTL, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/list/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Current List playground and all eight visual baselines were reviewed during implementation.</t>
+        </is>
+      </c>
+      <c r="M18" s="26">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>L-11</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Physical mobile, 200%/400% zoom, rotation, narrow content, long copy, structured actions, and RTL remain readable and contained.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/list.md</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Automated reflow evidence passes; the human manual run is intentionally pending.</t>
+        </is>
+      </c>
+      <c r="M19" s="26">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>L-12</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Light, dark, forced colors, text spacing, markers, boundaries, and authored focus preserve hierarchy and contrast.</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/list.md; tests/components/list/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="n"/>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Automated appearance evidence passes; complete human appearance review is pending.</t>
+        </is>
+      </c>
+      <c r="M20" s="26">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>L-13</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Native output</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Root and Item</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>start, reversed, value, ordered output, nested lists, asChild, render ownership, and marker-none role behavior match the contract.</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>tests/components/list/behavior.spec.ts; ../test/components/list/list.test.tsx</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" s="26">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>L-14</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>The component-owned protocol covers every List playground scenario in one top-to-bottom review flow.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>manual-tests/list.md</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>Protocol exists; the owner deferred the human run.</t>
+        </is>
+      </c>
+      <c r="M22" s="26">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>L-15</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Source-backed ownership, anatomy, API, defaults, accessibility, CSS, customization, composition, and examples pass documentation gates.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/list/README.md</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" s="26">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>L-16</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>List owns a public component changelog and the package changelog records its addition.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>../docs/components/list/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>L-17</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>The packed Consumer proves the public List subpath in a realistic structured release checklist.</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M25" s="26">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1" s="17">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>L-18</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>The route covers all approved scenarios and eligible Consumer, Card, and Surface content lists adopt List with classified exclusions.</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr">
+        <is>
+          <t>docs/list-adoption-audit.md; ../scripts/verify-playground-list.mjs</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="n">
+        <v>46229</v>
+      </c>
+      <c r="K26" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M26" s="26">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="17">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>L-19</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Build, SSR, exports, CSS, Atom 0.9.1, tarball, React 18/19, packed Consumer, browser matrix, and adoption checks pass.</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>../test/package; ../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs; ../scripts/verify-playground-list.mjs</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="n"/>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>Automated package gates are tracked in the workstream; complete status waits for the component-owned human manual run.</t>
+        </is>
+      </c>
+      <c r="M27" s="26">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="H9:H27" type="list" allowBlank="0" showDropDown="0">
+      <formula1>"not started,partial,implemented,tested,verified,blocked,not applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I9:I27" type="list" allowBlank="0" showDropDown="0">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="24" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,15 +54,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breadcrumb" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabs" sheetId="46" state="visible" r:id="rId46"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skeleton" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown Menu" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context Menu" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menubar" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navigation Menu" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bottom Navigation" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visually Hidden" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$7:$M$57</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Index'!$A$1:$M$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'Select'!$A$8:$M$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'Textarea'!$A$8:$M$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'Radio Group'!$A$8:$M$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'Tabs'!$A$8:$M$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'Skeleton'!$A$8:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'Bottom Navigation'!$A$8:$M$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'Visually Hidden'!$A$8:$M$27</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
 </workbook>
@@ -1112,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.71" customWidth="1" style="15" min="1" max="1"/>
@@ -1141,7 +1149,7 @@
         </is>
       </c>
       <c r="B4" s="21">
-        <f>COUNTA(A8:A51)</f>
+        <f>COUNTA(A8:A57)</f>
         <v/>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -1150,7 +1158,7 @@
         </is>
       </c>
       <c r="E4" s="21">
-        <f>COUNTIF(M8:M51,"complete")</f>
+        <f>COUNTIF(M8:M57,"complete")</f>
         <v/>
       </c>
       <c r="G4" s="20" t="inlineStr">
@@ -1159,7 +1167,7 @@
         </is>
       </c>
       <c r="H4" s="21">
-        <f>COUNTIF(M8:M51,"blocked")</f>
+        <f>COUNTIF(M8:M57,"blocked")</f>
         <v/>
       </c>
       <c r="J4" s="20" t="inlineStr">
@@ -3659,13 +3667,343 @@
         <v/>
       </c>
     </row>
+    <row r="52" ht="15" customHeight="1" s="17">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="B52" s="15">
+        <f>INDIRECT("'"&amp;A52&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I52" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A52&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J52" s="16">
+        <f>INDIRECT("'"&amp;A52&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K52" s="15">
+        <f>INDIRECT("'"&amp;A52&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L52" s="15">
+        <f>INDIRECT("'"&amp;A52&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M52" s="15">
+        <f>IF(AND(J52=1,K52="complete",L52="complete"),"complete",IF(H52&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="17">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="B53" s="15">
+        <f>INDIRECT("'"&amp;A53&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I53" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A53&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J53" s="16">
+        <f>INDIRECT("'"&amp;A53&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K53" s="15">
+        <f>INDIRECT("'"&amp;A53&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L53" s="15">
+        <f>INDIRECT("'"&amp;A53&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M53" s="15">
+        <f>IF(AND(J53=1,K53="complete",L53="complete"),"complete",IF(H53&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="17">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="B54" s="15">
+        <f>INDIRECT("'"&amp;A54&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I54" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A54&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J54" s="16">
+        <f>INDIRECT("'"&amp;A54&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K54" s="15">
+        <f>INDIRECT("'"&amp;A54&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L54" s="15">
+        <f>INDIRECT("'"&amp;A54&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M54" s="15">
+        <f>IF(AND(J54=1,K54="complete",L54="complete"),"complete",IF(H54&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="17">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="B55" s="15">
+        <f>INDIRECT("'"&amp;A55&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I55" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A55&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J55" s="16">
+        <f>INDIRECT("'"&amp;A55&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K55" s="15">
+        <f>INDIRECT("'"&amp;A55&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L55" s="15">
+        <f>INDIRECT("'"&amp;A55&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M55" s="15">
+        <f>IF(AND(J55=1,K55="complete",L55="complete"),"complete",IF(H55&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="17">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="B56" s="15">
+        <f>INDIRECT("'"&amp;A56&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I56" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A56&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J56" s="16">
+        <f>INDIRECT("'"&amp;A56&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K56" s="15">
+        <f>INDIRECT("'"&amp;A56&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L56" s="15">
+        <f>INDIRECT("'"&amp;A56&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M56" s="15">
+        <f>IF(AND(J56=1,K56="complete",L56="complete"),"complete",IF(H56&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="17">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="B57" s="15">
+        <f>INDIRECT("'"&amp;A57&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"not started")</f>
+        <v/>
+      </c>
+      <c r="D57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"partial")</f>
+        <v/>
+      </c>
+      <c r="E57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"implemented")</f>
+        <v/>
+      </c>
+      <c r="F57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"tested")</f>
+        <v/>
+      </c>
+      <c r="G57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"verified")</f>
+        <v/>
+      </c>
+      <c r="H57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"blocked")</f>
+        <v/>
+      </c>
+      <c r="I57" s="15">
+        <f>COUNTIF(INDIRECT("'"&amp;A57&amp;"'!H9:H200"),"not applicable")</f>
+        <v/>
+      </c>
+      <c r="J57" s="16">
+        <f>INDIRECT("'"&amp;A57&amp;"'!H4")</f>
+        <v/>
+      </c>
+      <c r="K57" s="15">
+        <f>INDIRECT("'"&amp;A57&amp;"'!K4")</f>
+        <v/>
+      </c>
+      <c r="L57" s="15">
+        <f>INDIRECT("'"&amp;A57&amp;"'!E5")</f>
+        <v/>
+      </c>
+      <c r="M57" s="15">
+        <f>IF(AND(J57=1,K57="complete",L57="complete"),"complete",IF(H57&gt;0,"blocked","open"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:M51"/>
+  <autoFilter ref="A7:M57"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M8:M49">
+  <conditionalFormatting sqref="M8:M57">
     <cfRule type="containsText" rank="0" priority="2" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="complete" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("complete",M8)))</formula>
     </cfRule>
@@ -51114,6 +51452,3036 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Dropdown Menu Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed package, keyboard, browser, visual, accessibility, documentation, Consumer, composition, and responsive evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A31)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M31)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E31,"package",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I31,"yes",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E31,"consumer",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="17">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>DM-01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Brick styles released Atom 0.12.1 menu behavior without recreating open state, focus, keyboard, selection, dismissal, portals, or positioning.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/dropdown-menu</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="15">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="17">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>DM-02</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>The complete public namespace preserves trigger, popup, group, choice, indicator, static row, separator, arrow, and submenu ownership.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>../test/components/dropdown-menu/dropdown-menu.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="15">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="17">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>DM-03</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>DropdownMenu</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Root and dropdown-menu subpath expose the namespace, named parts, and public types with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="17">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>DM-04</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Closed sizes and tones plus Atom behavior, composition, native props, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>../test/types/components/dropdown-menu.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="17">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>DM-05</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Static CSS ships the popup surface, row anatomy, selection, danger, disabled, submenu, preference, and public-token recipes.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/dropdown-menu/dropdown-menu.css</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="17">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>DM-06</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Defaults</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Root/Trigger/Content/Item</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>A medium button-triggered menu opens with neutral rows and Atom-owned focus and dismissal.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="17">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>DM-07</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Content/SubContent</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Small, medium, and large change only shared popup row geometry and typography.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated size baselines.</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="17">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>DM-08</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Item anatomy</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Leading content, label, description, shortcut, groups, labels, separators, and Arrow align without changing command semantics.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected open and anatomy baselines.</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>DM-09</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>CheckboxItem/RadioItem</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Checked, mixed, and radio choices expose persistent Atom selection and visible indicators.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="17">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>DM-10</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>States</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Item/SubTrigger</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Neutral, highlighted, disabled, and danger commands remain distinct with identical default geometry.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts; tests/components/dropdown-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="17">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>DM-11</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Submenus</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Sub/SubTrigger/SubContent</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard and pointer submenu opening preserves nested focus, direction, collision, and dismissal.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="17">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>DM-12</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Trigger/Content</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Enter opens, menu focus enters, Escape closes, and focus returns to the trigger.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1" s="17">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>DM-13</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Trigger/static parts</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>asChild and render preserve the authored host, attributes, handlers, slots, and refs without duplicate controls.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>../test/components/dropdown-menu/dropdown-menu.test.tsx; tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected line and vertical baselines.</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1" s="17">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>DM-14</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Content/SubContent</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Constrained popups remain inside the viewport with reachable long and repeated commands.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts; tests/components/dropdown-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" s="17">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>DM-15</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Content/SubContent</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>RTL content and submenu direction mirror while authored text stays genuine.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" s="17">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>DM-16</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Named triggers and menus, roles, choice states, disabled state, focus return, forced colors, and axe pass.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="17">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>DM-17</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>DropdownMenu</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Reviewed baselines cover closed and open defaults, anatomy, choices, states, dark appearance, mobile RTL, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated Dropdown Menu baseline.</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="17">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>DM-18</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Interactive parts</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard opening, roving or adjacent navigation, activation, dismissal, and focus return remain Atom-owned.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/dropdown-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated Tabs baseline.</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="17">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>DM-19</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>A tester completes the concise top-to-bottom pointer, keyboard, AT, zoom, device, appearance, RTL, forced-color, and reduced-motion protocol.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>manual-tests/dropdown-menu.md</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="17">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>DM-20</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Source-backed usage, anatomy, API, recipes, accessibility, responsive behavior, composition, CSS, customization, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>../docs/components/dropdown-menu/README.md</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="15">
+        <f>IF(OR(AND(I28="yes",H28="verified"),AND(I28="no",OR(H28="tested",H28="verified")),AND(H28="not applicable",K28&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="17">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>DM-21</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>One navigable route exposes nine controlled scenarios and actual rendered composition output.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>src/components/dropdown-menu/DropdownMenuPage.tsx</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="15">
+        <f>IF(OR(AND(I29="yes",H29="verified"),AND(I29="no",OR(H29="tested",H29="verified")),AND(H29="not applicable",K29&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="17">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>DM-22</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and operates realistic component composition on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <f>IF(OR(AND(I30="yes",H30="verified"),AND(I30="no",OR(H30="tested",H30="verified")),AND(H30="not applicable",K30&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" s="17">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>DM-23</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, CSS, React 18/19, Consumer, configured browsers, docs, and exact Atom dependency pass.</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <f>IF(OR(AND(I31="yes",H31="verified"),AND(I31="no",OR(H31="tested",H31="verified")),AND(H31="not applicable",K31&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Context Menu Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed package, keyboard, browser, visual, accessibility, documentation, Consumer, composition, and responsive evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A31)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M31)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E31,"package",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I31,"yes",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E31,"consumer",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="17">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>CM-01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Brick styles released Atom 0.12.1 Context Menu behavior without recreating state, focus, keyboard, dismissal, portals, or positioning.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/context-menu</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="15">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="17">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>CM-02</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>The public namespace preserves every adopted host, semantic relationship, native prop, ref, and composition boundary.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>../test/components/context-menu/context-menu.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="15">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="17">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>CM-03</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>ContextMenu</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Root and component subpath expose the namespace, named parts, and public types with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="17">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CM-04</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Closed Brick recipes plus Atom behavior, composition, native props, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>../test/types/components/context-menu.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="17">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>CM-05</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Static CSS ships every adopted recipe, state, responsive boundary, preference mode, and public customization hook.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/context-menu/context-menu.css</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="17">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>CM-06</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Invocation</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Trigger/Content</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Pointer context gesture and Shift+F10 open at the intended target while essential actions remain visibly available.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="17">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>CM-07</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Content/SubContent</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Small, medium, and large change only popup row geometry and typography.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated component baselines.</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="17">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CM-08</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>All popup parts</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Groups, labels, rows, supporting content, separators, Arrow, choices, danger, disabled, and submenus remain aligned.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated component baselines.</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>CM-09</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>CheckboxItem/RadioItem</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Checked, mixed, and radio choices preserve Atom selection and indicators.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="17">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>CM-10</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>States</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Item/SubTrigger</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Neutral, highlighted, disabled, and danger commands stay distinct.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="17">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>CM-11</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Submenus</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Sub/SubTrigger/SubContent</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Nested context actions preserve keyboard direction, collision, focus, and dismissal.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="17">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CM-12</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Interactive parts</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard opening, roving or adjacent navigation, activation, dismissal, and focus return remain Atom-owned.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1" s="17">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>CM-13</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Composed parts</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>render and asChild preserve native hosts, semantic roles, attributes, state, handlers, slots, and refs.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected line and vertical baselines.</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1" s="17">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>CM-14</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Narrow viewports preserve reachable controls, constrained overlays, zoom, and the documented mobile boundary.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" s="17">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>CM-15</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Explicit RTL mirrors logical alignment and horizontal keyboard direction while preserving genuine text.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" s="17">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>CM-16</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Names, roles, states, keyboard order, focus, forced colors, and axe remain valid.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="17">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>CM-17</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Reviewed baselines cover defaults, recipes, states, dark appearance, mobile RTL, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated baseline.</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="17">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>CM-18</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Component-specific state and interaction remain covered by focused browser and unit evidence.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/context-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated Tabs baseline.</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="17">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>CM-19</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>A tester completes the concise top-to-bottom pointer, keyboard, AT, zoom, device, appearance, RTL, forced-color, and reduced-motion protocol.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>manual-tests/context-menu.md</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="17">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>CM-20</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Source-backed usage, anatomy, API, recipes, accessibility, responsive behavior, composition, CSS, customization, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>../docs/components/context-menu/README.md</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="15">
+        <f>IF(OR(AND(I28="yes",H28="verified"),AND(I28="no",OR(H28="tested",H28="verified")),AND(H28="not applicable",K28&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="17">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>CM-21</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>One navigable route exposes nine controlled scenarios and actual rendered composition output.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>src/components/context-menu/ContextMenuPage.tsx</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="15">
+        <f>IF(OR(AND(I29="yes",H29="verified"),AND(I29="no",OR(H29="tested",H29="verified")),AND(H29="not applicable",K29&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="17">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>CM-22</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and operates realistic component composition on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <f>IF(OR(AND(I30="yes",H30="verified"),AND(I30="no",OR(H30="tested",H30="verified")),AND(H30="not applicable",K30&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" s="17">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>CM-23</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Context Menu</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, CSS, React 18/19, Consumer, configured browsers, docs, and exact Atom dependency pass.</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <f>IF(OR(AND(I31="yes",H31="verified"),AND(I31="no",OR(H31="tested",H31="verified")),AND(H31="not applicable",K31&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -52228,6 +55596,6153 @@
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Menubar Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed package, keyboard, browser, visual, accessibility, documentation, Consumer, composition, and responsive evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A31)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M31)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E31,"package",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I31,"yes",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E31,"consumer",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="17">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>MB-01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Brick styles released Atom 0.12.1 Menubar behavior without recreating state, focus, keyboard, dismissal, portals, or positioning.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/menubar</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="15">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="17">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>MB-02</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>The public namespace preserves every adopted host, semantic relationship, native prop, ref, and composition boundary.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>../test/components/menubar/menubar.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="15">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="17">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>MB-03</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Root and component subpath expose the namespace, named parts, and public types with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="17">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>MB-04</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Closed Brick recipes plus Atom behavior, composition, native props, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>../test/types/components/menubar.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="17">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>MB-05</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Static CSS ships every adopted recipe, state, responsive boundary, preference mode, and public customization hook.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/menubar/menubar.css</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="17">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>MB-06</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Defaults</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Root/Menu/Trigger/Content</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>A medium horizontal menubar presents adjacent command categories and one Atom-owned popup.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="17">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>MB-07</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Root/Trigger</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Horizontal and vertical orientations change layout and adjacent-trigger keyboard axis together.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated variants baseline.</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="17">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>MB-08</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Root/Content</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Small, medium, and large change only persistent and popup control geometry.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated component baselines.</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>MB-09</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>States</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Trigger/Item</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Idle, focused, open, disabled, neutral, and danger states remain distinct.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="17">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>MB-10</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>CheckboxItem/RadioItem</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Persistent choices and indicators work inside command categories.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="17">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>MB-11</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Submenus</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Sub/SubTrigger/SubContent</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Nested command categories preserve focus, keyboard direction, and dismissal.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="17">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>MB-12</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Interactive parts</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard opening, roving or adjacent navigation, activation, dismissal, and focus return remain Atom-owned.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1" s="17">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>MB-13</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Composed parts</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>render and asChild preserve native hosts, semantic roles, attributes, state, handlers, slots, and refs.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected line and vertical baselines.</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1" s="17">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>MB-14</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Narrow viewports preserve reachable controls, constrained overlays, zoom, and the documented mobile boundary.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" s="17">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>MB-15</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Explicit RTL mirrors logical alignment and horizontal keyboard direction while preserving genuine text.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" s="17">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>MB-16</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Names, roles, states, keyboard order, focus, forced colors, and axe remain valid.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="17">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>MB-17</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Reviewed baselines cover defaults, recipes, states, dark appearance, mobile RTL, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated baseline.</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="17">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>MB-18</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Component-specific state and interaction remain covered by focused browser and unit evidence.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/menubar/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated Tabs baseline.</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="17">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>MB-19</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>A tester completes the concise top-to-bottom pointer, keyboard, AT, zoom, device, appearance, RTL, forced-color, and reduced-motion protocol.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>manual-tests/menubar.md</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="17">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>MB-20</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Source-backed usage, anatomy, API, recipes, accessibility, responsive behavior, composition, CSS, customization, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>../docs/components/menubar/README.md</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="15">
+        <f>IF(OR(AND(I28="yes",H28="verified"),AND(I28="no",OR(H28="tested",H28="verified")),AND(H28="not applicable",K28&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="17">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>MB-21</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>One navigable route exposes nine controlled scenarios and actual rendered composition output.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>src/components/menubar/MenubarPage.tsx</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="15">
+        <f>IF(OR(AND(I29="yes",H29="verified"),AND(I29="no",OR(H29="tested",H29="verified")),AND(H29="not applicable",K29&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="17">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>MB-22</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and operates realistic component composition on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <f>IF(OR(AND(I30="yes",H30="verified"),AND(I30="no",OR(H30="tested",H30="verified")),AND(H30="not applicable",K30&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" s="17">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>MB-23</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Menubar</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, CSS, React 18/19, Consumer, configured browsers, docs, and exact Atom dependency pass.</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <f>IF(OR(AND(I31="yes",H31="verified"),AND(I31="no",OR(H31="tested",H31="verified")),AND(H31="not applicable",K31&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Navigation Menu Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed package, keyboard, browser, visual, accessibility, documentation, Consumer, composition, and responsive evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A31)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M31)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E31,"package",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I31,"yes",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E31,"consumer",M9:M31,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="17">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>NM-01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Brick styles released Atom 0.12.1 Navigation Menu behavior without recreating state, focus, keyboard, dismissal, portals, or positioning.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/navigation-menu</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="15">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="17">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>NM-02</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>The public namespace preserves every adopted host, semantic relationship, native prop, ref, and composition boundary.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>../test/components/navigation-menu/navigation-menu.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="15">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="17">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>NM-03</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>NavigationMenu</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Root and component subpath expose the namespace, named parts, and public types with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="17">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>NM-04</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Closed Brick recipes plus Atom behavior, composition, native props, and refs type-check.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>../test/types/components/navigation-menu.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="17">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>NM-05</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Static CSS ships every adopted recipe, state, responsive boundary, preference mode, and public customization hook.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>../src/components/navigation-menu/navigation-menu.css</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="17">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>NM-06</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Defaults</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Root/List/Item/Trigger/Content</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>A medium horizontal navigation landmark combines native destinations with an optional rich panel.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="17">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>NM-07</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Link model</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Link/Trigger</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Direct current links remain anchors while disclosure triggers remain buttons.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated variants baseline.</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="17">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>NM-08</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Root/Sub</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Small, medium, and large change only navigation control geometry.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected generated component baselines.</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" s="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>NM-09</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Root/List</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Horizontal and vertical orientation change layout and keyboard axis together.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="17">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>NM-10</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Viewport</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Content/Viewport/Indicator</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Measured rich content, active trigger indicator, and viewport geometry follow Atom state.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="17">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>NM-11</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>States</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Trigger/Link</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Controlled open, current link, disabled trigger, hover, and focus states remain distinct.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="17">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>NM-12</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Interactive parts</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Keyboard opening, roving or adjacent navigation, activation, dismissal, and focus return remain Atom-owned.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1" s="17">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>NM-13</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Composed parts</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>render and asChild preserve native hosts, semantic roles, attributes, state, handlers, slots, and refs.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected line and vertical baselines.</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1" s="17">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>NM-14</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Narrow viewports preserve reachable controls, constrained overlays, zoom, and the documented mobile boundary.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" s="17">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>NM-15</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Explicit RTL mirrors logical alignment and horizontal keyboard direction while preserving genuine text.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1" s="17">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>NM-16</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Names, roles, states, keyboard order, focus, forced colors, and axe remain valid.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="17">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>NM-17</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Reviewed baselines cover defaults, recipes, states, dark appearance, mobile RTL, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated baseline.</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="17">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>NM-18</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Component-specific state and interaction remain covered by focused browser and unit evidence.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>tests/components/navigation-menu/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>Agent-inspected every generated Tabs baseline.</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="17">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>NM-19</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>A tester completes the concise top-to-bottom pointer, keyboard, AT, zoom, device, appearance, RTL, forced-color, and reduced-motion protocol.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>manual-tests/navigation-menu.md</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="17">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>NM-20</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Source-backed usage, anatomy, API, recipes, accessibility, responsive behavior, composition, CSS, customization, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>../docs/components/navigation-menu/README.md</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="15">
+        <f>IF(OR(AND(I28="yes",H28="verified"),AND(I28="no",OR(H28="tested",H28="verified")),AND(H28="not applicable",K28&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="17">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>NM-21</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>One navigable route exposes nine controlled scenarios and actual rendered composition output.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>src/components/navigation-menu/NavigationMenuPage.tsx</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="15">
+        <f>IF(OR(AND(I29="yes",H29="verified"),AND(I29="no",OR(H29="tested",H29="verified")),AND(H29="not applicable",K29&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="17">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>NM-22</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and operates realistic component composition on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <f>IF(OR(AND(I30="yes",H30="verified"),AND(I30="no",OR(H30="tested",H30="verified")),AND(H30="not applicable",K30&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" s="17">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>NM-23</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Navigation Menu</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, CSS, React 18/19, Consumer, configured browsers, docs, and exact Atom dependency pass.</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <f>IF(OR(AND(I31="yes",H31="verified"),AND(I31="no",OR(H31="tested",H31="verified")),AND(H31="not applicable",K31&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Bottom Navigation Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed recipes, destination behavior, position, labels, selection, accessibility, visual, documentation, Consumer, and package evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A36)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M36)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E36,"package",M9:M36,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I36,"yes",M9:M36,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E36,"consumer",M9:M36,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>BN-01</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Brick styles released Atom 0.13.0 Bottom Navigation behavior without recreating selection, native destination semantics, position, label visibility, disabled behavior, accessibility, refs, or composition.</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>../src/components/bottom-navigation</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="24">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>BN-02</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Root/Item/Icon/Label</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>The public four-part namespace preserves Atom's native nav, anchor/button destination, authored Icon/Label spans, semantic relationships, slots, props, refs, and static-content boundaries.</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/bottom-navigation/bottom-navigation.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="24">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>BN-03</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>BottomNavigation</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Root and bottom-navigation subpath expose the namespace, named parts, recipe types, inherited position/label types, and public props with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="24">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>BN-04</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Closed recipes and the discriminated indicator/item selection shapes type-check; unsupported sizes and a circular whole-item selection fail.</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>../test/types/components/bottom-navigation.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="24">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>BN-05</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Static CSS ships four variants, two tones, two layouts, two arrangements, three sizes, four positions, both selection targets, valid shapes, states, preferences, and documented variables.</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>../src/components/bottom-navigation/bottom-navigation.css</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="24">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>BN-06</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Defaults</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Root/Item/Icon/Label</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Defaults are outline, accent, full, equal, medium, static, indicator/pill, always-visible labels, safe-area support, and no blur or elevation.</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="24">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>BN-07</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Solid, soft, outline, and ghost remain visually distinct in accent and fully neutral palettes without changing destination geometry.</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="24">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>BN-08</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Root/Item</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Full versus floating controls outer geometry independently from equal versus centered destination distribution.</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="24">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>BN-09</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Small, medium, and large coordinate Root padding, Item target, Icon, indicator, and label typography as one recipe.</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="24">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>BN-10</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Static, sticky, absolute, and fixed retain distinct computed positioning; safe-area ownership is internal for full bars and an outer offset for positioned floating bars.</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; ../test/components/bottom-navigation/bottom-navigation.test.tsx</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="24">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>BN-11</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Root/Icon/Item</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>Indicator selection paints only Icon with circle, rounded, or pill geometry; Item selection paints the whole destination with square, rounded, or pill geometry and no layout shift.</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="24">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>BN-12</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Root/Label</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>always, active, and hidden policies change only visual label presentation while every destination retains the authored accessible name.</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="24">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>BN-13</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Selection behavior</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Root/Item</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Controlled and uncontrolled values update exactly one active destination and call the application change handler.</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/bottom-navigation/bottom-navigation.test.tsx; tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="24">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>BN-14</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Destinations/states</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>href Items remain native current-page anchors; Items without href remain buttons; hover, pressed, focus-visible, current, and disabled behavior stay distinct.</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; ../test/components/bottom-navigation/bottom-navigation.test.tsx</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="24">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>BN-15</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>Icon/Label</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>Three, four, and five destinations plus Notification Badge composition retain one destination name, one focus target, and bounded geometry.</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="24">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>BN-16</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>Router asChild output preserves the native anchor, href, state, Brick/Atom class and slot ownership without another interactive wrapper.</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/bottom-navigation/bottom-navigation.test.tsx; tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="24">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>BN-17</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Effects</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>Elevation and blur are opt-in paint effects that do not imply layout or position; reduced transparency removes blur while preserving the surface.</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="24">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1" s="17">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>BN-18</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Customization</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>The documented CSS variables exactly produce the amber surface, border, selected indicator, and active foreground shown beside the code.</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>src/components/bottom-navigation/BottomNavigationPage.tsx; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="25" t="inlineStr">
+        <is>
+          <t>Agent inspected the generated customization and appearance baselines.</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="24">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="17">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>BN-19</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>Narrow width, genuine long labels, three-to-five destinations, mobile viewports, and zoom guidance remain contained without horizontal page overflow.</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="24">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1" s="17">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>BN-20</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Direction/preferences</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>RTL uses logical order and genuine Arabic content; forced colors and reduced motion preserve selection, focus, and usable geometry.</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts; tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="24">
+        <f>IF(OR(AND(I28="yes",H28="verified"),AND(I28="no",OR(H28="tested",H28="verified")),AND(H28="not applicable",K28&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1" s="17">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>BN-21</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>Named navigation landmarks, native link/button roles, aria-current, disabled state, silent Icons, hidden labels, focus, target geometry, and axe remain valid.</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="24">
+        <f>IF(OR(AND(I29="yes",H29="verified"),AND(I29="no",OR(H29="tested",H29="verified")),AND(H29="not applicable",K29&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1" s="17">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>BN-22</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>All parts</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>Reviewed Chromium baselines cover defaults, all recipes, layout, selection, content, behavior, effects, dark appearance, mobile RTL, safe areas, and forced colors.</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/bottom-navigation/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>Agent inspected every revised Bottom Navigation baseline.</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="24">
+        <f>IF(OR(AND(I30="yes",H30="verified"),AND(I30="no",OR(H30="tested",H30="verified")),AND(H30="not applicable",K30&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1" s="17">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>BN-23</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>A tester completes the concise top-down pointer, keyboard, AT, zoom, mobile, safe-area, appearance, RTL, forced-color, and preference protocol.</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>manual-tests/bottom-navigation.md</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="24">
+        <f>IF(OR(AND(I31="yes",H31="verified"),AND(I31="no",OR(H31="tested",H31="verified")),AND(H31="not applicable",K31&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1" s="17">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>BN-24</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>Source-backed usage, anatomy, API, recipes, positions, labels, accessibility, responsive behavior, composition, CSS, customization, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>../docs/components/bottom-navigation/README.md</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="24">
+        <f>IF(OR(AND(I32="yes",H32="verified"),AND(I32="no",OR(H32="tested",H32="verified")),AND(H32="not applicable",K32&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1" s="17">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>BN-25</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>Bottom Navigation owns a public changelog and the package changelog records the public addition.</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>../docs/components/bottom-navigation/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="24">
+        <f>IF(OR(AND(I33="yes",H33="verified"),AND(I33="no",OR(H33="tested",H33="verified")),AND(H33="not applicable",K33&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1" s="17">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>BN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>One navigable route exposes nine comprehensive scenarios, actual rendered composition output, and Brick-only public imports.</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>src/components/bottom-navigation/BottomNavigationPage.tsx</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="24">
+        <f>IF(OR(AND(I34="yes",H34="verified"),AND(I34="no",OR(H34="tested",H34="verified")),AND(H34="not applicable",K34&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1" s="17">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>BN-27</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and operates realistic controlled and badged destinations on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="24">
+        <f>IF(OR(AND(I35="yes",H35="verified"),AND(I35="no",OR(H35="tested",H35="verified")),AND(H35="not applicable",K35&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1" s="17">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>BN-28</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>Bottom Navigation</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, CSS, React 18/19, Consumer, configured desktop/mobile browsers, docs, ownership, and exact Atom 0.13.0 dependency pass.</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="24">
+        <f>IF(OR(AND(I36="yes",H36="verified"),AND(I36="no",OR(H36="tested",H36="verified")),AND(H36="not applicable",K36&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:M36"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="H9:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"not started,partial,implemented,tested,verified,blocked,not applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I9:I36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.71" customWidth="1" style="15" min="1" max="1"/>
+    <col width="15.71" customWidth="1" style="15" min="2" max="2"/>
+    <col width="18.71" customWidth="1" style="15" min="3" max="3"/>
+    <col width="58.71" customWidth="1" style="15" min="4" max="4"/>
+    <col width="14.71" customWidth="1" style="15" min="5" max="6"/>
+    <col width="50.71" customWidth="1" style="15" min="7" max="7"/>
+    <col width="17.71" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.71" customWidth="1" style="15" min="9" max="9"/>
+    <col width="14.71" customWidth="1" style="23" min="10" max="10"/>
+    <col width="42.71" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.71" customWidth="1" style="15" min="12" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.5" customHeight="1" s="17">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Visually Hidden Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="17">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assertion-level Atom-backed assistive text, naming, composition, native ownership, accessibility, visual, documentation, Consumer, and package evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="17">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTA(A9:A27)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
+        <f>SUM(M9:M27)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(B4=0,0,E4/B4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Package gate</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(COUNTIFS(E9:E27,"package",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="17">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Manual review</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>IF(COUNTIFS(I9:I27,"yes",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Consumer gate</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
+        <f>IF(COUNTIFS(E9:E27,"consumer",M9:M27,0)&gt;0,"open","complete")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence type</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Evidence / link</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Human review?</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Blocker / N/A reason</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="17">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>VH-01</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Brick delegates all assistive-text behavior to released Atom 0.13.0 Visually Hidden and adds only the stable Brick class and default slot.</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>../src/components/visually-hidden</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="24">
+        <f>IF(OR(AND(I9="yes",H9="verified"),AND(I9="no",OR(H9="tested",H9="verified")),AND(H9="not applicable",K9&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="17">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>VH-02</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>The one-part namespace preserves Atom's default span, children, inline hiding behavior, native props, composition, and ref.</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/visually-hidden/visually-hidden.test.tsx</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="24">
+        <f>IF(OR(AND(I10="yes",H10="verified"),AND(I10="no",OR(H10="tested",H10="verified")),AND(H10="not applicable",K10&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="17">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>VH-03</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>VisuallyHidden</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Root and visually-hidden subpath expose the namespace, named Root, and Root props with identical runtime identities.</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>../test/package/package.test.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="24">
+        <f>IF(OR(AND(I11="yes",H11="verified"),AND(I11="no",OR(H11="tested",H11="verified")),AND(H11="not applicable",K11&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="17">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>VH-04</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Children, native span attributes, style, ref, render, and asChild type-check through the public subpath.</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>types</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>../test/types/components/visually-hidden.test.ts</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="24">
+        <f>IF(OR(AND(I12="yes",H12="verified"),AND(I12="no",OR(H12="tested",H12="verified")),AND(H12="not applicable",K12&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="17">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>VH-05</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Hooks</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Root emits the stable brick-visually-hidden class and default data-slot without inventing recipe props or public CSS variables.</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/visually-hidden/visually-hidden.test.tsx</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="24">
+        <f>IF(OR(AND(I13="yes",H13="verified"),AND(I13="no",OR(H13="tested",H13="verified")),AND(H13="not applicable",K13&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="17">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>VH-06</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Atom-owned inline styles resolve to an absolute 1px by 1px clipped box with no visible layout footprint.</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="24">
+        <f>IF(OR(AND(I14="yes",H14="verified"),AND(I14="no",OR(H14="tested",H14="verified")),AND(H14="not applicable",K14&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" s="17">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>VH-07</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Accessible naming</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Hidden text supplies the complete accessible name for an icon-only Brick Button while the Icon remains decorative.</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="24">
+        <f>IF(OR(AND(I15="yes",H15="verified"),AND(I15="no",OR(H15="tested",H15="verified")),AND(H15="not applicable",K15&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="17">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>VH-08</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Supplemental context</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Hidden context extends visible destructive-action text into one complete accessible name without duplicate visible copy.</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="24">
+        <f>IF(OR(AND(I16="yes",H16="verified"),AND(I16="no",OR(H16="tested",H16="verified")),AND(H16="not applicable",K16&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" s="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>VH-09</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>render and asChild change the host to strong or em while preserving hidden behavior, authored content, class, and slot.</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>../test/components/visually-hidden/visually-hidden.test.tsx; tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="24">
+        <f>IF(OR(AND(I17="yes",H17="verified"),AND(I17="no",OR(H17="tested",H17="verified")),AND(H17="not applicable",K17&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="17">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>VH-10</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Native ownership</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Consumer class, data attributes, authored slot, styles, and the default span ref pass through and remain inspectable.</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="24">
+        <f>IF(OR(AND(I18="yes",H18="verified"),AND(I18="no",OR(H18="tested",H18="verified")),AND(H18="not applicable",K18&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1" s="17">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>VH-11</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>Long English and Arabic names, RTL, dark appearance, narrow mobile layout, and zoom create no visible footprint or horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts; tests/components/visually-hidden/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="24">
+        <f>IF(OR(AND(I19="yes",H19="verified"),AND(I19="no",OR(H19="tested",H19="verified")),AND(H19="not applicable",K19&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" s="17">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>VH-12</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Named controls remain discoverable and the route has no automatically detectable accessibility violations across configured desktop/mobile browsers.</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>axe</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/behavior.spec.ts</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="24">
+        <f>IF(OR(AND(I20="yes",H20="verified"),AND(I20="no",OR(H20="tested",H20="verified")),AND(H20="not applicable",K20&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" s="17">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>VH-13</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Reviewed baselines prove that naming, composition, output, appearance, RTL, and mobile stress add no visible hidden-text footprint.</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>tests/components/visually-hidden/visual.spec.ts</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
+        <is>
+          <t>Agent inspected every Visually Hidden baseline.</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="24">
+        <f>IF(OR(AND(I21="yes",H21="verified"),AND(I21="no",OR(H21="tested",H21="verified")),AND(H21="not applicable",K21&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1" s="17">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>VH-14</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>A tester completes the concise naming, output, composition, native ownership, mobile, zoom, forced-color, and screen-reader protocol.</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>manual-tests/visually-hidden.md</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>Human run intentionally unclaimed.</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="24">
+        <f>IF(OR(AND(I22="yes",H22="verified"),AND(I22="no",OR(H22="tested",H22="verified")),AND(H22="not applicable",K22&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1" s="17">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>VH-15</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>Source-backed use, misuse, anatomy, API, hooks, customization limits, responsive behavior, accessibility, composition, and evidence are documented.</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>../docs/components/visually-hidden/README.md</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="24">
+        <f>IF(OR(AND(I23="yes",H23="verified"),AND(I23="no",OR(H23="tested",H23="verified")),AND(H23="not applicable",K23&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="17">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>VH-16</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Changelog</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>Visually Hidden owns a public changelog and the package changelog records the public addition.</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>../docs/components/visually-hidden/CHANGELOG.md; ../CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="24">
+        <f>IF(OR(AND(I24="yes",H24="verified"),AND(I24="no",OR(H24="tested",H24="verified")),AND(H24="not applicable",K24&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="17">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>VH-17</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>One navigable route exposes six focused scenarios, actual rendered output, composition evidence, native props, and responsive stress.</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>src/components/visually-hidden/VisuallyHiddenPage.tsx</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="24">
+        <f>IF(OR(AND(I25="yes",H25="verified"),AND(I25="no",OR(H25="tested",H25="verified")),AND(H25="not applicable",K25&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1" s="17">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>VH-18</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>Packed Consumer imports the public subpath and adds supplemental context to a real link on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>../apps/consumer/src/App.tsx; ../apps/consumer/tests/consumer.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="24">
+        <f>IF(OR(AND(I26="yes",H26="verified"),AND(I26="no",OR(H26="tested",H26="verified")),AND(H26="not applicable",K26&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="17">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>VH-19</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>Visually Hidden</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>Build, exports, SSR, tarball, React 18/19, Consumer, configured desktop/mobile browsers, docs, ownership, and exact Atom 0.13.0 dependency pass.</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>../scripts/verify-package.mjs; ../scripts/verify-consumers.mjs</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>tested</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="24">
+        <f>IF(OR(AND(I27="yes",H27="verified"),AND(I27="no",OR(H27="tested",H27="verified")),AND(H27="not applicable",K27&lt;&gt;"")),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1" s="17"/>
+    <row r="29" ht="54" customHeight="1" s="17"/>
+    <row r="30" ht="54" customHeight="1" s="17"/>
+    <row r="31" ht="54" customHeight="1" s="17"/>
+    <row r="32" ht="54" customHeight="1" s="17"/>
+    <row r="33" ht="54" customHeight="1" s="17"/>
+    <row r="34" ht="54" customHeight="1" s="17"/>
+    <row r="35" ht="54" customHeight="1" s="17"/>
+    <row r="36" ht="54" customHeight="1" s="17"/>
+  </sheetData>
+  <autoFilter ref="A8:M27"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="H9:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"not started,partial,implemented,tested,verified,blocked,not applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I9:I27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 

--- a/playground/component-coverage.xlsx
+++ b/playground/component-coverage.xlsx
@@ -7637,10 +7637,10 @@
     <t xml:space="preserve">Agent inspected the final appearance baselines.</t>
   </si>
   <si>
-    <t xml:space="preserve">Eight reviewed baselines cover overview, variants, sizing, sorting, sticky, dark, mobile RTL, and forced colors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent inspected every final Table baseline.</t>
+    <t xml:space="preserve">Ten reviewed baselines cover overview, variants, sizing, alignment, sorting, sticky, dark, responsive mobile, RTL mobile, and forced colors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent inspected every final Table baseline after the playground review corrections.</t>
   </si>
   <si>
     <t xml:space="preserve">Native structure, independent tab stops, no grid role/tabindex, labelled scrolling, and axe remain valid.</t>
@@ -11700,7 +11700,7 @@
         <v>open</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
@@ -57725,7 +57725,7 @@
         <v>98</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>2515</v>
